--- a/Data_analysis_using_excel/Employee_Table.xlsx
+++ b/Data_analysis_using_excel/Employee_Table.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VISHWAS SHARMA\Documents\Xcel_portfolio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VISHWAS SHARMA\Documents\Xcel_portfolio\Data_analysis_using_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{00D5458C-5812-4DCA-8012-3DA18A21E65B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1DB532B-BD5B-43E0-A709-EB5A3073B11F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="employee" sheetId="1" r:id="rId1"/>
@@ -285,6 +285,28 @@
 </comments>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="107">
   <si>
@@ -1365,31 +1387,19 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="153">
+  <cellXfs count="140">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1405,11 +1415,11 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1420,13 +1430,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1437,7 +1446,7 @@
     <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="13" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1454,23 +1463,19 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
@@ -1478,9 +1483,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1499,16 +1501,7 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1521,9 +1514,6 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1534,12 +1524,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -1552,14 +1536,14 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1580,33 +1564,25 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="40" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="43" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="3" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="0" borderId="42" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="43" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="44" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="45" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="32" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1616,7 +1592,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="46" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
@@ -1632,6 +1608,35 @@
     <xf numFmtId="1" fontId="10" fillId="0" borderId="30" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="15" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1641,24 +1646,24 @@
     <xf numFmtId="0" fontId="15" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="47" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="27" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1944,1476 +1949,1476 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="14.25" customHeight="1">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="130" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="B1" s="130"/>
+      <c r="C1" s="130"/>
+      <c r="D1" s="130"/>
+      <c r="E1" s="130"/>
+      <c r="F1" s="130"/>
+      <c r="G1" s="130"/>
+      <c r="H1" s="130"/>
     </row>
     <row r="2" spans="1:25" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A2" s="4"/>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4"/>
-      <c r="U2" s="5" t="s">
+      <c r="A2" s="130"/>
+      <c r="B2" s="130"/>
+      <c r="C2" s="130"/>
+      <c r="D2" s="130"/>
+      <c r="E2" s="130"/>
+      <c r="F2" s="130"/>
+      <c r="G2" s="130"/>
+      <c r="H2" s="130"/>
+      <c r="U2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="V2" s="5" t="s">
+      <c r="V2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="W2" s="129" t="s">
         <v>37</v>
       </c>
-      <c r="X2" s="2"/>
-      <c r="Y2" s="5" t="s">
+      <c r="X2" s="129"/>
+      <c r="Y2" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:25" ht="23.25" customHeight="1">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="140" t="s">
+      <c r="K3" s="131" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="141"/>
-      <c r="M3" s="141"/>
-      <c r="N3" s="141"/>
-      <c r="O3" s="141"/>
-      <c r="P3" s="141"/>
-      <c r="Q3" s="142"/>
-      <c r="U3" s="10">
+      <c r="L3" s="132"/>
+      <c r="M3" s="132"/>
+      <c r="N3" s="132"/>
+      <c r="O3" s="132"/>
+      <c r="P3" s="132"/>
+      <c r="Q3" s="133"/>
+      <c r="U3" s="6">
         <v>1</v>
       </c>
-      <c r="V3" s="146" t="s">
+      <c r="V3" s="120" t="s">
         <v>39</v>
       </c>
-      <c r="W3" s="10"/>
-      <c r="X3" s="10"/>
-      <c r="Y3" s="10" t="str">
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6" t="str">
         <f>INDEX(A3:H15,4,2)</f>
         <v>Kapil Singh</v>
       </c>
     </row>
     <row r="4" spans="1:25" ht="21" customHeight="1" thickBot="1">
-      <c r="A4" s="6">
+      <c r="A4" s="3">
         <v>20012</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="4">
         <v>26</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="3">
         <v>26500</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="5">
         <v>8877456987</v>
       </c>
-      <c r="K4" s="132" t="str">
+      <c r="K4" s="110" t="str" cm="1">
         <f t="array" ref="K4:Q4">_xlfn.XLOOKUP(A4,A3:A15,B3:H15)</f>
         <v>Kapil Sharma</v>
       </c>
-      <c r="L4" s="133">
+      <c r="L4" s="111">
         <v>26</v>
       </c>
-      <c r="M4" s="133" t="str">
+      <c r="M4" s="111" t="str">
         <v>Engineer</v>
       </c>
-      <c r="N4" s="133" t="str">
+      <c r="N4" s="111" t="str">
         <v>Technical</v>
       </c>
-      <c r="O4" s="133">
+      <c r="O4" s="111">
         <v>26500</v>
       </c>
-      <c r="P4" s="133" t="str">
+      <c r="P4" s="111" t="str">
         <v>Indore</v>
       </c>
-      <c r="Q4" s="139">
+      <c r="Q4" s="117">
         <v>8877456987</v>
       </c>
-      <c r="U4" s="10">
+      <c r="U4" s="6">
         <v>2</v>
       </c>
-      <c r="V4" s="146" t="s">
+      <c r="V4" s="120" t="s">
         <v>40</v>
       </c>
-      <c r="W4" s="147">
+      <c r="W4" s="121">
         <v>20012</v>
       </c>
-      <c r="X4" s="147" t="s">
+      <c r="X4" s="121" t="s">
         <v>3</v>
       </c>
-      <c r="Y4" s="10">
+      <c r="Y4" s="6">
         <f>INDEX(A3:H15,MATCH(W4,A3:A15,0),MATCH(X4,A3:H3,0))</f>
         <v>26</v>
       </c>
     </row>
     <row r="5" spans="1:25" ht="21" customHeight="1">
-      <c r="A5" s="6">
+      <c r="A5" s="3">
         <v>20013</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="4">
         <v>25</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="3">
         <v>13000</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="5">
         <v>8569741235</v>
       </c>
-      <c r="U5" s="10">
+      <c r="U5" s="6">
         <v>3</v>
       </c>
-      <c r="V5" s="146" t="s">
+      <c r="V5" s="120" t="s">
         <v>41</v>
       </c>
-      <c r="W5" s="10"/>
-      <c r="X5" s="10"/>
-      <c r="Y5" s="10">
+      <c r="W5" s="6"/>
+      <c r="X5" s="6"/>
+      <c r="Y5" s="6">
         <f>SUM(F4:F15)</f>
         <v>285000</v>
       </c>
     </row>
     <row r="6" spans="1:25" ht="21" customHeight="1">
-      <c r="A6" s="6">
+      <c r="A6" s="3">
         <v>20014</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="4">
         <v>28</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="3">
         <v>20000</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="5">
         <v>7584963214</v>
       </c>
-      <c r="U6" s="10">
+      <c r="U6" s="6">
         <v>4</v>
       </c>
-      <c r="V6" s="146" t="s">
+      <c r="V6" s="120" t="s">
         <v>42</v>
       </c>
-      <c r="W6" s="10"/>
-      <c r="X6" s="10"/>
-      <c r="Y6" s="10">
+      <c r="W6" s="6"/>
+      <c r="X6" s="6"/>
+      <c r="Y6" s="6">
         <f>MIN(F4:F15)</f>
         <v>13000</v>
       </c>
     </row>
     <row r="7" spans="1:25" ht="21" customHeight="1">
-      <c r="A7" s="6">
+      <c r="A7" s="3">
         <v>20015</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="4">
         <v>27</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="3">
         <v>15000</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="5">
         <v>7788994455</v>
       </c>
-      <c r="U7" s="10">
+      <c r="U7" s="6">
         <v>5</v>
       </c>
-      <c r="V7" s="146" t="s">
+      <c r="V7" s="120" t="s">
         <v>43</v>
       </c>
-      <c r="W7" s="10"/>
-      <c r="X7" s="10"/>
-      <c r="Y7" s="10">
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="6">
         <f>MAX(F4:F15)</f>
         <v>40500</v>
       </c>
     </row>
     <row r="8" spans="1:25" ht="21" customHeight="1">
-      <c r="A8" s="6">
+      <c r="A8" s="3">
         <v>20016</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="4">
         <v>25</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="25" t="s">
+      <c r="E8" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="143">
+      <c r="F8" s="118">
         <v>20000</v>
       </c>
-      <c r="G8" s="23" t="s">
+      <c r="G8" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="5">
         <v>8798654512</v>
       </c>
-      <c r="U8" s="10">
+      <c r="U8" s="6">
         <v>6</v>
       </c>
-      <c r="V8" s="146" t="s">
+      <c r="V8" s="120" t="s">
         <v>44</v>
       </c>
-      <c r="W8" s="10"/>
-      <c r="X8" s="10"/>
-      <c r="Y8" s="10">
+      <c r="W8" s="6"/>
+      <c r="X8" s="6"/>
+      <c r="Y8" s="6">
         <f>AVERAGE(F4:F15)</f>
         <v>23750</v>
       </c>
     </row>
     <row r="9" spans="1:25" ht="21" customHeight="1">
-      <c r="A9" s="6">
+      <c r="A9" s="3">
         <v>20017</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="4">
         <v>26</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="3">
         <v>33000</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="5">
         <v>9874563214</v>
       </c>
-      <c r="U9" s="10">
+      <c r="U9" s="6">
         <v>7</v>
       </c>
-      <c r="V9" s="146" t="s">
+      <c r="V9" s="120" t="s">
         <v>45</v>
       </c>
-      <c r="W9" s="10"/>
-      <c r="X9" s="10"/>
-      <c r="Y9" s="10">
+      <c r="W9" s="6"/>
+      <c r="X9" s="6"/>
+      <c r="Y9" s="6">
         <f>SUMIF(C4:C15,"&gt;25",F4:F15)</f>
         <v>231000</v>
       </c>
     </row>
     <row r="10" spans="1:25" ht="21" customHeight="1" thickBot="1">
-      <c r="A10" s="6">
+      <c r="A10" s="3">
         <v>20018</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="4">
         <v>25</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="3">
         <v>21000</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="5">
         <v>8974563214</v>
       </c>
-      <c r="U10" s="10">
+      <c r="U10" s="6">
         <v>8</v>
       </c>
-      <c r="V10" s="146" t="s">
+      <c r="V10" s="120" t="s">
         <v>46</v>
       </c>
-      <c r="W10" s="10"/>
-      <c r="X10" s="10"/>
-      <c r="Y10" s="10">
+      <c r="W10" s="6"/>
+      <c r="X10" s="6"/>
+      <c r="Y10" s="6">
         <f>SUMIF(E4:E15,E4,F4:F15)</f>
         <v>167000</v>
       </c>
     </row>
     <row r="11" spans="1:25" ht="21" customHeight="1" thickBot="1">
-      <c r="A11" s="6">
+      <c r="A11" s="3">
         <v>20019</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="4">
         <v>26</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="3">
         <v>31500</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="5">
         <v>8745968745</v>
       </c>
-      <c r="K11" s="135" t="s">
+      <c r="K11" s="113" t="s">
         <v>25</v>
       </c>
-      <c r="L11" s="136"/>
-      <c r="M11" s="136"/>
-      <c r="N11" s="136"/>
-      <c r="O11" s="136"/>
-      <c r="P11" s="136"/>
-      <c r="Q11" s="148"/>
-      <c r="U11" s="10">
+      <c r="L11" s="114"/>
+      <c r="M11" s="114"/>
+      <c r="N11" s="114"/>
+      <c r="O11" s="114"/>
+      <c r="P11" s="114"/>
+      <c r="Q11" s="25"/>
+      <c r="U11" s="6">
         <v>9</v>
       </c>
-      <c r="V11" s="146" t="s">
+      <c r="V11" s="120" t="s">
         <v>47</v>
       </c>
-      <c r="W11" s="10"/>
-      <c r="X11" s="10"/>
-      <c r="Y11" s="10">
+      <c r="W11" s="6"/>
+      <c r="X11" s="6"/>
+      <c r="Y11" s="6">
         <f>SUMIFS(F4:F15,E4:E15,E5,C4:C15,"&gt;26")</f>
         <v>55500</v>
       </c>
     </row>
     <row r="12" spans="1:25" ht="21" customHeight="1">
-      <c r="A12" s="6">
+      <c r="A12" s="3">
         <v>20020</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="4">
         <v>28</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="3">
         <v>40500</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="5">
         <v>9874569874</v>
       </c>
-      <c r="K12" s="64"/>
-      <c r="L12" s="149" t="str">
+      <c r="K12" s="56"/>
+      <c r="L12" s="122" t="str">
         <f t="array" ref="L12:N24">CHOOSE({1,2,3},F3:F15,C3:C15,A3:A15)</f>
         <v>Salary</v>
       </c>
-      <c r="M12" s="150" t="str">
+      <c r="M12" s="123" t="str">
         <v>Age</v>
       </c>
-      <c r="N12" s="150" t="str">
+      <c r="N12" s="123" t="str">
         <v>Emp. ID</v>
       </c>
-      <c r="O12" s="151"/>
-      <c r="P12" s="152"/>
-      <c r="U12" s="10">
+      <c r="O12" s="124"/>
+      <c r="P12" s="125"/>
+      <c r="U12" s="6">
         <v>10</v>
       </c>
-      <c r="V12" s="146" t="s">
+      <c r="V12" s="120" t="s">
         <v>48</v>
       </c>
-      <c r="W12" s="10"/>
-      <c r="X12" s="10"/>
-      <c r="Y12" s="10">
+      <c r="W12" s="6"/>
+      <c r="X12" s="6"/>
+      <c r="Y12" s="6">
         <f>COUNTIF(G4:G15,G5)</f>
         <v>4</v>
       </c>
     </row>
     <row r="13" spans="1:25" ht="21" customHeight="1">
-      <c r="A13" s="6">
+      <c r="A13" s="3">
         <v>20021</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="4">
         <v>27</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="3">
         <v>25500</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="5">
         <v>8574965874</v>
       </c>
-      <c r="K13" s="64"/>
-      <c r="L13" s="129">
+      <c r="K13" s="56"/>
+      <c r="L13" s="107">
         <v>26500</v>
       </c>
-      <c r="M13" s="130">
+      <c r="M13" s="108">
         <v>26</v>
       </c>
-      <c r="N13" s="130">
+      <c r="N13" s="108">
         <v>20012</v>
       </c>
-      <c r="O13" s="130"/>
-      <c r="P13" s="131"/>
-      <c r="U13" s="10">
+      <c r="O13" s="108"/>
+      <c r="P13" s="109"/>
+      <c r="U13" s="6">
         <v>11</v>
       </c>
-      <c r="V13" s="146" t="s">
+      <c r="V13" s="120" t="s">
         <v>49</v>
       </c>
-      <c r="W13" s="10"/>
-      <c r="X13" s="10"/>
-      <c r="Y13" s="10">
+      <c r="W13" s="6"/>
+      <c r="X13" s="6"/>
+      <c r="Y13" s="6">
         <f>VLOOKUP(B9,CHOOSE({1,2},B3:B15,A3:A15),2,0)</f>
         <v>20017</v>
       </c>
     </row>
     <row r="14" spans="1:25" ht="21" customHeight="1">
-      <c r="A14" s="6">
+      <c r="A14" s="3">
         <v>20022</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="4">
         <v>26</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="3">
         <v>18000</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="5">
         <v>8521479632</v>
       </c>
-      <c r="K14" s="64"/>
-      <c r="L14" s="129">
+      <c r="K14" s="56"/>
+      <c r="L14" s="107">
         <v>13000</v>
       </c>
-      <c r="M14" s="130">
+      <c r="M14" s="108">
         <v>25</v>
       </c>
-      <c r="N14" s="130">
+      <c r="N14" s="108">
         <v>20013</v>
       </c>
-      <c r="O14" s="130"/>
-      <c r="P14" s="131"/>
-      <c r="U14" s="10">
+      <c r="O14" s="108"/>
+      <c r="P14" s="109"/>
+      <c r="U14" s="6">
         <v>12</v>
       </c>
-      <c r="V14" s="146" t="s">
+      <c r="V14" s="120" t="s">
         <v>50</v>
       </c>
-      <c r="W14" s="10"/>
-      <c r="X14" s="10"/>
-      <c r="Y14" s="10">
+      <c r="W14" s="6"/>
+      <c r="X14" s="6"/>
+      <c r="Y14" s="6">
         <f>_xlfn.XLOOKUP(A4,A3:A15,C3:C15)</f>
         <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:25" ht="21" customHeight="1">
-      <c r="A15" s="6">
+      <c r="A15" s="3">
         <v>20023</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="4">
         <v>27</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="3">
         <v>21000</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="5">
         <v>8569745623</v>
       </c>
-      <c r="K15" s="64"/>
-      <c r="L15" s="129">
+      <c r="K15" s="56"/>
+      <c r="L15" s="107">
         <v>20000</v>
       </c>
-      <c r="M15" s="130">
+      <c r="M15" s="108">
         <v>28</v>
       </c>
-      <c r="N15" s="130">
+      <c r="N15" s="108">
         <v>20014</v>
       </c>
-      <c r="O15" s="130"/>
-      <c r="P15" s="131"/>
-      <c r="U15" s="10">
+      <c r="O15" s="108"/>
+      <c r="P15" s="109"/>
+      <c r="U15" s="6">
         <v>13</v>
       </c>
-      <c r="V15" s="146" t="s">
+      <c r="V15" s="120" t="s">
         <v>51</v>
       </c>
-      <c r="W15" s="147">
+      <c r="W15" s="121">
         <v>40500</v>
       </c>
-      <c r="X15" s="10"/>
-      <c r="Y15" s="10" t="str">
+      <c r="X15" s="6"/>
+      <c r="Y15" s="6" t="str">
         <f>VLOOKUP(W15,CHOOSE({1,2},F3:F15,B3:B15,),2,0)</f>
         <v>Vikas Patel</v>
       </c>
     </row>
     <row r="16" spans="1:25" ht="14.25" customHeight="1">
-      <c r="K16" s="64"/>
-      <c r="L16" s="129">
+      <c r="K16" s="56"/>
+      <c r="L16" s="107">
         <v>15000</v>
       </c>
-      <c r="M16" s="130">
+      <c r="M16" s="108">
         <v>27</v>
       </c>
-      <c r="N16" s="130">
+      <c r="N16" s="108">
         <v>20015</v>
       </c>
-      <c r="O16" s="130"/>
-      <c r="P16" s="131"/>
-      <c r="U16" s="10">
+      <c r="O16" s="108"/>
+      <c r="P16" s="109"/>
+      <c r="U16" s="6">
         <v>14</v>
       </c>
-      <c r="V16" s="146" t="s">
+      <c r="V16" s="120" t="s">
         <v>52</v>
       </c>
-      <c r="W16" s="10"/>
-      <c r="X16" s="10"/>
-      <c r="Y16" s="10">
+      <c r="W16" s="6"/>
+      <c r="X16" s="6"/>
+      <c r="Y16" s="6">
         <f>VLOOKUP(H5,CHOOSE({1,2},H3:H15,A3:A15),2,0)</f>
         <v>20013</v>
       </c>
     </row>
     <row r="17" spans="2:25" ht="14.25" customHeight="1">
-      <c r="K17" s="64"/>
-      <c r="L17" s="129">
+      <c r="K17" s="56"/>
+      <c r="L17" s="107">
         <v>20000</v>
       </c>
-      <c r="M17" s="130">
+      <c r="M17" s="108">
         <v>25</v>
       </c>
-      <c r="N17" s="130">
+      <c r="N17" s="108">
         <v>20016</v>
       </c>
-      <c r="O17" s="130"/>
-      <c r="P17" s="131"/>
-      <c r="U17" s="10">
+      <c r="O17" s="108"/>
+      <c r="P17" s="109"/>
+      <c r="U17" s="6">
         <v>15</v>
       </c>
-      <c r="V17" s="146" t="s">
+      <c r="V17" s="120" t="s">
         <v>53</v>
       </c>
-      <c r="W17" s="10"/>
-      <c r="X17" s="10"/>
-      <c r="Y17" s="10">
+      <c r="W17" s="6"/>
+      <c r="X17" s="6"/>
+      <c r="Y17" s="6">
         <f>SUM(_xlfn._xlws.FILTER(F3:F15,E3:E15="Technical"))</f>
         <v>167000</v>
       </c>
     </row>
     <row r="18" spans="2:25" ht="14.25" customHeight="1">
-      <c r="K18" s="64"/>
-      <c r="L18" s="129">
+      <c r="K18" s="56"/>
+      <c r="L18" s="107">
         <v>33000</v>
       </c>
-      <c r="M18" s="130">
+      <c r="M18" s="108">
         <v>26</v>
       </c>
-      <c r="N18" s="130">
+      <c r="N18" s="108">
         <v>20017</v>
       </c>
-      <c r="O18" s="130"/>
-      <c r="P18" s="131"/>
+      <c r="O18" s="108"/>
+      <c r="P18" s="109"/>
     </row>
     <row r="19" spans="2:25" ht="14.25" customHeight="1">
-      <c r="K19" s="64"/>
-      <c r="L19" s="129">
+      <c r="K19" s="56"/>
+      <c r="L19" s="107">
         <v>21000</v>
       </c>
-      <c r="M19" s="130">
+      <c r="M19" s="108">
         <v>25</v>
       </c>
-      <c r="N19" s="130">
+      <c r="N19" s="108">
         <v>20018</v>
       </c>
-      <c r="O19" s="130"/>
-      <c r="P19" s="131"/>
+      <c r="O19" s="108"/>
+      <c r="P19" s="109"/>
     </row>
     <row r="20" spans="2:25" ht="14.25" customHeight="1">
-      <c r="K20" s="64"/>
-      <c r="L20" s="129">
+      <c r="K20" s="56"/>
+      <c r="L20" s="107">
         <v>31500</v>
       </c>
-      <c r="M20" s="130">
+      <c r="M20" s="108">
         <v>26</v>
       </c>
-      <c r="N20" s="130">
+      <c r="N20" s="108">
         <v>20019</v>
       </c>
-      <c r="O20" s="130"/>
-      <c r="P20" s="131"/>
+      <c r="O20" s="108"/>
+      <c r="P20" s="109"/>
     </row>
     <row r="21" spans="2:25" ht="21" customHeight="1">
-      <c r="K21" s="64"/>
-      <c r="L21" s="129">
+      <c r="K21" s="56"/>
+      <c r="L21" s="107">
         <v>40500</v>
       </c>
-      <c r="M21" s="130">
+      <c r="M21" s="108">
         <v>28</v>
       </c>
-      <c r="N21" s="130">
+      <c r="N21" s="108">
         <v>20020</v>
       </c>
-      <c r="O21" s="130"/>
-      <c r="P21" s="131"/>
+      <c r="O21" s="108"/>
+      <c r="P21" s="109"/>
     </row>
     <row r="22" spans="2:25" ht="14.25" customHeight="1">
-      <c r="K22" s="64"/>
-      <c r="L22" s="129">
+      <c r="K22" s="56"/>
+      <c r="L22" s="107">
         <v>25500</v>
       </c>
-      <c r="M22" s="130">
+      <c r="M22" s="108">
         <v>27</v>
       </c>
-      <c r="N22" s="130">
+      <c r="N22" s="108">
         <v>20021</v>
       </c>
-      <c r="O22" s="130"/>
-      <c r="P22" s="131"/>
+      <c r="O22" s="108"/>
+      <c r="P22" s="109"/>
     </row>
     <row r="23" spans="2:25" ht="14.25" customHeight="1" thickBot="1">
-      <c r="K23" s="64"/>
-      <c r="L23" s="129">
+      <c r="K23" s="56"/>
+      <c r="L23" s="107">
         <v>18000</v>
       </c>
-      <c r="M23" s="130">
+      <c r="M23" s="108">
         <v>26</v>
       </c>
-      <c r="N23" s="130">
+      <c r="N23" s="108">
         <v>20022</v>
       </c>
-      <c r="O23" s="130"/>
-      <c r="P23" s="131"/>
+      <c r="O23" s="108"/>
+      <c r="P23" s="109"/>
     </row>
     <row r="24" spans="2:25" ht="21" customHeight="1" thickBot="1">
-      <c r="B24" s="87" t="s">
+      <c r="B24" s="126" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="88"/>
-      <c r="D24" s="88"/>
-      <c r="E24" s="88"/>
-      <c r="F24" s="88"/>
-      <c r="G24" s="88"/>
-      <c r="H24" s="88"/>
-      <c r="I24" s="145"/>
-      <c r="K24" s="65"/>
-      <c r="L24" s="132">
+      <c r="C24" s="127"/>
+      <c r="D24" s="127"/>
+      <c r="E24" s="127"/>
+      <c r="F24" s="127"/>
+      <c r="G24" s="127"/>
+      <c r="H24" s="127"/>
+      <c r="I24" s="128"/>
+      <c r="K24" s="57"/>
+      <c r="L24" s="110">
         <v>21000</v>
       </c>
-      <c r="M24" s="133">
+      <c r="M24" s="111">
         <v>27</v>
       </c>
-      <c r="N24" s="133">
+      <c r="N24" s="111">
         <v>20023</v>
       </c>
-      <c r="O24" s="133"/>
-      <c r="P24" s="134"/>
+      <c r="O24" s="111"/>
+      <c r="P24" s="112"/>
     </row>
     <row r="25" spans="2:25" ht="14.25" customHeight="1">
-      <c r="B25" s="64" t="str">
+      <c r="B25" s="56" t="str">
         <f t="array" ref="B25:I34">_xlfn._xlws.FILTER(A3:H15,C3:C15&gt;25)</f>
         <v>Emp. ID</v>
       </c>
-      <c r="C25" s="30" t="str">
+      <c r="C25" t="str">
         <v>Name</v>
       </c>
-      <c r="D25" s="30" t="str">
+      <c r="D25" t="str">
         <v>Age</v>
       </c>
-      <c r="E25" s="30" t="str">
+      <c r="E25" t="str">
         <v>Designation</v>
       </c>
-      <c r="F25" s="30" t="str">
+      <c r="F25" t="str">
         <v>Department</v>
       </c>
-      <c r="G25" s="30" t="str">
+      <c r="G25" t="str">
         <v>Salary</v>
       </c>
-      <c r="H25" s="30" t="str">
+      <c r="H25" t="str">
         <v>Place</v>
       </c>
-      <c r="I25" s="63" t="str">
+      <c r="I25" s="55" t="str">
         <v>Mob.No.</v>
       </c>
     </row>
     <row r="26" spans="2:25" ht="14.25" customHeight="1">
-      <c r="B26" s="64">
+      <c r="B26" s="56">
         <v>20012</v>
       </c>
-      <c r="C26" s="30" t="str">
+      <c r="C26" t="str">
         <v>Kapil Sharma</v>
       </c>
-      <c r="D26" s="30">
+      <c r="D26">
         <v>26</v>
       </c>
-      <c r="E26" s="30" t="str">
+      <c r="E26" t="str">
         <v>Engineer</v>
       </c>
-      <c r="F26" s="30" t="str">
+      <c r="F26" t="str">
         <v>Technical</v>
       </c>
-      <c r="G26" s="30">
+      <c r="G26">
         <v>26500</v>
       </c>
-      <c r="H26" s="30" t="str">
+      <c r="H26" t="str">
         <v>Indore</v>
       </c>
-      <c r="I26" s="144">
+      <c r="I26" s="119">
         <v>8877456987</v>
       </c>
     </row>
     <row r="27" spans="2:25" ht="14.25" customHeight="1">
-      <c r="B27" s="64">
+      <c r="B27" s="56">
         <v>20014</v>
       </c>
-      <c r="C27" s="30" t="str">
+      <c r="C27" t="str">
         <v>Kapil Singh</v>
       </c>
-      <c r="D27" s="30">
+      <c r="D27">
         <v>28</v>
       </c>
-      <c r="E27" s="30" t="str">
+      <c r="E27" t="str">
         <v>CAD Designer</v>
       </c>
-      <c r="F27" s="30" t="str">
+      <c r="F27" t="str">
         <v>Technical</v>
       </c>
-      <c r="G27" s="30">
+      <c r="G27">
         <v>20000</v>
       </c>
-      <c r="H27" s="30" t="str">
+      <c r="H27" t="str">
         <v>Indore</v>
       </c>
-      <c r="I27" s="144">
+      <c r="I27" s="119">
         <v>7584963214</v>
       </c>
     </row>
     <row r="28" spans="2:25" ht="14.25" customHeight="1">
-      <c r="B28" s="64">
+      <c r="B28" s="56">
         <v>20015</v>
       </c>
-      <c r="C28" s="30" t="str">
+      <c r="C28" t="str">
         <v>Ali Asgar</v>
       </c>
-      <c r="D28" s="30">
+      <c r="D28">
         <v>27</v>
       </c>
-      <c r="E28" s="30" t="str">
+      <c r="E28" t="str">
         <v>Accountant</v>
       </c>
-      <c r="F28" s="30" t="str">
+      <c r="F28" t="str">
         <v>Finance</v>
       </c>
-      <c r="G28" s="30">
+      <c r="G28">
         <v>15000</v>
       </c>
-      <c r="H28" s="30" t="str">
+      <c r="H28" t="str">
         <v>Bhopal</v>
       </c>
-      <c r="I28" s="144">
+      <c r="I28" s="119">
         <v>7788994455</v>
       </c>
     </row>
     <row r="29" spans="2:25" ht="14.25" customHeight="1">
-      <c r="B29" s="64">
+      <c r="B29" s="56">
         <v>20017</v>
       </c>
-      <c r="C29" s="30" t="str">
+      <c r="C29" t="str">
         <v>Mohan Patel</v>
       </c>
-      <c r="D29" s="30">
+      <c r="D29">
         <v>26</v>
       </c>
-      <c r="E29" s="30" t="str">
+      <c r="E29" t="str">
         <v>Engineer</v>
       </c>
-      <c r="F29" s="30" t="str">
+      <c r="F29" t="str">
         <v>Technical</v>
       </c>
-      <c r="G29" s="30">
+      <c r="G29">
         <v>33000</v>
       </c>
-      <c r="H29" s="30" t="str">
+      <c r="H29" t="str">
         <v>Bhopal</v>
       </c>
-      <c r="I29" s="144">
+      <c r="I29" s="119">
         <v>9874563214</v>
       </c>
     </row>
     <row r="30" spans="2:25" ht="14.25" customHeight="1">
-      <c r="B30" s="64">
+      <c r="B30" s="56">
         <v>20019</v>
       </c>
-      <c r="C30" s="30" t="str">
+      <c r="C30" t="str">
         <v>Deepak Singh</v>
       </c>
-      <c r="D30" s="30">
+      <c r="D30">
         <v>26</v>
       </c>
-      <c r="E30" s="30" t="str">
+      <c r="E30" t="str">
         <v>Accountant</v>
       </c>
-      <c r="F30" s="30" t="str">
+      <c r="F30" t="str">
         <v>Finance</v>
       </c>
-      <c r="G30" s="30">
+      <c r="G30">
         <v>31500</v>
       </c>
-      <c r="H30" s="30" t="str">
+      <c r="H30" t="str">
         <v>Bhopal</v>
       </c>
-      <c r="I30" s="144">
+      <c r="I30" s="119">
         <v>8745968745</v>
       </c>
     </row>
     <row r="31" spans="2:25" ht="14.25" customHeight="1">
-      <c r="B31" s="64">
+      <c r="B31" s="56">
         <v>20020</v>
       </c>
-      <c r="C31" s="30" t="str">
+      <c r="C31" t="str">
         <v>Vikas Patel</v>
       </c>
-      <c r="D31" s="30">
+      <c r="D31">
         <v>28</v>
       </c>
-      <c r="E31" s="30" t="str">
+      <c r="E31" t="str">
         <v>Accountant</v>
       </c>
-      <c r="F31" s="30" t="str">
+      <c r="F31" t="str">
         <v>Finance</v>
       </c>
-      <c r="G31" s="30">
+      <c r="G31">
         <v>40500</v>
       </c>
-      <c r="H31" s="30" t="str">
+      <c r="H31" t="str">
         <v>Indore</v>
       </c>
-      <c r="I31" s="144">
+      <c r="I31" s="119">
         <v>9874569874</v>
       </c>
     </row>
     <row r="32" spans="2:25" ht="14.25" customHeight="1">
-      <c r="B32" s="64">
+      <c r="B32" s="56">
         <v>20021</v>
       </c>
-      <c r="C32" s="30" t="str">
+      <c r="C32" t="str">
         <v>Gopal Jat</v>
       </c>
-      <c r="D32" s="30">
+      <c r="D32">
         <v>27</v>
       </c>
-      <c r="E32" s="30" t="str">
+      <c r="E32" t="str">
         <v>Engineer</v>
       </c>
-      <c r="F32" s="30" t="str">
+      <c r="F32" t="str">
         <v>Technical</v>
       </c>
-      <c r="G32" s="30">
+      <c r="G32">
         <v>25500</v>
       </c>
-      <c r="H32" s="30" t="str">
+      <c r="H32" t="str">
         <v>ujjain</v>
       </c>
-      <c r="I32" s="144">
+      <c r="I32" s="119">
         <v>8574965874</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B33" s="64">
+      <c r="B33" s="56">
         <v>20022</v>
       </c>
-      <c r="C33" s="30" t="str">
+      <c r="C33" t="str">
         <v>Rohan Yadav</v>
       </c>
-      <c r="D33" s="30">
+      <c r="D33">
         <v>26</v>
       </c>
-      <c r="E33" s="30" t="str">
+      <c r="E33" t="str">
         <v>Accountant</v>
       </c>
-      <c r="F33" s="30" t="str">
+      <c r="F33" t="str">
         <v>Finance</v>
       </c>
-      <c r="G33" s="30">
+      <c r="G33">
         <v>18000</v>
       </c>
-      <c r="H33" s="30" t="str">
+      <c r="H33" t="str">
         <v>ujjain</v>
       </c>
-      <c r="I33" s="144">
+      <c r="I33" s="119">
         <v>8521479632</v>
       </c>
     </row>
     <row r="34" spans="2:9" ht="14.25" customHeight="1" thickBot="1">
-      <c r="B34" s="65">
+      <c r="B34" s="57">
         <v>20023</v>
       </c>
-      <c r="C34" s="66" t="str">
+      <c r="C34" s="58" t="str">
         <v>Janwi Rai</v>
       </c>
-      <c r="D34" s="66">
+      <c r="D34" s="58">
         <v>27</v>
       </c>
-      <c r="E34" s="66" t="str">
+      <c r="E34" s="58" t="str">
         <v>CAD Designer</v>
       </c>
-      <c r="F34" s="66" t="str">
+      <c r="F34" s="58" t="str">
         <v>Technical</v>
       </c>
-      <c r="G34" s="66">
+      <c r="G34" s="58">
         <v>21000</v>
       </c>
-      <c r="H34" s="66" t="str">
+      <c r="H34" s="58" t="str">
         <v>Indore</v>
       </c>
-      <c r="I34" s="67">
+      <c r="I34" s="59">
         <v>8569745623</v>
       </c>
     </row>
     <row r="35" spans="2:9" ht="21" customHeight="1">
-      <c r="B35" s="87" t="s">
+      <c r="B35" s="126" t="s">
         <v>32</v>
       </c>
-      <c r="C35" s="88"/>
-      <c r="D35" s="88"/>
-      <c r="E35" s="88"/>
-      <c r="F35" s="88"/>
-      <c r="G35" s="88"/>
-      <c r="H35" s="88"/>
-      <c r="I35" s="145"/>
+      <c r="C35" s="127"/>
+      <c r="D35" s="127"/>
+      <c r="E35" s="127"/>
+      <c r="F35" s="127"/>
+      <c r="G35" s="127"/>
+      <c r="H35" s="127"/>
+      <c r="I35" s="128"/>
     </row>
     <row r="36" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B36" s="64">
+      <c r="B36" s="56">
         <f t="array" ref="B36:I42">_xlfn._xlws.FILTER(A3:H15,E3:E15="Technical")</f>
         <v>20012</v>
       </c>
-      <c r="C36" s="30" t="str">
+      <c r="C36" t="str">
         <v>Kapil Sharma</v>
       </c>
-      <c r="D36" s="30">
+      <c r="D36">
         <v>26</v>
       </c>
-      <c r="E36" s="30" t="str">
+      <c r="E36" t="str">
         <v>Engineer</v>
       </c>
-      <c r="F36" s="30" t="str">
+      <c r="F36" t="str">
         <v>Technical</v>
       </c>
-      <c r="G36" s="30">
+      <c r="G36">
         <v>26500</v>
       </c>
-      <c r="H36" s="30" t="str">
+      <c r="H36" t="str">
         <v>Indore</v>
       </c>
-      <c r="I36" s="144">
+      <c r="I36" s="119">
         <v>8877456987</v>
       </c>
     </row>
     <row r="37" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B37" s="64">
+      <c r="B37" s="56">
         <v>20014</v>
       </c>
-      <c r="C37" s="30" t="str">
+      <c r="C37" t="str">
         <v>Kapil Singh</v>
       </c>
-      <c r="D37" s="30">
+      <c r="D37">
         <v>28</v>
       </c>
-      <c r="E37" s="30" t="str">
+      <c r="E37" t="str">
         <v>CAD Designer</v>
       </c>
-      <c r="F37" s="30" t="str">
+      <c r="F37" t="str">
         <v>Technical</v>
       </c>
-      <c r="G37" s="30">
+      <c r="G37">
         <v>20000</v>
       </c>
-      <c r="H37" s="30" t="str">
+      <c r="H37" t="str">
         <v>Indore</v>
       </c>
-      <c r="I37" s="144">
+      <c r="I37" s="119">
         <v>7584963214</v>
       </c>
     </row>
     <row r="38" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B38" s="64">
+      <c r="B38" s="56">
         <v>20016</v>
       </c>
-      <c r="C38" s="30" t="str">
+      <c r="C38" t="str">
         <v>Sunil Singh</v>
       </c>
-      <c r="D38" s="30">
+      <c r="D38">
         <v>25</v>
       </c>
-      <c r="E38" s="30" t="str">
+      <c r="E38" t="str">
         <v>Engineer</v>
       </c>
-      <c r="F38" s="30" t="str">
+      <c r="F38" t="str">
         <v>Technical</v>
       </c>
-      <c r="G38" s="30">
+      <c r="G38">
         <v>20000</v>
       </c>
-      <c r="H38" s="30" t="str">
+      <c r="H38" t="str">
         <v>ujjain</v>
       </c>
-      <c r="I38" s="144">
+      <c r="I38" s="119">
         <v>8798654512</v>
       </c>
     </row>
     <row r="39" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B39" s="64">
+      <c r="B39" s="56">
         <v>20017</v>
       </c>
-      <c r="C39" s="30" t="str">
+      <c r="C39" t="str">
         <v>Mohan Patel</v>
       </c>
-      <c r="D39" s="30">
+      <c r="D39">
         <v>26</v>
       </c>
-      <c r="E39" s="30" t="str">
+      <c r="E39" t="str">
         <v>Engineer</v>
       </c>
-      <c r="F39" s="30" t="str">
+      <c r="F39" t="str">
         <v>Technical</v>
       </c>
-      <c r="G39" s="30">
+      <c r="G39">
         <v>33000</v>
       </c>
-      <c r="H39" s="30" t="str">
+      <c r="H39" t="str">
         <v>Bhopal</v>
       </c>
-      <c r="I39" s="144">
+      <c r="I39" s="119">
         <v>9874563214</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B40" s="64">
+      <c r="B40" s="56">
         <v>20018</v>
       </c>
-      <c r="C40" s="30" t="str">
+      <c r="C40" t="str">
         <v>Ravi Verma</v>
       </c>
-      <c r="D40" s="30">
+      <c r="D40">
         <v>25</v>
       </c>
-      <c r="E40" s="30" t="str">
+      <c r="E40" t="str">
         <v>CAD Designer</v>
       </c>
-      <c r="F40" s="30" t="str">
+      <c r="F40" t="str">
         <v>Technical</v>
       </c>
-      <c r="G40" s="30">
+      <c r="G40">
         <v>21000</v>
       </c>
-      <c r="H40" s="30" t="str">
+      <c r="H40" t="str">
         <v>Indore</v>
       </c>
-      <c r="I40" s="144">
+      <c r="I40" s="119">
         <v>8974563214</v>
       </c>
     </row>
     <row r="41" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B41" s="64">
+      <c r="B41" s="56">
         <v>20021</v>
       </c>
-      <c r="C41" s="30" t="str">
+      <c r="C41" t="str">
         <v>Gopal Jat</v>
       </c>
-      <c r="D41" s="30">
+      <c r="D41">
         <v>27</v>
       </c>
-      <c r="E41" s="30" t="str">
+      <c r="E41" t="str">
         <v>Engineer</v>
       </c>
-      <c r="F41" s="30" t="str">
+      <c r="F41" t="str">
         <v>Technical</v>
       </c>
-      <c r="G41" s="30">
+      <c r="G41">
         <v>25500</v>
       </c>
-      <c r="H41" s="30" t="str">
+      <c r="H41" t="str">
         <v>ujjain</v>
       </c>
-      <c r="I41" s="144">
+      <c r="I41" s="119">
         <v>8574965874</v>
       </c>
     </row>
     <row r="42" spans="2:9" ht="14.25" customHeight="1" thickBot="1">
-      <c r="B42" s="65">
+      <c r="B42" s="57">
         <v>20023</v>
       </c>
-      <c r="C42" s="66" t="str">
+      <c r="C42" s="58" t="str">
         <v>Janwi Rai</v>
       </c>
-      <c r="D42" s="66">
+      <c r="D42" s="58">
         <v>27</v>
       </c>
-      <c r="E42" s="66" t="str">
+      <c r="E42" s="58" t="str">
         <v>CAD Designer</v>
       </c>
-      <c r="F42" s="66" t="str">
+      <c r="F42" s="58" t="str">
         <v>Technical</v>
       </c>
-      <c r="G42" s="66">
+      <c r="G42" s="58">
         <v>21000</v>
       </c>
-      <c r="H42" s="66" t="str">
+      <c r="H42" s="58" t="str">
         <v>Indore</v>
       </c>
-      <c r="I42" s="67">
+      <c r="I42" s="59">
         <v>8569745623</v>
       </c>
     </row>
     <row r="43" spans="2:9" ht="21" customHeight="1">
-      <c r="B43" s="87" t="s">
+      <c r="B43" s="126" t="s">
         <v>33</v>
       </c>
-      <c r="C43" s="88"/>
-      <c r="D43" s="88"/>
-      <c r="E43" s="88"/>
-      <c r="F43" s="88"/>
-      <c r="G43" s="88"/>
-      <c r="H43" s="88"/>
-      <c r="I43" s="145"/>
+      <c r="C43" s="127"/>
+      <c r="D43" s="127"/>
+      <c r="E43" s="127"/>
+      <c r="F43" s="127"/>
+      <c r="G43" s="127"/>
+      <c r="H43" s="127"/>
+      <c r="I43" s="128"/>
     </row>
     <row r="44" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B44" s="64">
+      <c r="B44" s="56">
         <f t="array" ref="B44:I47">_xlfn._xlws.FILTER(A3:H15,G3:G15="Bhopal")</f>
         <v>20013</v>
       </c>
-      <c r="C44" s="30" t="str">
+      <c r="C44" t="str">
         <v>Sunil Grover</v>
       </c>
-      <c r="D44" s="30">
+      <c r="D44">
         <v>25</v>
       </c>
-      <c r="E44" s="30" t="str">
+      <c r="E44" t="str">
         <v>Accountant</v>
       </c>
-      <c r="F44" s="30" t="str">
+      <c r="F44" t="str">
         <v>Finance</v>
       </c>
-      <c r="G44" s="30">
+      <c r="G44">
         <v>13000</v>
       </c>
-      <c r="H44" s="30" t="str">
+      <c r="H44" t="str">
         <v>Bhopal</v>
       </c>
-      <c r="I44" s="144">
+      <c r="I44" s="119">
         <v>8569741235</v>
       </c>
     </row>
     <row r="45" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B45" s="64">
+      <c r="B45" s="56">
         <v>20015</v>
       </c>
-      <c r="C45" s="30" t="str">
+      <c r="C45" t="str">
         <v>Ali Asgar</v>
       </c>
-      <c r="D45" s="30">
+      <c r="D45">
         <v>27</v>
       </c>
-      <c r="E45" s="30" t="str">
+      <c r="E45" t="str">
         <v>Accountant</v>
       </c>
-      <c r="F45" s="30" t="str">
+      <c r="F45" t="str">
         <v>Finance</v>
       </c>
-      <c r="G45" s="30">
+      <c r="G45">
         <v>15000</v>
       </c>
-      <c r="H45" s="30" t="str">
+      <c r="H45" t="str">
         <v>Bhopal</v>
       </c>
-      <c r="I45" s="144">
+      <c r="I45" s="119">
         <v>7788994455</v>
       </c>
     </row>
     <row r="46" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B46" s="64">
+      <c r="B46" s="56">
         <v>20017</v>
       </c>
-      <c r="C46" s="30" t="str">
+      <c r="C46" t="str">
         <v>Mohan Patel</v>
       </c>
-      <c r="D46" s="30">
+      <c r="D46">
         <v>26</v>
       </c>
-      <c r="E46" s="30" t="str">
+      <c r="E46" t="str">
         <v>Engineer</v>
       </c>
-      <c r="F46" s="30" t="str">
+      <c r="F46" t="str">
         <v>Technical</v>
       </c>
-      <c r="G46" s="30">
+      <c r="G46">
         <v>33000</v>
       </c>
-      <c r="H46" s="30" t="str">
+      <c r="H46" t="str">
         <v>Bhopal</v>
       </c>
-      <c r="I46" s="144">
+      <c r="I46" s="119">
         <v>9874563214</v>
       </c>
     </row>
     <row r="47" spans="2:9" ht="14.25" customHeight="1" thickBot="1">
-      <c r="B47" s="65">
+      <c r="B47" s="57">
         <v>20019</v>
       </c>
-      <c r="C47" s="66" t="str">
+      <c r="C47" s="58" t="str">
         <v>Deepak Singh</v>
       </c>
-      <c r="D47" s="66">
+      <c r="D47" s="58">
         <v>26</v>
       </c>
-      <c r="E47" s="66" t="str">
+      <c r="E47" s="58" t="str">
         <v>Accountant</v>
       </c>
-      <c r="F47" s="66" t="str">
+      <c r="F47" s="58" t="str">
         <v>Finance</v>
       </c>
-      <c r="G47" s="66">
+      <c r="G47" s="58">
         <v>31500</v>
       </c>
-      <c r="H47" s="66" t="str">
+      <c r="H47" s="58" t="str">
         <v>Bhopal</v>
       </c>
-      <c r="I47" s="67">
+      <c r="I47" s="59">
         <v>8745968745</v>
       </c>
     </row>
     <row r="48" spans="2:9" ht="21" customHeight="1">
-      <c r="B48" s="87" t="s">
+      <c r="B48" s="126" t="s">
         <v>34</v>
       </c>
-      <c r="C48" s="88"/>
-      <c r="D48" s="88"/>
-      <c r="E48" s="88"/>
-      <c r="F48" s="88"/>
-      <c r="G48" s="88"/>
-      <c r="H48" s="88"/>
-      <c r="I48" s="145"/>
+      <c r="C48" s="127"/>
+      <c r="D48" s="127"/>
+      <c r="E48" s="127"/>
+      <c r="F48" s="127"/>
+      <c r="G48" s="127"/>
+      <c r="H48" s="127"/>
+      <c r="I48" s="128"/>
     </row>
     <row r="49" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B49" s="64" t="str">
+      <c r="B49" s="56" t="str">
         <f t="array" ref="B49:I52">_xlfn._xlws.FILTER(A3:H15,F3:F15&gt;30000)</f>
         <v>Emp. ID</v>
       </c>
-      <c r="C49" s="30" t="str">
+      <c r="C49" t="str">
         <v>Name</v>
       </c>
-      <c r="D49" s="30" t="str">
+      <c r="D49" t="str">
         <v>Age</v>
       </c>
-      <c r="E49" s="30" t="str">
+      <c r="E49" t="str">
         <v>Designation</v>
       </c>
-      <c r="F49" s="30" t="str">
+      <c r="F49" t="str">
         <v>Department</v>
       </c>
-      <c r="G49" s="30" t="str">
+      <c r="G49" t="str">
         <v>Salary</v>
       </c>
-      <c r="H49" s="30" t="str">
+      <c r="H49" t="str">
         <v>Place</v>
       </c>
-      <c r="I49" s="63" t="str">
+      <c r="I49" s="55" t="str">
         <v>Mob.No.</v>
       </c>
     </row>
     <row r="50" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B50" s="64">
+      <c r="B50" s="56">
         <v>20017</v>
       </c>
-      <c r="C50" s="30" t="str">
+      <c r="C50" t="str">
         <v>Mohan Patel</v>
       </c>
-      <c r="D50" s="30">
+      <c r="D50">
         <v>26</v>
       </c>
-      <c r="E50" s="30" t="str">
+      <c r="E50" t="str">
         <v>Engineer</v>
       </c>
-      <c r="F50" s="30" t="str">
+      <c r="F50" t="str">
         <v>Technical</v>
       </c>
-      <c r="G50" s="30">
+      <c r="G50">
         <v>33000</v>
       </c>
-      <c r="H50" s="30" t="str">
+      <c r="H50" t="str">
         <v>Bhopal</v>
       </c>
-      <c r="I50" s="144">
+      <c r="I50" s="119">
         <v>9874563214</v>
       </c>
     </row>
     <row r="51" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B51" s="64">
+      <c r="B51" s="56">
         <v>20019</v>
       </c>
-      <c r="C51" s="30" t="str">
+      <c r="C51" t="str">
         <v>Deepak Singh</v>
       </c>
-      <c r="D51" s="30">
+      <c r="D51">
         <v>26</v>
       </c>
-      <c r="E51" s="30" t="str">
+      <c r="E51" t="str">
         <v>Accountant</v>
       </c>
-      <c r="F51" s="30" t="str">
+      <c r="F51" t="str">
         <v>Finance</v>
       </c>
-      <c r="G51" s="30">
+      <c r="G51">
         <v>31500</v>
       </c>
-      <c r="H51" s="30" t="str">
+      <c r="H51" t="str">
         <v>Bhopal</v>
       </c>
-      <c r="I51" s="144">
+      <c r="I51" s="119">
         <v>8745968745</v>
       </c>
     </row>
     <row r="52" spans="2:9" ht="14.25" customHeight="1" thickBot="1">
-      <c r="B52" s="65">
+      <c r="B52" s="57">
         <v>20020</v>
       </c>
-      <c r="C52" s="66" t="str">
+      <c r="C52" s="58" t="str">
         <v>Vikas Patel</v>
       </c>
-      <c r="D52" s="66">
+      <c r="D52" s="58">
         <v>28</v>
       </c>
-      <c r="E52" s="66" t="str">
+      <c r="E52" s="58" t="str">
         <v>Accountant</v>
       </c>
-      <c r="F52" s="66" t="str">
+      <c r="F52" s="58" t="str">
         <v>Finance</v>
       </c>
-      <c r="G52" s="66">
+      <c r="G52" s="58">
         <v>40500</v>
       </c>
-      <c r="H52" s="66" t="str">
+      <c r="H52" s="58" t="str">
         <v>Indore</v>
       </c>
-      <c r="I52" s="67">
+      <c r="I52" s="59">
         <v>9874569874</v>
       </c>
     </row>
@@ -3471,95 +3476,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="41.25" customHeight="1">
-      <c r="B1" s="75" t="s">
+      <c r="B1" s="64" t="s">
         <v>103</v>
       </c>
-      <c r="C1" s="62">
+      <c r="C1" s="54">
         <f>VLOOKUP(B2,employee!A3:H15,6,0)</f>
         <v>20000</v>
       </c>
-      <c r="D1" s="16"/>
+      <c r="D1" s="12"/>
     </row>
     <row r="2" spans="2:10" ht="14.25" customHeight="1" thickBot="1">
-      <c r="B2" s="76">
+      <c r="B2" s="65">
         <v>20016</v>
       </c>
-      <c r="C2" s="127"/>
+      <c r="C2" s="105"/>
     </row>
     <row r="3" spans="2:10" ht="27.75" customHeight="1">
-      <c r="B3" s="75" t="s">
+      <c r="B3" s="64" t="s">
         <v>104</v>
       </c>
-      <c r="C3" s="93" t="str">
+      <c r="C3" s="79" t="str">
         <f t="array" ref="C3:I3">VLOOKUP(B4,Vlookup!A3:H15,{2,3,4,5,6,7,8},0)</f>
         <v>Sunil Grover</v>
       </c>
-      <c r="D3" s="93">
+      <c r="D3" s="79">
         <v>25</v>
       </c>
-      <c r="E3" s="93" t="str">
+      <c r="E3" s="79" t="str">
         <v>Accountant</v>
       </c>
-      <c r="F3" s="93" t="str">
+      <c r="F3" s="79" t="str">
         <v>Finance</v>
       </c>
-      <c r="G3" s="93">
+      <c r="G3" s="79">
         <v>13000</v>
       </c>
-      <c r="H3" s="93" t="str">
+      <c r="H3" s="79" t="str">
         <v>Bhopal</v>
       </c>
-      <c r="I3" s="128">
+      <c r="I3" s="106">
         <v>8569741235</v>
       </c>
-      <c r="J3" s="16"/>
+      <c r="J3" s="12"/>
     </row>
     <row r="4" spans="2:10" ht="14.25" customHeight="1">
-      <c r="B4" s="76">
+      <c r="B4" s="65">
         <v>20013</v>
       </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="30"/>
-      <c r="E4" s="30"/>
-      <c r="F4" s="30"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="30"/>
-      <c r="I4" s="63"/>
+      <c r="I4" s="55"/>
     </row>
     <row r="5" spans="2:10" ht="14.25" customHeight="1" thickBot="1">
-      <c r="B5" s="65"/>
-      <c r="C5" s="66"/>
-      <c r="D5" s="66"/>
-      <c r="E5" s="66"/>
-      <c r="F5" s="66"/>
-      <c r="G5" s="66"/>
-      <c r="H5" s="66"/>
-      <c r="I5" s="68"/>
+      <c r="B5" s="57"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="60"/>
     </row>
     <row r="6" spans="2:10" ht="14.25" customHeight="1">
-      <c r="B6" s="137" t="s">
+      <c r="B6" s="115" t="s">
         <v>105</v>
       </c>
-      <c r="C6" s="63">
+      <c r="C6" s="55">
         <f>VLOOKUP(B7,Vlookup!B3:H15,MATCH(' hlookup(employee_table)'!B8,Vlookup!B3:H3,0),0)</f>
         <v>25500</v>
       </c>
     </row>
     <row r="7" spans="2:10">
-      <c r="B7" s="76" t="s">
+      <c r="B7" s="65" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="63"/>
+      <c r="C7" s="55"/>
     </row>
     <row r="8" spans="2:10">
-      <c r="B8" s="138" t="s">
+      <c r="B8" s="116" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="63"/>
+      <c r="C8" s="55"/>
     </row>
     <row r="9" spans="2:10" ht="15" thickBot="1">
-      <c r="B9" s="65"/>
-      <c r="C9" s="68"/>
+      <c r="B9" s="57"/>
+      <c r="C9" s="60"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3578,403 +3577,403 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="14.25" customHeight="1">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="129" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="J1" s="5" t="s">
+      <c r="B1" s="129"/>
+      <c r="C1" s="129"/>
+      <c r="D1" s="129"/>
+      <c r="E1" s="129"/>
+      <c r="F1" s="129"/>
+      <c r="G1" s="129"/>
+      <c r="H1" s="129"/>
+      <c r="J1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="1" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="2" spans="1:11" ht="14.25" customHeight="1">
-      <c r="A2" s="2"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="J2" s="13" t="s">
+      <c r="A2" s="129"/>
+      <c r="B2" s="129"/>
+      <c r="C2" s="129"/>
+      <c r="D2" s="129"/>
+      <c r="E2" s="129"/>
+      <c r="F2" s="129"/>
+      <c r="G2" s="129"/>
+      <c r="H2" s="129"/>
+      <c r="J2" s="9" t="s">
         <v>60</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2" s="4">
         <f>SUBTOTAL(9,H4:H15)</f>
         <v>43850</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="24" customHeight="1">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="12" t="s">
+      <c r="C3" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="7" t="s">
         <v>57</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="J3" s="13" t="s">
+      <c r="J3" s="9" t="s">
         <v>61</v>
       </c>
-      <c r="K3" s="14">
+      <c r="K3" s="10">
         <f>SUBTOTAL(1,H4:H15)</f>
         <v>3654.1666666666665</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="21" customHeight="1">
-      <c r="A4" s="6">
+      <c r="A4" s="3">
         <v>20012</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="4">
         <v>4520</v>
       </c>
-      <c r="D4" s="6">
+      <c r="D4" s="3">
         <v>2600</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="3">
         <v>3640</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="3">
         <v>2430</v>
       </c>
-      <c r="G4" s="6">
+      <c r="G4" s="3">
         <v>3530</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="3">
         <v>4130</v>
       </c>
-      <c r="J4" s="13" t="s">
+      <c r="J4" s="9" t="s">
         <v>62</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="4">
         <f>SUBTOTAL(2,H4:H15)</f>
         <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="21" customHeight="1">
-      <c r="A5" s="6">
+      <c r="A5" s="3">
         <v>20013</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="4">
         <v>2310</v>
       </c>
-      <c r="D5" s="6">
+      <c r="D5" s="3">
         <v>3570</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="3">
         <v>4870</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="3">
         <v>3000</v>
       </c>
-      <c r="G5" s="6">
+      <c r="G5" s="3">
         <v>4590</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="3">
         <v>3370</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="J5" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="K5" s="14">
+      <c r="K5" s="10">
         <f>SUBTOTAL(101,H4:H15)</f>
         <v>3654.1666666666665</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="21" customHeight="1">
-      <c r="A6" s="6">
+      <c r="A6" s="3">
         <v>20014</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="4">
         <v>3610</v>
       </c>
-      <c r="D6" s="6">
+      <c r="D6" s="3">
         <v>3930</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="3">
         <v>4090</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="3">
         <v>4050</v>
       </c>
-      <c r="G6" s="6">
+      <c r="G6" s="3">
         <v>2850</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="3">
         <v>4530</v>
       </c>
-      <c r="J6" s="13" t="s">
+      <c r="J6" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="K6" s="7">
+      <c r="K6" s="4">
         <f>SUBTOTAL(9,H7,G7)</f>
         <v>4810</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="21" customHeight="1">
-      <c r="A7" s="6">
+      <c r="A7" s="3">
         <v>20015</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="4">
         <v>4920</v>
       </c>
-      <c r="D7" s="6">
+      <c r="D7" s="3">
         <v>4530</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="3">
         <v>4400</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="3">
         <v>4060</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="3">
         <v>2240</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="3">
         <v>2570</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="21" customHeight="1">
-      <c r="A8" s="6">
+      <c r="A8" s="3">
         <v>20016</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="4">
         <v>2920</v>
       </c>
-      <c r="D8" s="6">
+      <c r="D8" s="3">
         <v>2080</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="3">
         <v>3040</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="3">
         <v>2960</v>
       </c>
-      <c r="G8" s="6">
+      <c r="G8" s="3">
         <v>3010</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="3">
         <v>3400</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="21" customHeight="1">
-      <c r="A9" s="6">
+      <c r="A9" s="3">
         <v>20017</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="4">
         <v>4580</v>
       </c>
-      <c r="D9" s="6">
+      <c r="D9" s="3">
         <v>3910</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="3">
         <v>3960</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="3">
         <v>2970</v>
       </c>
-      <c r="G9" s="6">
+      <c r="G9" s="3">
         <v>2080</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="3">
         <v>2390</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="21" customHeight="1">
-      <c r="A10" s="6">
+      <c r="A10" s="3">
         <v>20018</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="4">
         <v>3710</v>
       </c>
-      <c r="D10" s="6">
+      <c r="D10" s="3">
         <v>4470</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="3">
         <v>4310</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="3">
         <v>2760</v>
       </c>
-      <c r="G10" s="6">
+      <c r="G10" s="3">
         <v>2050</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="3">
         <v>3800</v>
       </c>
     </row>
     <row r="11" spans="1:11" ht="21" customHeight="1">
-      <c r="A11" s="6">
+      <c r="A11" s="3">
         <v>20019</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="4">
         <v>2870</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="3">
         <v>2840</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="3">
         <v>4890</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="3">
         <v>2510</v>
       </c>
-      <c r="G11" s="6">
+      <c r="G11" s="3">
         <v>3290</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="3">
         <v>2040</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="21" customHeight="1">
-      <c r="A12" s="6">
+      <c r="A12" s="3">
         <v>20020</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="4">
         <v>2160</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="3">
         <v>4350</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="3">
         <v>2950</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="3">
         <v>2730</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G12" s="3">
         <v>3890</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="3">
         <v>4820</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="21" customHeight="1">
-      <c r="A13" s="6">
+      <c r="A13" s="3">
         <v>20021</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="4">
         <v>2630</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="3">
         <v>4000</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="3">
         <v>2200</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="3">
         <v>3850</v>
       </c>
-      <c r="G13" s="6">
+      <c r="G13" s="3">
         <v>2620</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="3">
         <v>4540</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="21" customHeight="1">
-      <c r="A14" s="6">
+      <c r="A14" s="3">
         <v>20022</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="4">
         <v>2000</v>
       </c>
-      <c r="D14" s="6">
+      <c r="D14" s="3">
         <v>3030</v>
       </c>
-      <c r="E14" s="6">
+      <c r="E14" s="3">
         <v>4530</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="3">
         <v>4240</v>
       </c>
-      <c r="G14" s="6">
+      <c r="G14" s="3">
         <v>2250</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="3">
         <v>4190</v>
       </c>
     </row>
     <row r="15" spans="1:11" ht="21" customHeight="1">
-      <c r="A15" s="6">
+      <c r="A15" s="3">
         <v>20023</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="4">
         <v>2360</v>
       </c>
-      <c r="D15" s="6">
+      <c r="D15" s="3">
         <v>3050</v>
       </c>
-      <c r="E15" s="6">
+      <c r="E15" s="3">
         <v>4040</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="3">
         <v>3220</v>
       </c>
-      <c r="G15" s="6">
+      <c r="G15" s="3">
         <v>2910</v>
       </c>
-      <c r="H15" s="6">
+      <c r="H15" s="3">
         <v>4070</v>
       </c>
     </row>
@@ -4003,7 +4002,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B3:AA25"/>
+  <dimension ref="B3:Z25"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="10" customWidth="1"/>
@@ -4028,737 +4027,727 @@
     <col min="26" max="26" width="11.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:27" ht="23.25" customHeight="1">
-      <c r="B3" s="46" t="s">
+    <row r="3" spans="2:26" ht="23.25" customHeight="1">
+      <c r="B3" s="41" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="46" t="s">
+      <c r="C3" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="46" t="s">
+      <c r="D3" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="46" t="s">
+      <c r="E3" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="46" t="s">
+      <c r="F3" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="46" t="s">
+      <c r="G3" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="46" t="s">
+      <c r="H3" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="50"/>
-      <c r="J3" s="26"/>
-      <c r="K3" s="46" t="s">
+      <c r="I3" s="45"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="41" t="s">
         <v>2</v>
       </c>
-      <c r="L3" s="46" t="s">
+      <c r="L3" s="41" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="46" t="s">
+      <c r="M3" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="N3" s="46" t="s">
+      <c r="N3" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="O3" s="46" t="s">
+      <c r="O3" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="P3" s="46" t="s">
+      <c r="P3" s="41" t="s">
         <v>7</v>
       </c>
-      <c r="Q3" s="46" t="s">
+      <c r="Q3" s="41" t="s">
         <v>8</v>
       </c>
-      <c r="T3" s="59" t="s">
+      <c r="T3" s="52" t="s">
         <v>66</v>
       </c>
-      <c r="U3" s="52"/>
-      <c r="V3" s="37">
+      <c r="U3" s="47"/>
+      <c r="V3" s="32">
         <f>VLOOKUP(B7,CHOOSE({1,2},B3:B15,L3:L15),2,0)</f>
         <v>27</v>
       </c>
-      <c r="W3" s="27"/>
-      <c r="X3" s="27"/>
-      <c r="Y3" s="27"/>
-      <c r="Z3" s="28"/>
-    </row>
-    <row r="4" spans="2:27" ht="21" customHeight="1">
-      <c r="B4" s="48">
+      <c r="W3" s="23"/>
+      <c r="X3" s="23"/>
+      <c r="Y3" s="23"/>
+      <c r="Z3" s="24"/>
+    </row>
+    <row r="4" spans="2:26" ht="21" customHeight="1">
+      <c r="B4" s="43">
         <v>20012</v>
       </c>
-      <c r="C4" s="47" t="s">
+      <c r="C4" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="48" t="s">
+      <c r="D4" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="48" t="s">
+      <c r="E4" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="48">
+      <c r="F4" s="43">
         <v>26500</v>
       </c>
-      <c r="G4" s="48" t="s">
+      <c r="G4" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="49">
+      <c r="H4" s="44">
         <v>8877456987</v>
       </c>
-      <c r="I4" s="23"/>
-      <c r="J4" s="25"/>
-      <c r="K4" s="47" t="s">
+      <c r="I4" s="19"/>
+      <c r="J4" s="21"/>
+      <c r="K4" s="42" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="47">
+      <c r="L4" s="42">
         <v>26</v>
       </c>
-      <c r="M4" s="48" t="s">
+      <c r="M4" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="48" t="s">
+      <c r="N4" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="48">
+      <c r="O4" s="43">
         <v>26500</v>
       </c>
-      <c r="P4" s="48" t="s">
+      <c r="P4" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="Q4" s="49">
+      <c r="Q4" s="44">
         <v>8877456987</v>
       </c>
-      <c r="T4" s="32"/>
-      <c r="U4" s="33"/>
-      <c r="V4" s="33"/>
-      <c r="W4" s="33"/>
-      <c r="X4" s="33"/>
-      <c r="Y4" s="33"/>
-      <c r="Z4" s="34"/>
-    </row>
-    <row r="5" spans="2:27" ht="21" customHeight="1">
-      <c r="B5" s="48">
+      <c r="T4" s="27"/>
+      <c r="U4" s="28"/>
+      <c r="V4" s="28"/>
+      <c r="W4" s="28"/>
+      <c r="X4" s="28"/>
+      <c r="Y4" s="28"/>
+      <c r="Z4" s="29"/>
+    </row>
+    <row r="5" spans="2:26" ht="21" customHeight="1">
+      <c r="B5" s="43">
         <v>20013</v>
       </c>
-      <c r="C5" s="47" t="s">
+      <c r="C5" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="48" t="s">
+      <c r="D5" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="48" t="s">
+      <c r="E5" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="48">
+      <c r="F5" s="43">
         <v>13000</v>
       </c>
-      <c r="G5" s="48" t="s">
+      <c r="G5" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="49">
+      <c r="H5" s="44">
         <v>8569741235</v>
       </c>
-      <c r="I5" s="23"/>
-      <c r="J5" s="25"/>
-      <c r="K5" s="47" t="s">
+      <c r="I5" s="19"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="42" t="s">
         <v>13</v>
       </c>
-      <c r="L5" s="47">
+      <c r="L5" s="42">
         <v>25</v>
       </c>
-      <c r="M5" s="48" t="s">
+      <c r="M5" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="N5" s="48" t="s">
+      <c r="N5" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="O5" s="48">
+      <c r="O5" s="43">
         <v>13000</v>
       </c>
-      <c r="P5" s="48" t="s">
+      <c r="P5" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="Q5" s="49">
+      <c r="Q5" s="44">
         <v>8569741235</v>
       </c>
-      <c r="T5" s="42" t="s">
+      <c r="T5" s="37" t="s">
         <v>68</v>
       </c>
-      <c r="U5" s="35"/>
-      <c r="V5" s="38">
+      <c r="U5" s="30"/>
+      <c r="V5" s="33">
         <f>VLOOKUP(VLOOKUP(B4,B3:H15,2,0),K3:Q15,2,0)</f>
         <v>26</v>
       </c>
-      <c r="W5" s="35"/>
-      <c r="X5" s="35"/>
-      <c r="Y5" s="35"/>
-      <c r="Z5" s="36"/>
-    </row>
-    <row r="6" spans="2:27" ht="21" customHeight="1">
-      <c r="B6" s="48">
+      <c r="W5" s="30"/>
+      <c r="X5" s="30"/>
+      <c r="Y5" s="30"/>
+      <c r="Z5" s="31"/>
+    </row>
+    <row r="6" spans="2:26" ht="21" customHeight="1">
+      <c r="B6" s="43">
         <v>20014</v>
       </c>
-      <c r="C6" s="47" t="s">
+      <c r="C6" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="48" t="s">
+      <c r="D6" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="48" t="s">
+      <c r="E6" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="48">
+      <c r="F6" s="43">
         <v>20000</v>
       </c>
-      <c r="G6" s="48" t="s">
+      <c r="G6" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="49">
+      <c r="H6" s="44">
         <v>7584963214</v>
       </c>
-      <c r="I6" s="23"/>
-      <c r="J6" s="25"/>
-      <c r="K6" s="47" t="s">
+      <c r="I6" s="19"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="42" t="s">
         <v>17</v>
       </c>
-      <c r="L6" s="47">
+      <c r="L6" s="42">
         <v>28</v>
       </c>
-      <c r="M6" s="48" t="s">
+      <c r="M6" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="N6" s="48" t="s">
+      <c r="N6" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="O6" s="48">
+      <c r="O6" s="43">
         <v>20000</v>
       </c>
-      <c r="P6" s="48" t="s">
+      <c r="P6" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="Q6" s="49">
+      <c r="Q6" s="44">
         <v>7584963214</v>
       </c>
-      <c r="T6" s="51" t="s">
+      <c r="T6" s="46" t="s">
         <v>69</v>
       </c>
-      <c r="U6" s="52"/>
-      <c r="V6" s="52"/>
-      <c r="W6" s="52"/>
-      <c r="X6" s="52"/>
-      <c r="Y6" s="52"/>
-      <c r="Z6" s="53"/>
-    </row>
-    <row r="7" spans="2:27" ht="21" customHeight="1">
-      <c r="B7" s="48">
+      <c r="U6" s="47"/>
+      <c r="V6" s="47"/>
+      <c r="W6" s="47"/>
+      <c r="X6" s="47"/>
+      <c r="Y6" s="47"/>
+      <c r="Z6" s="48"/>
+    </row>
+    <row r="7" spans="2:26" ht="21" customHeight="1">
+      <c r="B7" s="43">
         <v>20015</v>
       </c>
-      <c r="C7" s="47" t="s">
+      <c r="C7" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="48" t="s">
+      <c r="D7" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="48" t="s">
+      <c r="E7" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="48">
+      <c r="F7" s="43">
         <v>15000</v>
       </c>
-      <c r="G7" s="48" t="s">
+      <c r="G7" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="49">
+      <c r="H7" s="44">
         <v>7788994455</v>
       </c>
-      <c r="I7" s="23"/>
-      <c r="J7" s="25"/>
-      <c r="K7" s="47" t="s">
+      <c r="I7" s="19"/>
+      <c r="J7" s="21"/>
+      <c r="K7" s="42" t="s">
         <v>19</v>
       </c>
-      <c r="L7" s="47">
+      <c r="L7" s="42">
         <v>27</v>
       </c>
-      <c r="M7" s="48" t="s">
+      <c r="M7" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="N7" s="48" t="s">
+      <c r="N7" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="O7" s="48">
+      <c r="O7" s="43">
         <v>15000</v>
       </c>
-      <c r="P7" s="48" t="s">
+      <c r="P7" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="Q7" s="49">
+      <c r="Q7" s="44">
         <v>7788994455</v>
       </c>
-      <c r="T7" s="32"/>
-      <c r="U7" s="39">
+      <c r="T7" s="27"/>
+      <c r="U7" s="34" cm="1">
         <f t="array" ref="U7:Z7">VLOOKUP(VLOOKUP(B4,B3:H15,2,0),K3:Q15,{2,3,4,5,6,7},0)</f>
         <v>26</v>
       </c>
-      <c r="V7" s="39" t="str">
+      <c r="V7" s="34" t="str">
         <v>Engineer</v>
       </c>
-      <c r="W7" s="39" t="str">
+      <c r="W7" s="34" t="str">
         <v>Technical</v>
       </c>
-      <c r="X7" s="39">
+      <c r="X7" s="34">
         <v>26500</v>
       </c>
-      <c r="Y7" s="39" t="str">
+      <c r="Y7" s="34" t="str">
         <v>Indore</v>
       </c>
-      <c r="Z7" s="40">
+      <c r="Z7" s="35">
         <v>8877456987</v>
       </c>
     </row>
-    <row r="8" spans="2:27" ht="21" customHeight="1">
-      <c r="B8" s="48">
+    <row r="8" spans="2:26" ht="21" customHeight="1">
+      <c r="B8" s="43">
         <v>20016</v>
       </c>
-      <c r="C8" s="47" t="s">
+      <c r="C8" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="48" t="s">
+      <c r="D8" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="48" t="s">
+      <c r="E8" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="48">
+      <c r="F8" s="43">
         <v>20000</v>
       </c>
-      <c r="G8" s="48" t="s">
+      <c r="G8" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="49">
+      <c r="H8" s="44">
         <v>8798654512</v>
       </c>
-      <c r="I8" s="23"/>
-      <c r="J8" s="25"/>
-      <c r="K8" s="47" t="s">
+      <c r="I8" s="19"/>
+      <c r="J8" s="21"/>
+      <c r="K8" s="42" t="s">
         <v>20</v>
       </c>
-      <c r="L8" s="47">
+      <c r="L8" s="42">
         <v>25</v>
       </c>
-      <c r="M8" s="48" t="s">
+      <c r="M8" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="N8" s="48" t="s">
+      <c r="N8" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="O8" s="48">
+      <c r="O8" s="43">
         <v>20000</v>
       </c>
-      <c r="P8" s="48" t="s">
+      <c r="P8" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="Q8" s="49">
+      <c r="Q8" s="44">
         <v>8798654512</v>
       </c>
-      <c r="T8" s="29"/>
-      <c r="U8" s="30"/>
-      <c r="V8" s="30"/>
-      <c r="W8" s="30"/>
-      <c r="X8" s="30"/>
-      <c r="Y8" s="30"/>
-      <c r="Z8" s="31"/>
-      <c r="AA8" s="54"/>
-    </row>
-    <row r="9" spans="2:27" ht="21" customHeight="1">
-      <c r="B9" s="48">
+      <c r="T8" s="25"/>
+      <c r="Z8" s="26"/>
+    </row>
+    <row r="9" spans="2:26" ht="21" customHeight="1">
+      <c r="B9" s="43">
         <v>20017</v>
       </c>
-      <c r="C9" s="47" t="s">
+      <c r="C9" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="48" t="s">
+      <c r="D9" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="48" t="s">
+      <c r="E9" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="48">
+      <c r="F9" s="43">
         <v>33000</v>
       </c>
-      <c r="G9" s="48" t="s">
+      <c r="G9" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="49">
+      <c r="H9" s="44">
         <v>9874563214</v>
       </c>
-      <c r="I9" s="23"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="47" t="s">
+      <c r="I9" s="19"/>
+      <c r="J9" s="21"/>
+      <c r="K9" s="42" t="s">
         <v>22</v>
       </c>
-      <c r="L9" s="47">
+      <c r="L9" s="42">
         <v>26</v>
       </c>
-      <c r="M9" s="48" t="s">
+      <c r="M9" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="N9" s="48" t="s">
+      <c r="N9" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="O9" s="48">
+      <c r="O9" s="43">
         <v>33000</v>
       </c>
-      <c r="P9" s="48" t="s">
+      <c r="P9" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="Q9" s="49">
+      <c r="Q9" s="44">
         <v>9874563214</v>
       </c>
-      <c r="T9" s="55" t="s">
+      <c r="T9" s="49" t="s">
         <v>71</v>
       </c>
-      <c r="U9" s="56"/>
-      <c r="V9" s="56"/>
-      <c r="W9" s="41" t="str">
+      <c r="U9" s="2"/>
+      <c r="V9" s="2"/>
+      <c r="W9" s="36" t="str">
         <f>IFERROR(VLOOKUP(VLOOKUP(B5,B3:H15,2,0),K3:Q15,MATCH(V11,K3:Q3,0),0),"Not available")</f>
         <v>Accountant</v>
       </c>
-      <c r="X9" s="30"/>
-      <c r="Y9" s="30"/>
-      <c r="Z9" s="31"/>
-    </row>
-    <row r="10" spans="2:27" ht="21" customHeight="1">
-      <c r="B10" s="48">
+      <c r="Z9" s="26"/>
+    </row>
+    <row r="10" spans="2:26" ht="21" customHeight="1">
+      <c r="B10" s="43">
         <v>20018</v>
       </c>
-      <c r="C10" s="47" t="s">
+      <c r="C10" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="48" t="s">
+      <c r="D10" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="48" t="s">
+      <c r="E10" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="48">
+      <c r="F10" s="43">
         <v>21000</v>
       </c>
-      <c r="G10" s="48" t="s">
+      <c r="G10" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="H10" s="49">
+      <c r="H10" s="44">
         <v>8974563214</v>
       </c>
-      <c r="I10" s="23"/>
-      <c r="J10" s="25"/>
-      <c r="K10" s="47" t="s">
+      <c r="I10" s="19"/>
+      <c r="J10" s="21"/>
+      <c r="K10" s="42" t="s">
         <v>23</v>
       </c>
-      <c r="L10" s="47">
+      <c r="L10" s="42">
         <v>25</v>
       </c>
-      <c r="M10" s="48" t="s">
+      <c r="M10" s="43" t="s">
         <v>18</v>
       </c>
-      <c r="N10" s="48" t="s">
+      <c r="N10" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="O10" s="48">
+      <c r="O10" s="43">
         <v>21000</v>
       </c>
-      <c r="P10" s="48" t="s">
+      <c r="P10" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="Q10" s="49">
+      <c r="Q10" s="44">
         <v>8974563214</v>
       </c>
-      <c r="T10" s="32"/>
-      <c r="U10" s="33"/>
-      <c r="V10" s="33"/>
-      <c r="W10" s="33"/>
-      <c r="X10" s="33"/>
-      <c r="Y10" s="33"/>
-      <c r="Z10" s="34"/>
-    </row>
-    <row r="11" spans="2:27" ht="15.5">
-      <c r="B11" s="48">
+      <c r="T10" s="27"/>
+      <c r="U10" s="28"/>
+      <c r="V10" s="28"/>
+      <c r="W10" s="28"/>
+      <c r="X10" s="28"/>
+      <c r="Y10" s="28"/>
+      <c r="Z10" s="29"/>
+    </row>
+    <row r="11" spans="2:26" ht="15.5">
+      <c r="B11" s="43">
         <v>20019</v>
       </c>
-      <c r="C11" s="47" t="s">
+      <c r="C11" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="48" t="s">
+      <c r="D11" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="48" t="s">
+      <c r="E11" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="48">
+      <c r="F11" s="43">
         <v>31500</v>
       </c>
-      <c r="G11" s="48" t="s">
+      <c r="G11" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="H11" s="49">
+      <c r="H11" s="44">
         <v>8745968745</v>
       </c>
-      <c r="I11" s="23"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="47" t="s">
+      <c r="I11" s="19"/>
+      <c r="J11" s="21"/>
+      <c r="K11" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="L11" s="47">
+      <c r="L11" s="42">
         <v>26</v>
       </c>
-      <c r="M11" s="48" t="s">
+      <c r="M11" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="N11" s="48" t="s">
+      <c r="N11" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="O11" s="48">
+      <c r="O11" s="43">
         <v>31500</v>
       </c>
-      <c r="P11" s="48" t="s">
+      <c r="P11" s="43" t="s">
         <v>16</v>
       </c>
-      <c r="Q11" s="49">
+      <c r="Q11" s="44">
         <v>8745968745</v>
       </c>
-      <c r="T11" s="44" t="s">
+      <c r="T11" s="39" t="s">
         <v>65</v>
       </c>
-      <c r="U11" s="57">
+      <c r="U11" s="50">
         <v>20019</v>
       </c>
-      <c r="V11" s="58" t="s">
+      <c r="V11" s="51" t="s">
         <v>4</v>
       </c>
-      <c r="W11" s="27"/>
-      <c r="X11" s="27"/>
-      <c r="Y11" s="27"/>
-      <c r="Z11" s="28"/>
-    </row>
-    <row r="12" spans="2:27" ht="21" customHeight="1">
-      <c r="B12" s="48">
+      <c r="W11" s="23"/>
+      <c r="X11" s="23"/>
+      <c r="Y11" s="23"/>
+      <c r="Z11" s="24"/>
+    </row>
+    <row r="12" spans="2:26" ht="21" customHeight="1">
+      <c r="B12" s="43">
         <v>20020</v>
       </c>
-      <c r="C12" s="47" t="s">
+      <c r="C12" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="48" t="s">
+      <c r="D12" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="48" t="s">
+      <c r="E12" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="48">
+      <c r="F12" s="43">
         <v>40500</v>
       </c>
-      <c r="G12" s="48" t="s">
+      <c r="G12" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="49">
+      <c r="H12" s="44">
         <v>9874569874</v>
       </c>
-      <c r="I12" s="23"/>
-      <c r="J12" s="25"/>
-      <c r="K12" s="47" t="s">
+      <c r="I12" s="19"/>
+      <c r="J12" s="21"/>
+      <c r="K12" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="L12" s="47">
+      <c r="L12" s="42">
         <v>28</v>
       </c>
-      <c r="M12" s="48" t="s">
+      <c r="M12" s="43" t="s">
         <v>14</v>
       </c>
-      <c r="N12" s="48" t="s">
+      <c r="N12" s="43" t="s">
         <v>15</v>
       </c>
-      <c r="O12" s="48">
+      <c r="O12" s="43">
         <v>40500</v>
       </c>
-      <c r="P12" s="48" t="s">
+      <c r="P12" s="43" t="s">
         <v>12</v>
       </c>
-      <c r="Q12" s="49">
+      <c r="Q12" s="44">
         <v>9874569874</v>
       </c>
-      <c r="T12" s="43" t="s">
+      <c r="T12" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="U12" s="30"/>
-      <c r="V12" s="60"/>
-      <c r="W12" s="60"/>
-      <c r="X12" s="60"/>
-      <c r="Y12" s="30"/>
-      <c r="Z12" s="31"/>
-    </row>
-    <row r="13" spans="2:27" ht="21" customHeight="1">
-      <c r="B13" s="48">
+      <c r="V12" s="2"/>
+      <c r="W12" s="2"/>
+      <c r="X12" s="2"/>
+      <c r="Z12" s="26"/>
+    </row>
+    <row r="13" spans="2:26" ht="21" customHeight="1">
+      <c r="B13" s="43">
         <v>20021</v>
       </c>
-      <c r="C13" s="47" t="s">
+      <c r="C13" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="48" t="s">
+      <c r="D13" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="48" t="s">
+      <c r="E13" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="F13" s="48">
+      <c r="F13" s="43">
         <v>25500</v>
       </c>
-      <c r="G13" s="48" t="s">
+      <c r="G13" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="H13" s="49">
+      <c r="H13" s="44">
         <v>8574965874</v>
       </c>
-      <c r="I13" s="23"/>
-      <c r="J13" s="25"/>
-      <c r="K13" s="47" t="s">
+      <c r="I13" s="19"/>
+      <c r="J13" s="21"/>
+      <c r="K13" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="L13" s="47">
+      <c r="L13" s="42">
         <v>27</v>
       </c>
-      <c r="M13" s="48" t="s">
+      <c r="M13" s="43" t="s">
         <v>10</v>
       </c>
-      <c r="N13" s="48" t="s">
+      <c r="N13" s="43" t="s">
         <v>11</v>
       </c>
-      <c r="O13" s="48">
+      <c r="O13" s="43">
         <v>25500</v>
       </c>
-      <c r="P13" s="48" t="s">
+      <c r="P13" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="Q13" s="49">
+      <c r="Q13" s="44">
         <v>8574965874</v>
       </c>
-      <c r="T13" s="32"/>
-      <c r="U13" s="33"/>
-      <c r="V13" s="39" t="str">
+      <c r="T13" s="27"/>
+      <c r="U13" s="28"/>
+      <c r="V13" s="34" t="str">
         <f>VLOOKUP(VLOOKUP(U11,B3:H15,2,0),K3:Q15,MATCH(V11,K3:Q3,0),0)</f>
         <v>Accountant</v>
       </c>
-      <c r="W13" s="33"/>
-      <c r="X13" s="33"/>
-      <c r="Y13" s="33"/>
-      <c r="Z13" s="34"/>
-    </row>
-    <row r="14" spans="2:27">
-      <c r="B14" s="20">
+      <c r="W13" s="28"/>
+      <c r="X13" s="28"/>
+      <c r="Y13" s="28"/>
+      <c r="Z13" s="29"/>
+    </row>
+    <row r="14" spans="2:26">
+      <c r="B14" s="16">
         <v>20022</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="E14" s="16" t="s">
         <v>15</v>
       </c>
-      <c r="F14" s="20">
+      <c r="F14" s="16">
         <v>18000</v>
       </c>
-      <c r="G14" s="20" t="s">
+      <c r="G14" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="H14" s="22">
+      <c r="H14" s="18">
         <v>8521479632</v>
       </c>
-      <c r="K14" s="17" t="s">
+      <c r="K14" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="L14" s="17">
+      <c r="L14" s="13">
         <v>26</v>
       </c>
-      <c r="M14" s="18" t="s">
+      <c r="M14" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="N14" s="18" t="s">
+      <c r="N14" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="O14" s="18">
+      <c r="O14" s="14">
         <v>18000</v>
       </c>
-      <c r="P14" s="18" t="s">
+      <c r="P14" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="Q14" s="19">
+      <c r="Q14" s="15">
         <v>8521479632</v>
       </c>
-      <c r="T14" s="45" t="s">
+      <c r="T14" s="40" t="s">
         <v>70</v>
       </c>
-      <c r="U14" s="27"/>
-      <c r="V14" s="37" t="str">
+      <c r="U14" s="23"/>
+      <c r="V14" s="32" t="str">
         <f>IFERROR(VLOOKUP(B5,B3:H15,8,0),"not available")</f>
         <v>not available</v>
       </c>
-      <c r="W14" s="27"/>
-      <c r="X14" s="27"/>
-      <c r="Y14" s="27"/>
-      <c r="Z14" s="28"/>
-    </row>
-    <row r="15" spans="2:27" ht="21" customHeight="1">
-      <c r="B15" s="20">
+      <c r="W14" s="23"/>
+      <c r="X14" s="23"/>
+      <c r="Y14" s="23"/>
+      <c r="Z14" s="24"/>
+    </row>
+    <row r="15" spans="2:26" ht="21" customHeight="1">
+      <c r="B15" s="16">
         <v>20023</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="C15" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="E15" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="16">
         <v>21000</v>
       </c>
-      <c r="G15" s="20" t="s">
+      <c r="G15" s="16" t="s">
         <v>12</v>
       </c>
-      <c r="H15" s="22">
+      <c r="H15" s="18">
         <v>8569745623</v>
       </c>
-      <c r="K15" s="17" t="s">
+      <c r="K15" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="L15" s="17">
+      <c r="L15" s="13">
         <v>27</v>
       </c>
-      <c r="M15" s="18" t="s">
+      <c r="M15" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="N15" s="18" t="s">
+      <c r="N15" s="14" t="s">
         <v>11</v>
       </c>
-      <c r="O15" s="18">
+      <c r="O15" s="14">
         <v>21000</v>
       </c>
-      <c r="P15" s="18" t="s">
+      <c r="P15" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="Q15" s="19">
+      <c r="Q15" s="15">
         <v>8569745623</v>
       </c>
-      <c r="T15" s="32"/>
-      <c r="U15" s="33"/>
-      <c r="V15" s="33"/>
-      <c r="W15" s="33"/>
-      <c r="X15" s="33"/>
-      <c r="Y15" s="33"/>
-      <c r="Z15" s="34"/>
+      <c r="T15" s="27"/>
+      <c r="U15" s="28"/>
+      <c r="V15" s="28"/>
+      <c r="W15" s="28"/>
+      <c r="X15" s="28"/>
+      <c r="Y15" s="28"/>
+      <c r="Z15" s="29"/>
     </row>
     <row r="17" spans="10:12" ht="18" customHeight="1"/>
     <row r="18" spans="10:12" ht="54.75" customHeight="1"/>
@@ -4766,9 +4755,9 @@
     <row r="20" spans="10:12" ht="14.25" customHeight="1"/>
     <row r="21" spans="10:12" ht="27.75" customHeight="1"/>
     <row r="22" spans="10:12" ht="36" customHeight="1">
-      <c r="J22" s="3"/>
-      <c r="K22" s="3"/>
-      <c r="L22" s="3"/>
+      <c r="J22" s="134"/>
+      <c r="K22" s="134"/>
+      <c r="L22" s="134"/>
     </row>
     <row r="24" spans="10:12" ht="41.25" customHeight="1"/>
     <row r="25" spans="10:12" ht="14.25" customHeight="1"/>
@@ -4776,7 +4765,7 @@
   <mergeCells count="1">
     <mergeCell ref="J22:L22"/>
   </mergeCells>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B4:B15" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>#REF!</formula1>
       <formula2>0</formula2>
@@ -4813,610 +4802,610 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="23.25" customHeight="1" thickBot="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="F1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="G1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="I1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="J1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="K1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="L1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="M1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="N1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="O1" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:22" ht="21" customHeight="1">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2" s="3">
         <v>20012</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="3">
         <v>26500</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G2" s="8">
+      <c r="G2" s="5">
         <v>8877456987</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="4">
         <v>26</v>
       </c>
-      <c r="K2" s="6" t="s">
+      <c r="K2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L2" s="6" t="s">
+      <c r="L2" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="6">
+      <c r="M2" s="3">
         <v>26500</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="O2" s="8">
+      <c r="O2" s="5">
         <v>8877456987</v>
       </c>
-      <c r="Q2" s="70" t="s">
+      <c r="Q2" s="62" t="s">
         <v>72</v>
       </c>
-      <c r="R2" s="61"/>
-      <c r="S2" s="62">
+      <c r="R2" s="53"/>
+      <c r="S2" s="54">
         <f>VLOOKUP(VLOOKUP(R3,CHOOSE({1,2},B1:B13,A1:A13),2,0),I1:O13,2,0)</f>
         <v>25</v>
       </c>
-      <c r="T2" s="9"/>
-      <c r="U2" s="9"/>
-      <c r="V2" s="9"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
     </row>
     <row r="3" spans="1:22" ht="21" customHeight="1">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3" s="3">
         <v>20013</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E3" s="6">
+      <c r="E3" s="3">
         <v>13000</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="5">
         <v>8569741235</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="7">
+      <c r="J3" s="4">
         <v>25</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="K3" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="6">
+      <c r="M3" s="3">
         <v>13000</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O3" s="8">
+      <c r="O3" s="5">
         <v>8569741235</v>
       </c>
-      <c r="Q3" s="69" t="s">
+      <c r="Q3" s="61" t="s">
         <v>73</v>
       </c>
-      <c r="R3" s="71">
+      <c r="R3" s="63">
         <v>20013</v>
       </c>
-      <c r="S3" s="63"/>
+      <c r="S3" s="55"/>
     </row>
     <row r="4" spans="1:22" ht="21" customHeight="1" thickBot="1">
-      <c r="A4" s="7" t="s">
+      <c r="A4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4" s="3">
         <v>20014</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="6">
+      <c r="E4" s="3">
         <v>20000</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="5">
         <v>7584963214</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="4">
         <v>28</v>
       </c>
-      <c r="K4" s="6" t="s">
+      <c r="K4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L4" s="6" t="s">
+      <c r="L4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M4" s="6">
+      <c r="M4" s="3">
         <v>20000</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="N4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="O4" s="8">
+      <c r="O4" s="5">
         <v>7584963214</v>
       </c>
-      <c r="Q4" s="65"/>
-      <c r="R4" s="66"/>
-      <c r="S4" s="68"/>
+      <c r="Q4" s="57"/>
+      <c r="R4" s="58"/>
+      <c r="S4" s="60"/>
     </row>
     <row r="5" spans="1:22" ht="21" customHeight="1">
-      <c r="A5" s="7" t="s">
+      <c r="A5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5" s="3">
         <v>20015</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="6">
+      <c r="E5" s="3">
         <v>15000</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="5">
         <v>7788994455</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="I5" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J5" s="7">
+      <c r="J5" s="4">
         <v>27</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M5" s="6">
+      <c r="M5" s="3">
         <v>15000</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="N5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O5" s="8">
+      <c r="O5" s="5">
         <v>7788994455</v>
       </c>
-      <c r="Q5" s="72" t="s">
+      <c r="Q5" s="135" t="s">
         <v>74</v>
       </c>
-      <c r="R5" s="73"/>
-      <c r="S5" s="74"/>
+      <c r="R5" s="136"/>
+      <c r="S5" s="137"/>
     </row>
     <row r="6" spans="1:22" ht="21" customHeight="1" thickBot="1">
-      <c r="A6" s="7" t="s">
+      <c r="A6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6" s="3">
         <v>20016</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="6">
+      <c r="E6" s="3">
         <v>20000</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="5">
         <v>8798654512</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="J6" s="7">
+      <c r="J6" s="4">
         <v>25</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="K6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="L6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M6" s="6">
+      <c r="M6" s="3">
         <v>20000</v>
       </c>
-      <c r="N6" s="6" t="s">
+      <c r="N6" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="O6" s="8">
+      <c r="O6" s="5">
         <v>8798654512</v>
       </c>
-      <c r="Q6" s="65">
+      <c r="Q6" s="57">
         <f t="array" ref="Q6:S6">IFERROR(VLOOKUP(VLOOKUP(R3,CHOOSE({1,2},B:B,A:A),2,0),I1:O13,{2,4,7},0),"NOT AVAILABLE")</f>
         <v>25</v>
       </c>
-      <c r="R6" s="66" t="str">
+      <c r="R6" s="58" t="str">
         <v>Finance</v>
       </c>
-      <c r="S6" s="67">
+      <c r="S6" s="59">
         <v>8569741235</v>
       </c>
     </row>
     <row r="7" spans="1:22" ht="21" customHeight="1">
-      <c r="A7" s="7" t="s">
+      <c r="A7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7" s="3">
         <v>20017</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E7" s="6">
+      <c r="E7" s="3">
         <v>33000</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="5">
         <v>9874563214</v>
       </c>
-      <c r="I7" s="7" t="s">
+      <c r="I7" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="J7" s="7">
+      <c r="J7" s="4">
         <v>26</v>
       </c>
-      <c r="K7" s="6" t="s">
+      <c r="K7" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L7" s="6" t="s">
+      <c r="L7" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="3">
         <v>33000</v>
       </c>
-      <c r="N7" s="6" t="s">
+      <c r="N7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O7" s="8">
+      <c r="O7" s="5">
         <v>9874563214</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="21" customHeight="1">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8" s="3">
         <v>20018</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E8" s="6">
+      <c r="E8" s="3">
         <v>21000</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="5">
         <v>8974563214</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="I8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="J8" s="7">
+      <c r="J8" s="4">
         <v>25</v>
       </c>
-      <c r="K8" s="6" t="s">
+      <c r="K8" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L8" s="6" t="s">
+      <c r="L8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M8" s="6">
+      <c r="M8" s="3">
         <v>21000</v>
       </c>
-      <c r="N8" s="6" t="s">
+      <c r="N8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="O8" s="8">
+      <c r="O8" s="5">
         <v>8974563214</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="21" customHeight="1">
-      <c r="A9" s="7" t="s">
+      <c r="A9" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9" s="3">
         <v>20019</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="6">
+      <c r="E9" s="3">
         <v>31500</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="5">
         <v>8745968745</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="J9" s="7">
+      <c r="J9" s="4">
         <v>26</v>
       </c>
-      <c r="K9" s="6" t="s">
+      <c r="K9" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="L9" s="6" t="s">
+      <c r="L9" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M9" s="6">
+      <c r="M9" s="3">
         <v>31500</v>
       </c>
-      <c r="N9" s="6" t="s">
+      <c r="N9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="O9" s="8">
+      <c r="O9" s="5">
         <v>8745968745</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="21" customHeight="1">
-      <c r="A10" s="7" t="s">
+      <c r="A10" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10" s="3">
         <v>20020</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="6">
+      <c r="E10" s="3">
         <v>40500</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="5">
         <v>9874569874</v>
       </c>
-      <c r="I10" s="7" t="s">
+      <c r="I10" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="J10" s="7">
+      <c r="J10" s="4">
         <v>28</v>
       </c>
-      <c r="K10" s="6" t="s">
+      <c r="K10" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="L10" s="6" t="s">
+      <c r="L10" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M10" s="6">
+      <c r="M10" s="3">
         <v>40500</v>
       </c>
-      <c r="N10" s="6" t="s">
+      <c r="N10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="O10" s="8">
+      <c r="O10" s="5">
         <v>9874569874</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="21" customHeight="1">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="3">
         <v>20021</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E11" s="6">
+      <c r="E11" s="3">
         <v>25500</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="5">
         <v>8574965874</v>
       </c>
-      <c r="I11" s="7" t="s">
+      <c r="I11" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="J11" s="7">
+      <c r="J11" s="4">
         <v>27</v>
       </c>
-      <c r="K11" s="6" t="s">
+      <c r="K11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L11" s="6" t="s">
+      <c r="L11" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M11" s="6">
+      <c r="M11" s="3">
         <v>25500</v>
       </c>
-      <c r="N11" s="6" t="s">
+      <c r="N11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="O11" s="8">
+      <c r="O11" s="5">
         <v>8574965874</v>
       </c>
     </row>
     <row r="12" spans="1:22" ht="21" customHeight="1">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="3">
         <v>20022</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E12" s="3">
         <v>18000</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="5">
         <v>8521479632</v>
       </c>
-      <c r="I12" s="7" t="s">
+      <c r="I12" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="J12" s="7">
+      <c r="J12" s="4">
         <v>26</v>
       </c>
-      <c r="K12" s="6" t="s">
+      <c r="K12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="L12" s="6" t="s">
+      <c r="L12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="M12" s="6">
+      <c r="M12" s="3">
         <v>18000</v>
       </c>
-      <c r="N12" s="6" t="s">
+      <c r="N12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="O12" s="8">
+      <c r="O12" s="5">
         <v>8521479632</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="21" customHeight="1">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="3">
         <v>20023</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C13" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E13" s="3">
         <v>21000</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="5">
         <v>8569745623</v>
       </c>
-      <c r="I13" s="7" t="s">
+      <c r="I13" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="J13" s="7">
+      <c r="J13" s="4">
         <v>27</v>
       </c>
-      <c r="K13" s="6" t="s">
+      <c r="K13" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="L13" s="6" t="s">
+      <c r="L13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M13" s="6">
+      <c r="M13" s="3">
         <v>21000</v>
       </c>
-      <c r="N13" s="6" t="s">
+      <c r="N13" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="O13" s="8">
+      <c r="O13" s="5">
         <v>8569745623</v>
       </c>
     </row>
@@ -5454,138 +5443,138 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="51" customHeight="1">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="24" t="s">
+      <c r="B1" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="80" t="s">
+      <c r="C1" s="69" t="s">
         <v>77</v>
       </c>
-      <c r="D1" s="62" t="str">
+      <c r="D1" s="54" t="str">
         <f>VLOOKUP(D2,A1:B6,2,1)</f>
         <v>B</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A2" s="6">
+      <c r="A2" s="3">
         <v>0</v>
       </c>
-      <c r="B2" s="25" t="s">
+      <c r="B2" s="21" t="s">
         <v>78</v>
       </c>
-      <c r="C2" s="78" t="s">
+      <c r="C2" s="67" t="s">
         <v>79</v>
       </c>
-      <c r="D2" s="79">
+      <c r="D2" s="68">
         <v>82</v>
       </c>
     </row>
     <row r="3" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A3" s="6">
+      <c r="A3" s="3">
         <v>40</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="3" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="4" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A4" s="6">
+      <c r="A4" s="3">
         <v>60</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="3" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A5" s="6">
+      <c r="A5" s="3">
         <v>75</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="3" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A6" s="6">
+      <c r="A6" s="3">
         <v>90</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="3" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="68.25" customHeight="1"/>
     <row r="9" spans="1:7" ht="14.25" customHeight="1"/>
     <row r="10" spans="1:7" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="B10" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="1" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="3">
         <v>110</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="3">
         <v>105</v>
       </c>
-      <c r="D11" s="6">
+      <c r="D11" s="3">
         <v>106</v>
       </c>
-      <c r="F11" s="75" t="s">
+      <c r="F11" s="64" t="s">
         <v>84</v>
       </c>
-      <c r="G11" s="62">
+      <c r="G11" s="54">
         <f>VLOOKUP(F12,A10:D13,MATCH(F13,A10:D10,0),0)</f>
         <v>110</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12" s="3">
         <v>110</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="3">
         <v>104</v>
       </c>
-      <c r="D12" s="6">
+      <c r="D12" s="3">
         <v>105</v>
       </c>
-      <c r="F12" s="76" t="s">
+      <c r="F12" s="65" t="s">
         <v>85</v>
       </c>
-      <c r="G12" s="63"/>
+      <c r="G12" s="55"/>
     </row>
     <row r="13" spans="1:7" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="B13" s="6">
+      <c r="B13" s="3">
         <v>103</v>
       </c>
-      <c r="C13" s="6">
+      <c r="C13" s="3">
         <v>100</v>
       </c>
-      <c r="D13" s="6">
+      <c r="D13" s="3">
         <v>106</v>
       </c>
-      <c r="F13" s="77" t="s">
+      <c r="F13" s="66" t="s">
         <v>86</v>
       </c>
-      <c r="G13" s="68"/>
+      <c r="G13" s="60"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -5615,556 +5604,526 @@
   </cols>
   <sheetData>
     <row r="2" spans="3:17" ht="21" customHeight="1">
-      <c r="C2" s="81" t="s">
+      <c r="C2" s="138" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="81"/>
-      <c r="E2" s="5" t="s">
+      <c r="D2" s="138"/>
+      <c r="E2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="5">
+      <c r="F2" s="1">
         <v>20012</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="1">
         <v>20013</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2" s="1">
         <v>20014</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="1">
         <v>20015</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2" s="1">
         <v>20016</v>
       </c>
-      <c r="K2" s="5">
+      <c r="K2" s="1">
         <v>20017</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="1">
         <v>20018</v>
       </c>
-      <c r="M2" s="5">
+      <c r="M2" s="1">
         <v>20019</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" s="1">
         <v>20020</v>
       </c>
-      <c r="O2" s="5">
+      <c r="O2" s="1">
         <v>20021</v>
       </c>
-      <c r="P2" s="5">
+      <c r="P2" s="1">
         <v>20022</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="Q2" s="1">
         <v>20023</v>
       </c>
     </row>
     <row r="3" spans="3:17" ht="23.25" customHeight="1">
-      <c r="C3" s="81"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="15" t="s">
+      <c r="C3" s="138"/>
+      <c r="D3" s="138"/>
+      <c r="E3" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="F3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="7" t="s">
+      <c r="H3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="I3" s="7" t="s">
+      <c r="I3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="J3" s="7" t="s">
+      <c r="J3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="K3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="L3" s="7" t="s">
+      <c r="L3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="M3" s="7" t="s">
+      <c r="M3" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="N3" s="7" t="s">
+      <c r="N3" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="O3" s="7" t="s">
+      <c r="O3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="P3" s="7" t="s">
+      <c r="P3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="Q3" s="7" t="s">
+      <c r="Q3" s="4" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="4" spans="3:17" ht="23.25" customHeight="1">
-      <c r="C4" s="81"/>
-      <c r="D4" s="81"/>
-      <c r="E4" s="15" t="s">
+      <c r="C4" s="138"/>
+      <c r="D4" s="138"/>
+      <c r="E4" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="4">
         <v>26</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="4">
         <v>25</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="4">
         <v>28</v>
       </c>
-      <c r="I4" s="7">
+      <c r="I4" s="4">
         <v>27</v>
       </c>
-      <c r="J4" s="7">
+      <c r="J4" s="4">
         <v>25</v>
       </c>
-      <c r="K4" s="7">
+      <c r="K4" s="4">
         <v>26</v>
       </c>
-      <c r="L4" s="7">
+      <c r="L4" s="4">
         <v>25</v>
       </c>
-      <c r="M4" s="7">
+      <c r="M4" s="4">
         <v>26</v>
       </c>
-      <c r="N4" s="7">
+      <c r="N4" s="4">
         <v>28</v>
       </c>
-      <c r="O4" s="7">
+      <c r="O4" s="4">
         <v>27</v>
       </c>
-      <c r="P4" s="7">
+      <c r="P4" s="4">
         <v>26</v>
       </c>
-      <c r="Q4" s="7">
+      <c r="Q4" s="4">
         <v>27</v>
       </c>
     </row>
     <row r="5" spans="3:17" ht="21" customHeight="1">
-      <c r="C5" s="81"/>
-      <c r="D5" s="81"/>
-      <c r="E5" s="15" t="s">
+      <c r="C5" s="138"/>
+      <c r="D5" s="138"/>
+      <c r="E5" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="6" t="s">
+      <c r="K5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="M5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="N5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="O5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="P5" s="6" t="s">
+      <c r="P5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="Q5" s="6" t="s">
+      <c r="Q5" s="3" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="6" spans="3:17" ht="21" customHeight="1">
-      <c r="C6" s="81"/>
-      <c r="D6" s="81"/>
-      <c r="E6" s="15" t="s">
+      <c r="C6" s="138"/>
+      <c r="D6" s="138"/>
+      <c r="E6" s="11" t="s">
         <v>5</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="K6" s="6" t="s">
+      <c r="K6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="L6" s="6" t="s">
+      <c r="L6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="M6" s="6" t="s">
+      <c r="M6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="N6" s="6" t="s">
+      <c r="N6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="O6" s="6" t="s">
+      <c r="O6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="P6" s="6" t="s">
+      <c r="P6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="Q6" s="6" t="s">
+      <c r="Q6" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="7" spans="3:17" ht="21" customHeight="1">
-      <c r="C7" s="81"/>
-      <c r="D7" s="81"/>
-      <c r="E7" s="15" t="s">
+      <c r="C7" s="138"/>
+      <c r="D7" s="138"/>
+      <c r="E7" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="3">
         <v>26500</v>
       </c>
-      <c r="G7" s="6">
+      <c r="G7" s="3">
         <v>13000</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="3">
         <v>20000</v>
       </c>
-      <c r="I7" s="6">
+      <c r="I7" s="3">
         <v>15000</v>
       </c>
-      <c r="J7" s="6">
+      <c r="J7" s="3">
         <v>20000</v>
       </c>
-      <c r="K7" s="6">
+      <c r="K7" s="3">
         <v>33000</v>
       </c>
-      <c r="L7" s="6">
+      <c r="L7" s="3">
         <v>21000</v>
       </c>
-      <c r="M7" s="6">
+      <c r="M7" s="3">
         <v>31500</v>
       </c>
-      <c r="N7" s="6">
+      <c r="N7" s="3">
         <v>40500</v>
       </c>
-      <c r="O7" s="6">
+      <c r="O7" s="3">
         <v>25500</v>
       </c>
-      <c r="P7" s="6">
+      <c r="P7" s="3">
         <v>18000</v>
       </c>
-      <c r="Q7" s="6">
+      <c r="Q7" s="3">
         <v>21000</v>
       </c>
     </row>
     <row r="8" spans="3:17" ht="21" customHeight="1">
-      <c r="C8" s="81"/>
-      <c r="D8" s="81"/>
-      <c r="E8" s="15" t="s">
+      <c r="C8" s="138"/>
+      <c r="D8" s="138"/>
+      <c r="E8" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="J8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="K8" s="6" t="s">
+      <c r="K8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L8" s="6" t="s">
+      <c r="L8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="M8" s="6" t="s">
+      <c r="M8" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="N8" s="6" t="s">
+      <c r="N8" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="O8" s="6" t="s">
+      <c r="O8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="P8" s="6" t="s">
+      <c r="P8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="Q8" s="6" t="s">
+      <c r="Q8" s="3" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="9" spans="3:17" ht="21" customHeight="1">
-      <c r="C9" s="81"/>
-      <c r="D9" s="81"/>
-      <c r="E9" s="15" t="s">
+      <c r="C9" s="138"/>
+      <c r="D9" s="138"/>
+      <c r="E9" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="8">
+      <c r="F9" s="5">
         <v>8877456987</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="5">
         <v>8569741235</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="5">
         <v>7584963214</v>
       </c>
-      <c r="I9" s="8">
+      <c r="I9" s="5">
         <v>7788994455</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="5">
         <v>8798654512</v>
       </c>
-      <c r="K9" s="8">
+      <c r="K9" s="5">
         <v>9874563214</v>
       </c>
-      <c r="L9" s="8">
+      <c r="L9" s="5">
         <v>8974563214</v>
       </c>
-      <c r="M9" s="8">
+      <c r="M9" s="5">
         <v>8745968745</v>
       </c>
-      <c r="N9" s="8">
+      <c r="N9" s="5">
         <v>9874569874</v>
       </c>
-      <c r="O9" s="8">
+      <c r="O9" s="5">
         <v>8574965874</v>
       </c>
-      <c r="P9" s="8">
+      <c r="P9" s="5">
         <v>8521479632</v>
       </c>
-      <c r="Q9" s="8">
+      <c r="Q9" s="5">
         <v>8569745623</v>
       </c>
     </row>
     <row r="12" spans="3:17" ht="15" thickBot="1">
-      <c r="C12" s="89" t="s">
+      <c r="C12" s="75" t="s">
         <v>92</v>
       </c>
-      <c r="D12" s="90">
+      <c r="D12" s="76">
         <v>20014</v>
       </c>
     </row>
     <row r="13" spans="3:17" ht="36" customHeight="1" thickBot="1">
-      <c r="C13" s="85" t="s">
+      <c r="C13" s="73" t="s">
         <v>93</v>
       </c>
-      <c r="D13" s="83" t="str">
+      <c r="D13" s="71" t="str">
         <f>HLOOKUP(D12,C2:Q9,2,0)</f>
         <v>Kapil Singh</v>
       </c>
     </row>
     <row r="14" spans="3:17" ht="14.25" customHeight="1" thickBot="1"/>
     <row r="15" spans="3:17" ht="41.25" customHeight="1" thickBot="1">
-      <c r="C15" s="85" t="s">
+      <c r="C15" s="73" t="s">
         <v>94</v>
       </c>
-      <c r="D15" s="84" t="str">
+      <c r="D15" s="72" t="str">
         <f t="array" ref="D15:F15">HLOOKUP(D12,E2:Q9,{2,3,4},0)</f>
         <v>Kapil Singh</v>
       </c>
-      <c r="E15" s="84">
+      <c r="E15" s="72">
         <v>28</v>
       </c>
-      <c r="F15" s="83" t="str">
+      <c r="F15" s="71" t="str">
         <v>CAD Designer</v>
       </c>
     </row>
     <row r="16" spans="3:17" ht="14.25" customHeight="1"/>
     <row r="17" spans="3:7" ht="14.25" customHeight="1" thickBot="1"/>
     <row r="18" spans="3:7" ht="27.75" customHeight="1">
-      <c r="C18" s="86" t="s">
+      <c r="C18" s="74" t="s">
         <v>95</v>
       </c>
-      <c r="D18" s="62">
+      <c r="D18" s="54">
         <f>HLOOKUP(D12,E2:Q9,MATCH(C19,E2:E9,0),0)</f>
         <v>20000</v>
       </c>
-      <c r="E18" s="82"/>
-      <c r="F18" s="82"/>
+      <c r="E18" s="70"/>
+      <c r="F18" s="70"/>
     </row>
     <row r="19" spans="3:7" ht="14.25" customHeight="1" thickBot="1">
-      <c r="C19" s="91" t="s">
+      <c r="C19" s="77" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="68"/>
+      <c r="D19" s="60"/>
     </row>
     <row r="20" spans="3:7" ht="14.25" customHeight="1"/>
     <row r="21" spans="3:7" ht="14.25" customHeight="1"/>
     <row r="22" spans="3:7" ht="14.25" customHeight="1" thickBot="1"/>
     <row r="23" spans="3:7" ht="14.25" customHeight="1">
-      <c r="C23" s="86" t="s">
+      <c r="C23" s="74" t="s">
         <v>96</v>
       </c>
-      <c r="D23" s="62" t="str">
+      <c r="D23" s="54" t="str">
         <f>HLOOKUP($D$12,$E$2:$Q$9,ROWS($E$2:E3),0)</f>
         <v>Kapil Singh</v>
       </c>
-      <c r="E23" s="82"/>
-      <c r="F23" s="82"/>
-      <c r="G23" s="82"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
     </row>
     <row r="24" spans="3:7" ht="14.25" customHeight="1">
-      <c r="C24" s="64"/>
-      <c r="D24" s="63">
+      <c r="C24" s="56"/>
+      <c r="D24" s="55">
         <f>HLOOKUP($D$12,$E$2:$Q$9,ROWS($E$2:E4),0)</f>
         <v>28</v>
       </c>
     </row>
     <row r="25" spans="3:7" ht="14.25" customHeight="1">
-      <c r="C25" s="64"/>
-      <c r="D25" s="63" t="str">
+      <c r="C25" s="56"/>
+      <c r="D25" s="55" t="str">
         <f>HLOOKUP($D$12,$E$2:$Q$9,ROWS($E$2:E5),0)</f>
         <v>CAD Designer</v>
       </c>
     </row>
     <row r="26" spans="3:7" ht="27.75" customHeight="1">
-      <c r="C26" s="64"/>
-      <c r="D26" s="63" t="str">
+      <c r="C26" s="56"/>
+      <c r="D26" s="55" t="str">
         <f>HLOOKUP($D$12,$E$2:$Q$9,ROWS($E$2:E6),0)</f>
         <v>Technical</v>
       </c>
     </row>
     <row r="27" spans="3:7" ht="14.25" customHeight="1">
-      <c r="C27" s="64"/>
-      <c r="D27" s="63">
+      <c r="C27" s="56"/>
+      <c r="D27" s="55">
         <f>HLOOKUP($D$12,$E$2:$Q$9,ROWS($E$2:E7),0)</f>
         <v>20000</v>
       </c>
     </row>
     <row r="28" spans="3:7" ht="14.25" customHeight="1">
-      <c r="C28" s="64"/>
-      <c r="D28" s="63" t="str">
+      <c r="C28" s="56"/>
+      <c r="D28" s="55" t="str">
         <f>HLOOKUP($D$12,$E$2:$Q$9,ROWS($E$2:E8),0)</f>
         <v>Indore</v>
       </c>
     </row>
     <row r="29" spans="3:7" ht="14.25" customHeight="1" thickBot="1">
-      <c r="C29" s="65"/>
-      <c r="D29" s="67">
+      <c r="C29" s="57"/>
+      <c r="D29" s="59">
         <f>HLOOKUP($D$12,$E$2:$Q$9,ROWS($E$2:E9),0)</f>
         <v>7584963214</v>
       </c>
-      <c r="F29" s="82"/>
-      <c r="G29" s="82"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
     </row>
     <row r="30" spans="3:7" ht="14.25" customHeight="1"/>
     <row r="31" spans="3:7" ht="14.25" customHeight="1"/>
     <row r="32" spans="3:7" ht="14.25" customHeight="1"/>
     <row r="33" spans="2:9" ht="14.25" customHeight="1" thickBot="1"/>
     <row r="34" spans="2:9" ht="68.25" customHeight="1">
-      <c r="B34" s="87" t="s">
+      <c r="B34" s="126" t="s">
         <v>97</v>
       </c>
-      <c r="C34" s="88"/>
-      <c r="D34" s="88"/>
-      <c r="E34" s="88"/>
-      <c r="F34" s="88"/>
-      <c r="G34" s="88"/>
-      <c r="H34" s="88"/>
-      <c r="I34" s="62" t="str">
-        <f>HLOOKUP($D$12,$E$2:$Q$9,ROW(E2),0)</f>
+      <c r="C34" s="127"/>
+      <c r="D34" s="127"/>
+      <c r="E34" s="127"/>
+      <c r="F34" s="127"/>
+      <c r="G34" s="127"/>
+      <c r="H34" s="127"/>
+      <c r="I34" s="54" t="str">
+        <f t="shared" ref="I34:I40" si="0">HLOOKUP($D$12,$E$2:$Q$9,ROW(E2),0)</f>
         <v>Kapil Singh</v>
       </c>
     </row>
     <row r="35" spans="2:9">
-      <c r="B35" s="64"/>
-      <c r="C35" s="30"/>
-      <c r="D35" s="30"/>
-      <c r="E35" s="30"/>
-      <c r="F35" s="30"/>
-      <c r="G35" s="30"/>
-      <c r="H35" s="30"/>
-      <c r="I35" s="63">
-        <f>HLOOKUP($D$12,$E$2:$Q$9,ROW(E3),0)</f>
+      <c r="B35" s="56"/>
+      <c r="I35" s="55">
+        <f t="shared" si="0"/>
         <v>28</v>
       </c>
     </row>
     <row r="36" spans="2:9">
-      <c r="B36" s="64"/>
-      <c r="C36" s="30"/>
-      <c r="D36" s="30"/>
-      <c r="E36" s="30"/>
-      <c r="F36" s="30"/>
-      <c r="G36" s="30"/>
-      <c r="H36" s="30"/>
-      <c r="I36" s="63" t="str">
-        <f>HLOOKUP($D$12,$E$2:$Q$9,ROW(E4),0)</f>
+      <c r="B36" s="56"/>
+      <c r="I36" s="55" t="str">
+        <f t="shared" si="0"/>
         <v>CAD Designer</v>
       </c>
     </row>
     <row r="37" spans="2:9">
-      <c r="B37" s="64"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="30"/>
-      <c r="I37" s="63" t="str">
-        <f>HLOOKUP($D$12,$E$2:$Q$9,ROW(E5),0)</f>
+      <c r="B37" s="56"/>
+      <c r="I37" s="55" t="str">
+        <f t="shared" si="0"/>
         <v>Technical</v>
       </c>
     </row>
     <row r="38" spans="2:9">
-      <c r="B38" s="64"/>
-      <c r="C38" s="30"/>
-      <c r="D38" s="30"/>
-      <c r="E38" s="30"/>
-      <c r="F38" s="30"/>
-      <c r="G38" s="30"/>
-      <c r="H38" s="30"/>
-      <c r="I38" s="63">
-        <f>HLOOKUP($D$12,$E$2:$Q$9,ROW(E6),0)</f>
+      <c r="B38" s="56"/>
+      <c r="I38" s="55">
+        <f t="shared" si="0"/>
         <v>20000</v>
       </c>
     </row>
     <row r="39" spans="2:9">
-      <c r="B39" s="64"/>
-      <c r="C39" s="30"/>
-      <c r="D39" s="30"/>
-      <c r="E39" s="30"/>
-      <c r="F39" s="30"/>
-      <c r="G39" s="30"/>
-      <c r="H39" s="30"/>
-      <c r="I39" s="63" t="str">
-        <f>HLOOKUP($D$12,$E$2:$Q$9,ROW(E7),0)</f>
+      <c r="B39" s="56"/>
+      <c r="I39" s="55" t="str">
+        <f t="shared" si="0"/>
         <v>Indore</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="15" thickBot="1">
-      <c r="B40" s="65"/>
-      <c r="C40" s="66"/>
-      <c r="D40" s="66"/>
-      <c r="E40" s="66"/>
-      <c r="F40" s="66"/>
-      <c r="G40" s="66"/>
-      <c r="H40" s="66"/>
-      <c r="I40" s="68">
-        <f>HLOOKUP($D$12,$E$2:$Q$9,ROW(E8),0)</f>
+      <c r="B40" s="57"/>
+      <c r="C40" s="58"/>
+      <c r="D40" s="58"/>
+      <c r="E40" s="58"/>
+      <c r="F40" s="58"/>
+      <c r="G40" s="58"/>
+      <c r="H40" s="58"/>
+      <c r="I40" s="60">
+        <f t="shared" si="0"/>
         <v>7584963214</v>
       </c>
     </row>
@@ -6187,7 +6146,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:X21"/>
+  <dimension ref="A1:S21"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
@@ -6212,649 +6171,584 @@
     <col min="24" max="24" width="11.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" ht="14.25" customHeight="1">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:19" ht="14.25" customHeight="1">
+      <c r="A1" s="139" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-    </row>
-    <row r="2" spans="1:24" ht="14.25" customHeight="1">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-    </row>
-    <row r="3" spans="1:24" ht="23.25" customHeight="1" thickBot="1">
-      <c r="A3" s="5" t="s">
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+    </row>
+    <row r="2" spans="1:19" ht="14.25" customHeight="1">
+      <c r="A2" s="139"/>
+      <c r="B2" s="139"/>
+      <c r="C2" s="139"/>
+      <c r="D2" s="139"/>
+      <c r="E2" s="139"/>
+      <c r="F2" s="139"/>
+      <c r="G2" s="139"/>
+      <c r="H2" s="139"/>
+    </row>
+    <row r="3" spans="1:19" ht="23.25" customHeight="1" thickBot="1">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="D3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="F3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="5" t="s">
+      <c r="G3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="97"/>
-      <c r="M3" s="97"/>
-      <c r="N3" s="97"/>
-      <c r="O3" s="97"/>
-      <c r="P3" s="97"/>
-      <c r="Q3" s="97"/>
-      <c r="R3" s="97"/>
-      <c r="S3" s="97"/>
-    </row>
-    <row r="4" spans="1:24" ht="21" customHeight="1">
-      <c r="A4" s="6">
+      <c r="L3" s="83"/>
+      <c r="M3" s="83"/>
+      <c r="N3" s="83"/>
+      <c r="O3" s="83"/>
+      <c r="P3" s="83"/>
+      <c r="Q3" s="83"/>
+      <c r="R3" s="83"/>
+      <c r="S3" s="83"/>
+    </row>
+    <row r="4" spans="1:19" ht="21" customHeight="1">
+      <c r="A4" s="3">
         <v>20012</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="7">
+      <c r="C4" s="4">
         <v>26</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="3">
         <v>26500</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="8">
+      <c r="H4" s="5">
         <v>8877456987</v>
       </c>
-      <c r="L4" s="101" t="s">
+      <c r="L4" s="87" t="s">
         <v>98</v>
       </c>
-      <c r="M4" s="102"/>
-      <c r="N4" s="102"/>
-      <c r="O4" s="102"/>
-      <c r="P4" s="102"/>
-      <c r="Q4" s="102"/>
-      <c r="R4" s="102"/>
-      <c r="S4" s="103"/>
-      <c r="T4" s="104"/>
-      <c r="U4" s="104"/>
-      <c r="V4" s="104"/>
-      <c r="W4" s="104"/>
-      <c r="X4" s="104"/>
-    </row>
-    <row r="5" spans="1:24" ht="21" customHeight="1">
-      <c r="A5" s="6">
+      <c r="M4" s="88"/>
+      <c r="N4" s="88"/>
+      <c r="O4" s="88"/>
+      <c r="P4" s="88"/>
+      <c r="Q4" s="88"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="89"/>
+    </row>
+    <row r="5" spans="1:19" ht="21" customHeight="1">
+      <c r="A5" s="3">
         <v>20013</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="4">
         <v>25</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="3">
         <v>13000</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="8">
+      <c r="H5" s="5">
         <v>8569741235</v>
       </c>
-      <c r="L5" s="69" t="s">
+      <c r="L5" s="61" t="s">
         <v>92</v>
       </c>
-      <c r="M5" s="105"/>
-      <c r="N5" s="105"/>
-      <c r="O5" s="105"/>
-      <c r="P5" s="105"/>
-      <c r="Q5" s="105"/>
-      <c r="R5" s="105"/>
-      <c r="S5" s="106"/>
-      <c r="T5" s="104"/>
-      <c r="U5" s="104"/>
-      <c r="V5" s="104"/>
-      <c r="W5" s="104"/>
-      <c r="X5" s="104"/>
-    </row>
-    <row r="6" spans="1:24" ht="21" customHeight="1" thickBot="1">
-      <c r="A6" s="6">
+      <c r="M5" s="3"/>
+      <c r="N5" s="3"/>
+      <c r="O5" s="3"/>
+      <c r="P5" s="3"/>
+      <c r="Q5" s="3"/>
+      <c r="R5" s="3"/>
+      <c r="S5" s="90"/>
+    </row>
+    <row r="6" spans="1:19" ht="21" customHeight="1" thickBot="1">
+      <c r="A6" s="3">
         <v>20014</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="7">
+      <c r="C6" s="4">
         <v>28</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="3">
         <v>20000</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="8">
+      <c r="H6" s="5">
         <v>7584963214</v>
       </c>
-      <c r="L6" s="107">
+      <c r="L6" s="91">
         <v>20015</v>
       </c>
-      <c r="M6" s="108" t="str">
+      <c r="M6" s="92" t="str">
         <f>VLOOKUP(L6,A3:H15,2,0)</f>
         <v>Ali Asgar</v>
       </c>
-      <c r="N6" s="108">
+      <c r="N6" s="92">
         <f>VLOOKUP(L6,A3:H15,3,0)</f>
         <v>27</v>
       </c>
-      <c r="O6" s="108" t="str">
+      <c r="O6" s="92" t="str">
         <f>VLOOKUP(L6,A3:H15,4,0)</f>
         <v>Accountant</v>
       </c>
-      <c r="P6" s="108" t="str">
+      <c r="P6" s="92" t="str">
         <f>VLOOKUP(L6,A3:H15,5,0)</f>
         <v>Finance</v>
       </c>
-      <c r="Q6" s="108">
+      <c r="Q6" s="92">
         <f>VLOOKUP(L6,A3:H15,6,0)</f>
         <v>15000</v>
       </c>
-      <c r="R6" s="108" t="str">
+      <c r="R6" s="92" t="str">
         <f>VLOOKUP(L6,A3:H15,7,0)</f>
         <v>Bhopal</v>
       </c>
-      <c r="S6" s="109">
+      <c r="S6" s="93">
         <f>VLOOKUP(L6,A3:H15,8,0)</f>
         <v>7788994455</v>
       </c>
-      <c r="T6" s="104"/>
-      <c r="U6" s="104"/>
-      <c r="V6" s="104"/>
-      <c r="W6" s="104"/>
-      <c r="X6" s="104"/>
-    </row>
-    <row r="7" spans="1:24" ht="21" customHeight="1" thickBot="1">
-      <c r="A7" s="6">
+    </row>
+    <row r="7" spans="1:19" ht="21" customHeight="1" thickBot="1">
+      <c r="A7" s="3">
         <v>20015</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="7">
+      <c r="C7" s="4">
         <v>27</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="3">
         <v>15000</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="8">
+      <c r="H7" s="5">
         <v>7788994455</v>
       </c>
-      <c r="J7" s="9"/>
-      <c r="L7" s="110" t="s">
+      <c r="J7" s="2"/>
+      <c r="L7" s="94" t="s">
         <v>99</v>
       </c>
-      <c r="M7" s="96">
+      <c r="M7" s="82">
         <f>VLOOKUP(B8,B3:H15,5,0)</f>
         <v>20000</v>
       </c>
-      <c r="N7" s="119"/>
-      <c r="O7" s="119"/>
-      <c r="P7" s="119"/>
-      <c r="Q7" s="119"/>
-      <c r="R7" s="120"/>
-      <c r="S7" s="121"/>
-      <c r="T7" s="104"/>
-      <c r="U7" s="104"/>
-      <c r="V7" s="104"/>
-      <c r="W7" s="104"/>
-      <c r="X7" s="104"/>
-    </row>
-    <row r="8" spans="1:24" ht="21" customHeight="1" thickBot="1">
-      <c r="A8" s="6">
+      <c r="N7" s="98"/>
+      <c r="O7" s="98"/>
+      <c r="P7" s="98"/>
+      <c r="Q7" s="98"/>
+      <c r="R7" s="99"/>
+      <c r="S7" s="100"/>
+    </row>
+    <row r="8" spans="1:19" ht="21" customHeight="1" thickBot="1">
+      <c r="A8" s="3">
         <v>20016</v>
       </c>
-      <c r="B8" s="7" t="s">
+      <c r="B8" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C8" s="7">
+      <c r="C8" s="4">
         <v>25</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="3">
         <v>20000</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="8">
+      <c r="H8" s="5">
         <v>8798654512</v>
       </c>
-      <c r="L8" s="104"/>
-      <c r="M8" s="104"/>
-      <c r="N8" s="104"/>
-      <c r="O8" s="104"/>
-      <c r="P8" s="104"/>
-      <c r="Q8" s="104"/>
-      <c r="R8" s="104"/>
-      <c r="S8" s="104"/>
-      <c r="T8" s="104"/>
-      <c r="U8" s="104"/>
-      <c r="V8" s="104"/>
-      <c r="W8" s="104"/>
-      <c r="X8" s="104"/>
-    </row>
-    <row r="9" spans="1:24" ht="21" customHeight="1">
-      <c r="A9" s="6">
+    </row>
+    <row r="9" spans="1:19" ht="21" customHeight="1">
+      <c r="A9" s="3">
         <v>20017</v>
       </c>
-      <c r="B9" s="7" t="s">
+      <c r="B9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="7">
+      <c r="C9" s="4">
         <v>26</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="3">
         <v>33000</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="8">
+      <c r="H9" s="5">
         <v>9874563214</v>
       </c>
-      <c r="L9" s="98" t="s">
+      <c r="L9" s="84" t="s">
         <v>106</v>
       </c>
-      <c r="M9" s="99"/>
-      <c r="N9" s="99"/>
-      <c r="O9" s="99"/>
-      <c r="P9" s="99"/>
-      <c r="Q9" s="99"/>
-      <c r="R9" s="99"/>
-      <c r="S9" s="100"/>
-      <c r="T9" s="104"/>
-      <c r="U9" s="104"/>
-      <c r="V9" s="104"/>
-      <c r="W9" s="104"/>
-      <c r="X9" s="104"/>
-    </row>
-    <row r="10" spans="1:24" ht="21" customHeight="1">
-      <c r="A10" s="6">
+      <c r="M9" s="85"/>
+      <c r="N9" s="85"/>
+      <c r="O9" s="85"/>
+      <c r="P9" s="85"/>
+      <c r="Q9" s="85"/>
+      <c r="R9" s="85"/>
+      <c r="S9" s="86"/>
+    </row>
+    <row r="10" spans="1:19" ht="21" customHeight="1">
+      <c r="A10" s="3">
         <v>20018</v>
       </c>
-      <c r="B10" s="7" t="s">
+      <c r="B10" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="7">
+      <c r="C10" s="4">
         <v>25</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="3">
         <v>21000</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H10" s="8">
+      <c r="H10" s="5">
         <v>8974563214</v>
       </c>
-      <c r="L10" s="111">
+      <c r="L10" s="56">
         <v>20016</v>
       </c>
-      <c r="M10" s="105" t="str">
+      <c r="M10" s="3" t="str">
         <f t="array" ref="M10:P10">VLOOKUP(A8,A3:H15,{2,4,6,8},0)</f>
         <v>Sunil Singh</v>
       </c>
-      <c r="N10" s="105" t="str">
+      <c r="N10" s="3" t="str">
         <v>Engineer</v>
       </c>
-      <c r="O10" s="105">
+      <c r="O10" s="3">
         <v>20000</v>
       </c>
-      <c r="P10" s="112">
+      <c r="P10" s="5">
         <v>8798654512</v>
       </c>
-      <c r="Q10" s="105"/>
-      <c r="R10" s="105"/>
-      <c r="S10" s="106"/>
-      <c r="T10" s="104"/>
-      <c r="U10" s="104"/>
-      <c r="V10" s="104"/>
-      <c r="W10" s="104"/>
-      <c r="X10" s="104"/>
-    </row>
-    <row r="11" spans="1:24" ht="21" customHeight="1">
-      <c r="A11" s="6">
+      <c r="Q10" s="3"/>
+      <c r="R10" s="3"/>
+      <c r="S10" s="90"/>
+    </row>
+    <row r="11" spans="1:19" ht="21" customHeight="1">
+      <c r="A11" s="3">
         <v>20019</v>
       </c>
-      <c r="B11" s="7" t="s">
+      <c r="B11" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C11" s="7">
+      <c r="C11" s="4">
         <v>26</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="3">
         <v>31500</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H11" s="8">
+      <c r="H11" s="5">
         <v>8745968745</v>
       </c>
-      <c r="L11" s="111">
+      <c r="L11" s="56">
         <v>20017</v>
       </c>
-      <c r="M11" s="105" t="str">
+      <c r="M11" s="3" t="str">
         <f t="array" ref="M11:P11">VLOOKUP(A9,A4:H16,{2,4,6,8},0)</f>
         <v>Mohan Patel</v>
       </c>
-      <c r="N11" s="105" t="str">
+      <c r="N11" s="3" t="str">
         <v>Engineer</v>
       </c>
-      <c r="O11" s="105">
+      <c r="O11" s="3">
         <v>33000</v>
       </c>
-      <c r="P11" s="112">
+      <c r="P11" s="5">
         <v>9874563214</v>
       </c>
-      <c r="Q11" s="113"/>
-      <c r="R11" s="113"/>
-      <c r="S11" s="114"/>
-      <c r="T11" s="104"/>
-      <c r="U11" s="104"/>
-      <c r="V11" s="104"/>
-      <c r="W11" s="104"/>
-      <c r="X11" s="104"/>
-    </row>
-    <row r="12" spans="1:24" ht="21" customHeight="1" thickBot="1">
-      <c r="A12" s="6">
+      <c r="S11" s="55"/>
+    </row>
+    <row r="12" spans="1:19" ht="21" customHeight="1" thickBot="1">
+      <c r="A12" s="3">
         <v>20020</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="7">
+      <c r="C12" s="4">
         <v>28</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="6">
+      <c r="F12" s="3">
         <v>40500</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="8">
+      <c r="H12" s="5">
         <v>9874569874</v>
       </c>
-      <c r="L12" s="115">
+      <c r="L12" s="57">
         <v>20020</v>
       </c>
-      <c r="M12" s="108" t="str">
+      <c r="M12" s="92" t="str">
         <f t="array" ref="M12:P12">VLOOKUP(A10,A5:H17,{2,4,6,8},0)</f>
         <v>Ravi Verma</v>
       </c>
-      <c r="N12" s="108" t="str">
+      <c r="N12" s="92" t="str">
         <v>CAD Designer</v>
       </c>
-      <c r="O12" s="108">
+      <c r="O12" s="92">
         <v>21000</v>
       </c>
-      <c r="P12" s="116">
+      <c r="P12" s="95">
         <v>8974563214</v>
       </c>
-      <c r="Q12" s="108"/>
-      <c r="R12" s="108"/>
-      <c r="S12" s="117"/>
-      <c r="T12" s="104"/>
-      <c r="U12" s="104"/>
-      <c r="V12" s="104"/>
-      <c r="W12" s="104"/>
-      <c r="X12" s="104"/>
-    </row>
-    <row r="13" spans="1:24" ht="21" customHeight="1" thickBot="1">
-      <c r="A13" s="6">
+      <c r="Q12" s="92"/>
+      <c r="R12" s="92"/>
+      <c r="S12" s="96"/>
+    </row>
+    <row r="13" spans="1:19" ht="21" customHeight="1" thickBot="1">
+      <c r="A13" s="3">
         <v>20021</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="C13" s="7">
+      <c r="C13" s="4">
         <v>27</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="E13" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="3">
         <v>25500</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H13" s="8">
+      <c r="H13" s="5">
         <v>8574965874</v>
       </c>
-      <c r="L13" s="104"/>
-      <c r="M13" s="122"/>
-      <c r="N13" s="122"/>
-      <c r="O13" s="122"/>
-      <c r="P13" s="122"/>
-      <c r="Q13" s="122"/>
-      <c r="R13" s="122"/>
-      <c r="S13" s="118"/>
-      <c r="T13" s="104"/>
-      <c r="U13" s="104"/>
-      <c r="V13" s="104"/>
-      <c r="W13" s="104"/>
-      <c r="X13" s="104"/>
-    </row>
-    <row r="14" spans="1:24" ht="21" customHeight="1" thickBot="1">
-      <c r="A14" s="6">
+      <c r="M13" s="101"/>
+      <c r="N13" s="101"/>
+      <c r="O13" s="101"/>
+      <c r="P13" s="101"/>
+      <c r="Q13" s="101"/>
+      <c r="R13" s="101"/>
+      <c r="S13" s="97"/>
+    </row>
+    <row r="14" spans="1:19" ht="21" customHeight="1" thickBot="1">
+      <c r="A14" s="3">
         <v>20022</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="7">
+      <c r="C14" s="4">
         <v>26</v>
       </c>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="E14" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="3">
         <v>18000</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="H14" s="8">
+      <c r="H14" s="5">
         <v>8521479632</v>
       </c>
-      <c r="L14" s="85" t="s">
+      <c r="L14" s="73" t="s">
         <v>100</v>
       </c>
-      <c r="M14" s="123">
+      <c r="M14" s="72">
         <f t="array" ref="M14:R14">VLOOKUP(B12,B3:H15,{2,3,4,5,6,7},0)</f>
         <v>28</v>
       </c>
-      <c r="N14" s="123" t="str">
+      <c r="N14" s="72" t="str">
         <v>Accountant</v>
       </c>
-      <c r="O14" s="123" t="str">
+      <c r="O14" s="72" t="str">
         <v>Finance</v>
       </c>
-      <c r="P14" s="123">
+      <c r="P14" s="72">
         <v>40500</v>
       </c>
-      <c r="Q14" s="123" t="str">
+      <c r="Q14" s="72" t="str">
         <v>Indore</v>
       </c>
-      <c r="R14" s="124">
+      <c r="R14" s="102">
         <v>9874569874</v>
       </c>
     </row>
-    <row r="15" spans="1:24" ht="21" customHeight="1" thickBot="1">
-      <c r="A15" s="6">
+    <row r="15" spans="1:19" ht="21" customHeight="1" thickBot="1">
+      <c r="A15" s="3">
         <v>20023</v>
       </c>
-      <c r="B15" s="7" t="s">
+      <c r="B15" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="7">
+      <c r="C15" s="4">
         <v>27</v>
       </c>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="3">
         <v>21000</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H15" s="8">
+      <c r="H15" s="5">
         <v>8569745623</v>
       </c>
-      <c r="S15" s="6"/>
-    </row>
-    <row r="16" spans="1:24">
-      <c r="L16" s="86" t="s">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19">
+      <c r="L16" s="74" t="s">
         <v>101</v>
       </c>
-      <c r="M16" s="92"/>
-      <c r="N16" s="92"/>
-      <c r="O16" s="93"/>
-      <c r="P16" s="93"/>
-      <c r="Q16" s="93"/>
-      <c r="R16" s="93"/>
-      <c r="S16" s="62"/>
+      <c r="M16" s="78"/>
+      <c r="N16" s="78"/>
+      <c r="O16" s="79"/>
+      <c r="P16" s="79"/>
+      <c r="Q16" s="79"/>
+      <c r="R16" s="79"/>
+      <c r="S16" s="54"/>
     </row>
     <row r="17" spans="12:19" ht="27.75" customHeight="1">
-      <c r="L17" s="64"/>
-      <c r="M17" s="94" t="s">
+      <c r="L17" s="56"/>
+      <c r="M17" s="80" t="s">
         <v>92</v>
       </c>
-      <c r="N17" s="95" t="s">
+      <c r="N17" s="81" t="s">
         <v>2</v>
       </c>
-      <c r="O17" s="30"/>
-      <c r="P17" s="30"/>
-      <c r="Q17" s="30"/>
-      <c r="R17" s="30"/>
-      <c r="S17" s="63"/>
+      <c r="S17" s="55"/>
     </row>
     <row r="18" spans="12:19" ht="36" customHeight="1" thickBot="1">
-      <c r="L18" s="65"/>
-      <c r="M18" s="66">
+      <c r="L18" s="57"/>
+      <c r="M18" s="58">
         <v>20017</v>
       </c>
-      <c r="N18" s="66" t="str">
+      <c r="N18" s="58" t="str">
         <f>VLOOKUP(M18,A3:H15,MATCH(N17,A3:H3,0),0)</f>
         <v>Mohan Patel</v>
       </c>
-      <c r="O18" s="66"/>
-      <c r="P18" s="66"/>
-      <c r="Q18" s="66"/>
-      <c r="R18" s="66"/>
-      <c r="S18" s="68"/>
+      <c r="O18" s="58"/>
+      <c r="P18" s="58"/>
+      <c r="Q18" s="58"/>
+      <c r="R18" s="58"/>
+      <c r="S18" s="60"/>
     </row>
     <row r="19" spans="12:19" ht="14.25" customHeight="1"/>
     <row r="20" spans="12:19" ht="14.25" customHeight="1" thickBot="1"/>
     <row r="21" spans="12:19" ht="36" customHeight="1" thickBot="1">
-      <c r="L21" s="126" t="s">
+      <c r="L21" s="104" t="s">
         <v>102</v>
       </c>
-      <c r="M21" s="84">
+      <c r="M21" s="72">
         <f>MATCH(B3,A3:H3,0)</f>
         <v>2</v>
       </c>
-      <c r="N21" s="125"/>
-      <c r="O21" s="60"/>
-      <c r="P21" s="60"/>
+      <c r="N21" s="103"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Data_analysis_using_excel/Employee_Table.xlsx
+++ b/Data_analysis_using_excel/Employee_Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VISHWAS SHARMA\Documents\Xcel_portfolio\Data_analysis_using_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1DB532B-BD5B-43E0-A709-EB5A3073B11F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21B3050D-4567-43B2-A761-D1812C1A7BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" tabRatio="500" firstSheet="4" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="employee" sheetId="1" r:id="rId1"/>
@@ -18,9 +18,8 @@
     <sheet name="subtotal" sheetId="2" r:id="rId3"/>
     <sheet name="Vlookup(2)" sheetId="4" r:id="rId4"/>
     <sheet name="vlookup(3)" sheetId="5" r:id="rId5"/>
-    <sheet name="approximate_match" sheetId="6" r:id="rId6"/>
-    <sheet name="hlookup(2)" sheetId="7" r:id="rId7"/>
-    <sheet name="Vlookup" sheetId="8" r:id="rId8"/>
+    <sheet name="hlookup(2)" sheetId="7" r:id="rId6"/>
+    <sheet name="Vlookup" sheetId="8" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">subtotal!$A$3:$H$15</definedName>
@@ -286,7 +285,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -308,7 +307,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="496" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="90">
   <si>
     <t>Employee Table</t>
   </si>
@@ -533,57 +532,6 @@
   </si>
   <si>
     <t>Q: Find Age, Department and Mobile No. for an employee given Emp ID, using nested VLOOKUP with IFERROR.</t>
-  </si>
-  <si>
-    <t>Marks</t>
-  </si>
-  <si>
-    <t>Grade</t>
-  </si>
-  <si>
-    <t>Q: Find the Grade for a given Marks value using VLOOKUP with approximate match.</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>Given Marks:</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>Q: Find the sales figure for a given Product and Month using VLOOKUP + MATCH.</t>
-  </si>
-  <si>
-    <t>Mango</t>
-  </si>
-  <si>
-    <t>Jan</t>
-  </si>
-  <si>
-    <t>Product</t>
-  </si>
-  <si>
-    <t>Feb</t>
-  </si>
-  <si>
-    <t>Mar</t>
-  </si>
-  <si>
-    <t>Apple</t>
-  </si>
-  <si>
-    <t>Banana</t>
   </si>
   <si>
     <t>Given Emp ID:</t>
@@ -1387,7 +1335,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="140">
+  <cellXfs count="135">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1426,9 +1374,6 @@
     </xf>
     <xf numFmtId="1" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1506,14 +1451,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="26" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="30" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1622,6 +1559,9 @@
     <xf numFmtId="0" fontId="10" fillId="6" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1660,9 +1600,6 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1949,36 +1886,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="14.25" customHeight="1">
-      <c r="A1" s="130" t="s">
+      <c r="A1" s="126" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="130"/>
-      <c r="C1" s="130"/>
-      <c r="D1" s="130"/>
-      <c r="E1" s="130"/>
-      <c r="F1" s="130"/>
-      <c r="G1" s="130"/>
-      <c r="H1" s="130"/>
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
+      <c r="E1" s="126"/>
+      <c r="F1" s="126"/>
+      <c r="G1" s="126"/>
+      <c r="H1" s="126"/>
     </row>
     <row r="2" spans="1:25" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A2" s="130"/>
-      <c r="B2" s="130"/>
-      <c r="C2" s="130"/>
-      <c r="D2" s="130"/>
-      <c r="E2" s="130"/>
-      <c r="F2" s="130"/>
-      <c r="G2" s="130"/>
-      <c r="H2" s="130"/>
+      <c r="A2" s="126"/>
+      <c r="B2" s="126"/>
+      <c r="C2" s="126"/>
+      <c r="D2" s="126"/>
+      <c r="E2" s="126"/>
+      <c r="F2" s="126"/>
+      <c r="G2" s="126"/>
+      <c r="H2" s="126"/>
       <c r="U2" s="1" t="s">
         <v>35</v>
       </c>
       <c r="V2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="W2" s="129" t="s">
+      <c r="W2" s="125" t="s">
         <v>37</v>
       </c>
-      <c r="X2" s="129"/>
+      <c r="X2" s="125"/>
       <c r="Y2" s="1" t="s">
         <v>38</v>
       </c>
@@ -2008,19 +1945,19 @@
       <c r="H3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="K3" s="131" t="s">
+      <c r="K3" s="127" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="132"/>
-      <c r="M3" s="132"/>
-      <c r="N3" s="132"/>
-      <c r="O3" s="132"/>
-      <c r="P3" s="132"/>
-      <c r="Q3" s="133"/>
+      <c r="L3" s="128"/>
+      <c r="M3" s="128"/>
+      <c r="N3" s="128"/>
+      <c r="O3" s="128"/>
+      <c r="P3" s="128"/>
+      <c r="Q3" s="129"/>
       <c r="U3" s="6">
         <v>1</v>
       </c>
-      <c r="V3" s="120" t="s">
+      <c r="V3" s="115" t="s">
         <v>39</v>
       </c>
       <c r="W3" s="6"/>
@@ -2055,38 +1992,38 @@
       <c r="H4" s="5">
         <v>8877456987</v>
       </c>
-      <c r="K4" s="110" t="str" cm="1">
+      <c r="K4" s="105" t="str" cm="1">
         <f t="array" ref="K4:Q4">_xlfn.XLOOKUP(A4,A3:A15,B3:H15)</f>
         <v>Kapil Sharma</v>
       </c>
-      <c r="L4" s="111">
+      <c r="L4" s="106">
         <v>26</v>
       </c>
-      <c r="M4" s="111" t="str">
+      <c r="M4" s="106" t="str">
         <v>Engineer</v>
       </c>
-      <c r="N4" s="111" t="str">
+      <c r="N4" s="106" t="str">
         <v>Technical</v>
       </c>
-      <c r="O4" s="111">
+      <c r="O4" s="106">
         <v>26500</v>
       </c>
-      <c r="P4" s="111" t="str">
+      <c r="P4" s="106" t="str">
         <v>Indore</v>
       </c>
-      <c r="Q4" s="117">
+      <c r="Q4" s="112">
         <v>8877456987</v>
       </c>
       <c r="U4" s="6">
         <v>2</v>
       </c>
-      <c r="V4" s="120" t="s">
+      <c r="V4" s="115" t="s">
         <v>40</v>
       </c>
-      <c r="W4" s="121">
+      <c r="W4" s="116">
         <v>20012</v>
       </c>
-      <c r="X4" s="121" t="s">
+      <c r="X4" s="116" t="s">
         <v>3</v>
       </c>
       <c r="Y4" s="6">
@@ -2122,7 +2059,7 @@
       <c r="U5" s="6">
         <v>3</v>
       </c>
-      <c r="V5" s="120" t="s">
+      <c r="V5" s="115" t="s">
         <v>41</v>
       </c>
       <c r="W5" s="6"/>
@@ -2160,7 +2097,7 @@
       <c r="U6" s="6">
         <v>4</v>
       </c>
-      <c r="V6" s="120" t="s">
+      <c r="V6" s="115" t="s">
         <v>42</v>
       </c>
       <c r="W6" s="6"/>
@@ -2198,7 +2135,7 @@
       <c r="U7" s="6">
         <v>5</v>
       </c>
-      <c r="V7" s="120" t="s">
+      <c r="V7" s="115" t="s">
         <v>43</v>
       </c>
       <c r="W7" s="6"/>
@@ -2221,10 +2158,10 @@
       <c r="D8" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="20" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="118">
+      <c r="F8" s="113">
         <v>20000</v>
       </c>
       <c r="G8" s="19" t="s">
@@ -2236,7 +2173,7 @@
       <c r="U8" s="6">
         <v>6</v>
       </c>
-      <c r="V8" s="120" t="s">
+      <c r="V8" s="115" t="s">
         <v>44</v>
       </c>
       <c r="W8" s="6"/>
@@ -2274,7 +2211,7 @@
       <c r="U9" s="6">
         <v>7</v>
       </c>
-      <c r="V9" s="120" t="s">
+      <c r="V9" s="115" t="s">
         <v>45</v>
       </c>
       <c r="W9" s="6"/>
@@ -2312,7 +2249,7 @@
       <c r="U10" s="6">
         <v>8</v>
       </c>
-      <c r="V10" s="120" t="s">
+      <c r="V10" s="115" t="s">
         <v>46</v>
       </c>
       <c r="W10" s="6"/>
@@ -2347,19 +2284,19 @@
       <c r="H11" s="5">
         <v>8745968745</v>
       </c>
-      <c r="K11" s="113" t="s">
+      <c r="K11" s="108" t="s">
         <v>25</v>
       </c>
-      <c r="L11" s="114"/>
-      <c r="M11" s="114"/>
-      <c r="N11" s="114"/>
-      <c r="O11" s="114"/>
-      <c r="P11" s="114"/>
-      <c r="Q11" s="25"/>
+      <c r="L11" s="109"/>
+      <c r="M11" s="109"/>
+      <c r="N11" s="109"/>
+      <c r="O11" s="109"/>
+      <c r="P11" s="109"/>
+      <c r="Q11" s="24"/>
       <c r="U11" s="6">
         <v>9</v>
       </c>
-      <c r="V11" s="120" t="s">
+      <c r="V11" s="115" t="s">
         <v>47</v>
       </c>
       <c r="W11" s="6"/>
@@ -2394,23 +2331,23 @@
       <c r="H12" s="5">
         <v>9874569874</v>
       </c>
-      <c r="K12" s="56"/>
-      <c r="L12" s="122" t="str">
+      <c r="K12" s="55"/>
+      <c r="L12" s="117" t="str">
         <f t="array" ref="L12:N24">CHOOSE({1,2,3},F3:F15,C3:C15,A3:A15)</f>
         <v>Salary</v>
       </c>
-      <c r="M12" s="123" t="str">
+      <c r="M12" s="118" t="str">
         <v>Age</v>
       </c>
-      <c r="N12" s="123" t="str">
+      <c r="N12" s="118" t="str">
         <v>Emp. ID</v>
       </c>
-      <c r="O12" s="124"/>
-      <c r="P12" s="125"/>
+      <c r="O12" s="119"/>
+      <c r="P12" s="120"/>
       <c r="U12" s="6">
         <v>10</v>
       </c>
-      <c r="V12" s="120" t="s">
+      <c r="V12" s="115" t="s">
         <v>48</v>
       </c>
       <c r="W12" s="6"/>
@@ -2445,22 +2382,22 @@
       <c r="H13" s="5">
         <v>8574965874</v>
       </c>
-      <c r="K13" s="56"/>
-      <c r="L13" s="107">
+      <c r="K13" s="55"/>
+      <c r="L13" s="102">
         <v>26500</v>
       </c>
-      <c r="M13" s="108">
+      <c r="M13" s="103">
         <v>26</v>
       </c>
-      <c r="N13" s="108">
+      <c r="N13" s="103">
         <v>20012</v>
       </c>
-      <c r="O13" s="108"/>
-      <c r="P13" s="109"/>
+      <c r="O13" s="103"/>
+      <c r="P13" s="104"/>
       <c r="U13" s="6">
         <v>11</v>
       </c>
-      <c r="V13" s="120" t="s">
+      <c r="V13" s="115" t="s">
         <v>49</v>
       </c>
       <c r="W13" s="6"/>
@@ -2495,22 +2432,22 @@
       <c r="H14" s="5">
         <v>8521479632</v>
       </c>
-      <c r="K14" s="56"/>
-      <c r="L14" s="107">
+      <c r="K14" s="55"/>
+      <c r="L14" s="102">
         <v>13000</v>
       </c>
-      <c r="M14" s="108">
+      <c r="M14" s="103">
         <v>25</v>
       </c>
-      <c r="N14" s="108">
+      <c r="N14" s="103">
         <v>20013</v>
       </c>
-      <c r="O14" s="108"/>
-      <c r="P14" s="109"/>
+      <c r="O14" s="103"/>
+      <c r="P14" s="104"/>
       <c r="U14" s="6">
         <v>12</v>
       </c>
-      <c r="V14" s="120" t="s">
+      <c r="V14" s="115" t="s">
         <v>50</v>
       </c>
       <c r="W14" s="6"/>
@@ -2545,25 +2482,25 @@
       <c r="H15" s="5">
         <v>8569745623</v>
       </c>
-      <c r="K15" s="56"/>
-      <c r="L15" s="107">
+      <c r="K15" s="55"/>
+      <c r="L15" s="102">
         <v>20000</v>
       </c>
-      <c r="M15" s="108">
+      <c r="M15" s="103">
         <v>28</v>
       </c>
-      <c r="N15" s="108">
+      <c r="N15" s="103">
         <v>20014</v>
       </c>
-      <c r="O15" s="108"/>
-      <c r="P15" s="109"/>
+      <c r="O15" s="103"/>
+      <c r="P15" s="104"/>
       <c r="U15" s="6">
         <v>13</v>
       </c>
-      <c r="V15" s="120" t="s">
+      <c r="V15" s="115" t="s">
         <v>51</v>
       </c>
-      <c r="W15" s="121">
+      <c r="W15" s="116">
         <v>40500</v>
       </c>
       <c r="X15" s="6"/>
@@ -2573,22 +2510,22 @@
       </c>
     </row>
     <row r="16" spans="1:25" ht="14.25" customHeight="1">
-      <c r="K16" s="56"/>
-      <c r="L16" s="107">
+      <c r="K16" s="55"/>
+      <c r="L16" s="102">
         <v>15000</v>
       </c>
-      <c r="M16" s="108">
+      <c r="M16" s="103">
         <v>27</v>
       </c>
-      <c r="N16" s="108">
+      <c r="N16" s="103">
         <v>20015</v>
       </c>
-      <c r="O16" s="108"/>
-      <c r="P16" s="109"/>
+      <c r="O16" s="103"/>
+      <c r="P16" s="104"/>
       <c r="U16" s="6">
         <v>14</v>
       </c>
-      <c r="V16" s="120" t="s">
+      <c r="V16" s="115" t="s">
         <v>52</v>
       </c>
       <c r="W16" s="6"/>
@@ -2599,22 +2536,22 @@
       </c>
     </row>
     <row r="17" spans="2:25" ht="14.25" customHeight="1">
-      <c r="K17" s="56"/>
-      <c r="L17" s="107">
+      <c r="K17" s="55"/>
+      <c r="L17" s="102">
         <v>20000</v>
       </c>
-      <c r="M17" s="108">
+      <c r="M17" s="103">
         <v>25</v>
       </c>
-      <c r="N17" s="108">
+      <c r="N17" s="103">
         <v>20016</v>
       </c>
-      <c r="O17" s="108"/>
-      <c r="P17" s="109"/>
+      <c r="O17" s="103"/>
+      <c r="P17" s="104"/>
       <c r="U17" s="6">
         <v>15</v>
       </c>
-      <c r="V17" s="120" t="s">
+      <c r="V17" s="115" t="s">
         <v>53</v>
       </c>
       <c r="W17" s="6"/>
@@ -2625,115 +2562,115 @@
       </c>
     </row>
     <row r="18" spans="2:25" ht="14.25" customHeight="1">
-      <c r="K18" s="56"/>
-      <c r="L18" s="107">
+      <c r="K18" s="55"/>
+      <c r="L18" s="102">
         <v>33000</v>
       </c>
-      <c r="M18" s="108">
+      <c r="M18" s="103">
         <v>26</v>
       </c>
-      <c r="N18" s="108">
+      <c r="N18" s="103">
         <v>20017</v>
       </c>
-      <c r="O18" s="108"/>
-      <c r="P18" s="109"/>
+      <c r="O18" s="103"/>
+      <c r="P18" s="104"/>
     </row>
     <row r="19" spans="2:25" ht="14.25" customHeight="1">
-      <c r="K19" s="56"/>
-      <c r="L19" s="107">
+      <c r="K19" s="55"/>
+      <c r="L19" s="102">
         <v>21000</v>
       </c>
-      <c r="M19" s="108">
+      <c r="M19" s="103">
         <v>25</v>
       </c>
-      <c r="N19" s="108">
+      <c r="N19" s="103">
         <v>20018</v>
       </c>
-      <c r="O19" s="108"/>
-      <c r="P19" s="109"/>
+      <c r="O19" s="103"/>
+      <c r="P19" s="104"/>
     </row>
     <row r="20" spans="2:25" ht="14.25" customHeight="1">
-      <c r="K20" s="56"/>
-      <c r="L20" s="107">
+      <c r="K20" s="55"/>
+      <c r="L20" s="102">
         <v>31500</v>
       </c>
-      <c r="M20" s="108">
+      <c r="M20" s="103">
         <v>26</v>
       </c>
-      <c r="N20" s="108">
+      <c r="N20" s="103">
         <v>20019</v>
       </c>
-      <c r="O20" s="108"/>
-      <c r="P20" s="109"/>
+      <c r="O20" s="103"/>
+      <c r="P20" s="104"/>
     </row>
     <row r="21" spans="2:25" ht="21" customHeight="1">
-      <c r="K21" s="56"/>
-      <c r="L21" s="107">
+      <c r="K21" s="55"/>
+      <c r="L21" s="102">
         <v>40500</v>
       </c>
-      <c r="M21" s="108">
+      <c r="M21" s="103">
         <v>28</v>
       </c>
-      <c r="N21" s="108">
+      <c r="N21" s="103">
         <v>20020</v>
       </c>
-      <c r="O21" s="108"/>
-      <c r="P21" s="109"/>
+      <c r="O21" s="103"/>
+      <c r="P21" s="104"/>
     </row>
     <row r="22" spans="2:25" ht="14.25" customHeight="1">
-      <c r="K22" s="56"/>
-      <c r="L22" s="107">
+      <c r="K22" s="55"/>
+      <c r="L22" s="102">
         <v>25500</v>
       </c>
-      <c r="M22" s="108">
+      <c r="M22" s="103">
         <v>27</v>
       </c>
-      <c r="N22" s="108">
+      <c r="N22" s="103">
         <v>20021</v>
       </c>
-      <c r="O22" s="108"/>
-      <c r="P22" s="109"/>
+      <c r="O22" s="103"/>
+      <c r="P22" s="104"/>
     </row>
     <row r="23" spans="2:25" ht="14.25" customHeight="1" thickBot="1">
-      <c r="K23" s="56"/>
-      <c r="L23" s="107">
+      <c r="K23" s="55"/>
+      <c r="L23" s="102">
         <v>18000</v>
       </c>
-      <c r="M23" s="108">
+      <c r="M23" s="103">
         <v>26</v>
       </c>
-      <c r="N23" s="108">
+      <c r="N23" s="103">
         <v>20022</v>
       </c>
-      <c r="O23" s="108"/>
-      <c r="P23" s="109"/>
+      <c r="O23" s="103"/>
+      <c r="P23" s="104"/>
     </row>
     <row r="24" spans="2:25" ht="21" customHeight="1" thickBot="1">
-      <c r="B24" s="126" t="s">
+      <c r="B24" s="122" t="s">
         <v>31</v>
       </c>
-      <c r="C24" s="127"/>
-      <c r="D24" s="127"/>
-      <c r="E24" s="127"/>
-      <c r="F24" s="127"/>
-      <c r="G24" s="127"/>
-      <c r="H24" s="127"/>
-      <c r="I24" s="128"/>
-      <c r="K24" s="57"/>
-      <c r="L24" s="110">
+      <c r="C24" s="123"/>
+      <c r="D24" s="123"/>
+      <c r="E24" s="123"/>
+      <c r="F24" s="123"/>
+      <c r="G24" s="123"/>
+      <c r="H24" s="123"/>
+      <c r="I24" s="124"/>
+      <c r="K24" s="56"/>
+      <c r="L24" s="105">
         <v>21000</v>
       </c>
-      <c r="M24" s="111">
+      <c r="M24" s="106">
         <v>27</v>
       </c>
-      <c r="N24" s="111">
+      <c r="N24" s="106">
         <v>20023</v>
       </c>
-      <c r="O24" s="111"/>
-      <c r="P24" s="112"/>
+      <c r="O24" s="106"/>
+      <c r="P24" s="107"/>
     </row>
     <row r="25" spans="2:25" ht="14.25" customHeight="1">
-      <c r="B25" s="56" t="str">
+      <c r="B25" s="55" t="str">
         <f t="array" ref="B25:I34">_xlfn._xlws.FILTER(A3:H15,C3:C15&gt;25)</f>
         <v>Emp. ID</v>
       </c>
@@ -2755,12 +2692,12 @@
       <c r="H25" t="str">
         <v>Place</v>
       </c>
-      <c r="I25" s="55" t="str">
+      <c r="I25" s="54" t="str">
         <v>Mob.No.</v>
       </c>
     </row>
     <row r="26" spans="2:25" ht="14.25" customHeight="1">
-      <c r="B26" s="56">
+      <c r="B26" s="55">
         <v>20012</v>
       </c>
       <c r="C26" t="str">
@@ -2781,12 +2718,12 @@
       <c r="H26" t="str">
         <v>Indore</v>
       </c>
-      <c r="I26" s="119">
+      <c r="I26" s="114">
         <v>8877456987</v>
       </c>
     </row>
     <row r="27" spans="2:25" ht="14.25" customHeight="1">
-      <c r="B27" s="56">
+      <c r="B27" s="55">
         <v>20014</v>
       </c>
       <c r="C27" t="str">
@@ -2807,12 +2744,12 @@
       <c r="H27" t="str">
         <v>Indore</v>
       </c>
-      <c r="I27" s="119">
+      <c r="I27" s="114">
         <v>7584963214</v>
       </c>
     </row>
     <row r="28" spans="2:25" ht="14.25" customHeight="1">
-      <c r="B28" s="56">
+      <c r="B28" s="55">
         <v>20015</v>
       </c>
       <c r="C28" t="str">
@@ -2833,12 +2770,12 @@
       <c r="H28" t="str">
         <v>Bhopal</v>
       </c>
-      <c r="I28" s="119">
+      <c r="I28" s="114">
         <v>7788994455</v>
       </c>
     </row>
     <row r="29" spans="2:25" ht="14.25" customHeight="1">
-      <c r="B29" s="56">
+      <c r="B29" s="55">
         <v>20017</v>
       </c>
       <c r="C29" t="str">
@@ -2859,12 +2796,12 @@
       <c r="H29" t="str">
         <v>Bhopal</v>
       </c>
-      <c r="I29" s="119">
+      <c r="I29" s="114">
         <v>9874563214</v>
       </c>
     </row>
     <row r="30" spans="2:25" ht="14.25" customHeight="1">
-      <c r="B30" s="56">
+      <c r="B30" s="55">
         <v>20019</v>
       </c>
       <c r="C30" t="str">
@@ -2885,12 +2822,12 @@
       <c r="H30" t="str">
         <v>Bhopal</v>
       </c>
-      <c r="I30" s="119">
+      <c r="I30" s="114">
         <v>8745968745</v>
       </c>
     </row>
     <row r="31" spans="2:25" ht="14.25" customHeight="1">
-      <c r="B31" s="56">
+      <c r="B31" s="55">
         <v>20020</v>
       </c>
       <c r="C31" t="str">
@@ -2911,12 +2848,12 @@
       <c r="H31" t="str">
         <v>Indore</v>
       </c>
-      <c r="I31" s="119">
+      <c r="I31" s="114">
         <v>9874569874</v>
       </c>
     </row>
     <row r="32" spans="2:25" ht="14.25" customHeight="1">
-      <c r="B32" s="56">
+      <c r="B32" s="55">
         <v>20021</v>
       </c>
       <c r="C32" t="str">
@@ -2937,12 +2874,12 @@
       <c r="H32" t="str">
         <v>ujjain</v>
       </c>
-      <c r="I32" s="119">
+      <c r="I32" s="114">
         <v>8574965874</v>
       </c>
     </row>
     <row r="33" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B33" s="56">
+      <c r="B33" s="55">
         <v>20022</v>
       </c>
       <c r="C33" t="str">
@@ -2963,50 +2900,50 @@
       <c r="H33" t="str">
         <v>ujjain</v>
       </c>
-      <c r="I33" s="119">
+      <c r="I33" s="114">
         <v>8521479632</v>
       </c>
     </row>
     <row r="34" spans="2:9" ht="14.25" customHeight="1" thickBot="1">
-      <c r="B34" s="57">
+      <c r="B34" s="56">
         <v>20023</v>
       </c>
-      <c r="C34" s="58" t="str">
+      <c r="C34" s="57" t="str">
         <v>Janwi Rai</v>
       </c>
-      <c r="D34" s="58">
+      <c r="D34" s="57">
         <v>27</v>
       </c>
-      <c r="E34" s="58" t="str">
+      <c r="E34" s="57" t="str">
         <v>CAD Designer</v>
       </c>
-      <c r="F34" s="58" t="str">
+      <c r="F34" s="57" t="str">
         <v>Technical</v>
       </c>
-      <c r="G34" s="58">
+      <c r="G34" s="57">
         <v>21000</v>
       </c>
-      <c r="H34" s="58" t="str">
+      <c r="H34" s="57" t="str">
         <v>Indore</v>
       </c>
-      <c r="I34" s="59">
+      <c r="I34" s="58">
         <v>8569745623</v>
       </c>
     </row>
     <row r="35" spans="2:9" ht="21" customHeight="1">
-      <c r="B35" s="126" t="s">
+      <c r="B35" s="122" t="s">
         <v>32</v>
       </c>
-      <c r="C35" s="127"/>
-      <c r="D35" s="127"/>
-      <c r="E35" s="127"/>
-      <c r="F35" s="127"/>
-      <c r="G35" s="127"/>
-      <c r="H35" s="127"/>
-      <c r="I35" s="128"/>
+      <c r="C35" s="123"/>
+      <c r="D35" s="123"/>
+      <c r="E35" s="123"/>
+      <c r="F35" s="123"/>
+      <c r="G35" s="123"/>
+      <c r="H35" s="123"/>
+      <c r="I35" s="124"/>
     </row>
     <row r="36" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B36" s="56">
+      <c r="B36" s="55">
         <f t="array" ref="B36:I42">_xlfn._xlws.FILTER(A3:H15,E3:E15="Technical")</f>
         <v>20012</v>
       </c>
@@ -3028,12 +2965,12 @@
       <c r="H36" t="str">
         <v>Indore</v>
       </c>
-      <c r="I36" s="119">
+      <c r="I36" s="114">
         <v>8877456987</v>
       </c>
     </row>
     <row r="37" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B37" s="56">
+      <c r="B37" s="55">
         <v>20014</v>
       </c>
       <c r="C37" t="str">
@@ -3054,12 +2991,12 @@
       <c r="H37" t="str">
         <v>Indore</v>
       </c>
-      <c r="I37" s="119">
+      <c r="I37" s="114">
         <v>7584963214</v>
       </c>
     </row>
     <row r="38" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B38" s="56">
+      <c r="B38" s="55">
         <v>20016</v>
       </c>
       <c r="C38" t="str">
@@ -3080,12 +3017,12 @@
       <c r="H38" t="str">
         <v>ujjain</v>
       </c>
-      <c r="I38" s="119">
+      <c r="I38" s="114">
         <v>8798654512</v>
       </c>
     </row>
     <row r="39" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B39" s="56">
+      <c r="B39" s="55">
         <v>20017</v>
       </c>
       <c r="C39" t="str">
@@ -3106,12 +3043,12 @@
       <c r="H39" t="str">
         <v>Bhopal</v>
       </c>
-      <c r="I39" s="119">
+      <c r="I39" s="114">
         <v>9874563214</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B40" s="56">
+      <c r="B40" s="55">
         <v>20018</v>
       </c>
       <c r="C40" t="str">
@@ -3132,12 +3069,12 @@
       <c r="H40" t="str">
         <v>Indore</v>
       </c>
-      <c r="I40" s="119">
+      <c r="I40" s="114">
         <v>8974563214</v>
       </c>
     </row>
     <row r="41" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B41" s="56">
+      <c r="B41" s="55">
         <v>20021</v>
       </c>
       <c r="C41" t="str">
@@ -3158,50 +3095,50 @@
       <c r="H41" t="str">
         <v>ujjain</v>
       </c>
-      <c r="I41" s="119">
+      <c r="I41" s="114">
         <v>8574965874</v>
       </c>
     </row>
     <row r="42" spans="2:9" ht="14.25" customHeight="1" thickBot="1">
-      <c r="B42" s="57">
+      <c r="B42" s="56">
         <v>20023</v>
       </c>
-      <c r="C42" s="58" t="str">
+      <c r="C42" s="57" t="str">
         <v>Janwi Rai</v>
       </c>
-      <c r="D42" s="58">
+      <c r="D42" s="57">
         <v>27</v>
       </c>
-      <c r="E42" s="58" t="str">
+      <c r="E42" s="57" t="str">
         <v>CAD Designer</v>
       </c>
-      <c r="F42" s="58" t="str">
+      <c r="F42" s="57" t="str">
         <v>Technical</v>
       </c>
-      <c r="G42" s="58">
+      <c r="G42" s="57">
         <v>21000</v>
       </c>
-      <c r="H42" s="58" t="str">
+      <c r="H42" s="57" t="str">
         <v>Indore</v>
       </c>
-      <c r="I42" s="59">
+      <c r="I42" s="58">
         <v>8569745623</v>
       </c>
     </row>
     <row r="43" spans="2:9" ht="21" customHeight="1">
-      <c r="B43" s="126" t="s">
+      <c r="B43" s="122" t="s">
         <v>33</v>
       </c>
-      <c r="C43" s="127"/>
-      <c r="D43" s="127"/>
-      <c r="E43" s="127"/>
-      <c r="F43" s="127"/>
-      <c r="G43" s="127"/>
-      <c r="H43" s="127"/>
-      <c r="I43" s="128"/>
+      <c r="C43" s="123"/>
+      <c r="D43" s="123"/>
+      <c r="E43" s="123"/>
+      <c r="F43" s="123"/>
+      <c r="G43" s="123"/>
+      <c r="H43" s="123"/>
+      <c r="I43" s="124"/>
     </row>
     <row r="44" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B44" s="56">
+      <c r="B44" s="55">
         <f t="array" ref="B44:I47">_xlfn._xlws.FILTER(A3:H15,G3:G15="Bhopal")</f>
         <v>20013</v>
       </c>
@@ -3223,12 +3160,12 @@
       <c r="H44" t="str">
         <v>Bhopal</v>
       </c>
-      <c r="I44" s="119">
+      <c r="I44" s="114">
         <v>8569741235</v>
       </c>
     </row>
     <row r="45" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B45" s="56">
+      <c r="B45" s="55">
         <v>20015</v>
       </c>
       <c r="C45" t="str">
@@ -3249,12 +3186,12 @@
       <c r="H45" t="str">
         <v>Bhopal</v>
       </c>
-      <c r="I45" s="119">
+      <c r="I45" s="114">
         <v>7788994455</v>
       </c>
     </row>
     <row r="46" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B46" s="56">
+      <c r="B46" s="55">
         <v>20017</v>
       </c>
       <c r="C46" t="str">
@@ -3275,50 +3212,50 @@
       <c r="H46" t="str">
         <v>Bhopal</v>
       </c>
-      <c r="I46" s="119">
+      <c r="I46" s="114">
         <v>9874563214</v>
       </c>
     </row>
     <row r="47" spans="2:9" ht="14.25" customHeight="1" thickBot="1">
-      <c r="B47" s="57">
+      <c r="B47" s="56">
         <v>20019</v>
       </c>
-      <c r="C47" s="58" t="str">
+      <c r="C47" s="57" t="str">
         <v>Deepak Singh</v>
       </c>
-      <c r="D47" s="58">
+      <c r="D47" s="57">
         <v>26</v>
       </c>
-      <c r="E47" s="58" t="str">
+      <c r="E47" s="57" t="str">
         <v>Accountant</v>
       </c>
-      <c r="F47" s="58" t="str">
+      <c r="F47" s="57" t="str">
         <v>Finance</v>
       </c>
-      <c r="G47" s="58">
+      <c r="G47" s="57">
         <v>31500</v>
       </c>
-      <c r="H47" s="58" t="str">
+      <c r="H47" s="57" t="str">
         <v>Bhopal</v>
       </c>
-      <c r="I47" s="59">
+      <c r="I47" s="58">
         <v>8745968745</v>
       </c>
     </row>
     <row r="48" spans="2:9" ht="21" customHeight="1">
-      <c r="B48" s="126" t="s">
+      <c r="B48" s="122" t="s">
         <v>34</v>
       </c>
-      <c r="C48" s="127"/>
-      <c r="D48" s="127"/>
-      <c r="E48" s="127"/>
-      <c r="F48" s="127"/>
-      <c r="G48" s="127"/>
-      <c r="H48" s="127"/>
-      <c r="I48" s="128"/>
+      <c r="C48" s="123"/>
+      <c r="D48" s="123"/>
+      <c r="E48" s="123"/>
+      <c r="F48" s="123"/>
+      <c r="G48" s="123"/>
+      <c r="H48" s="123"/>
+      <c r="I48" s="124"/>
     </row>
     <row r="49" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B49" s="56" t="str">
+      <c r="B49" s="55" t="str">
         <f t="array" ref="B49:I52">_xlfn._xlws.FILTER(A3:H15,F3:F15&gt;30000)</f>
         <v>Emp. ID</v>
       </c>
@@ -3340,12 +3277,12 @@
       <c r="H49" t="str">
         <v>Place</v>
       </c>
-      <c r="I49" s="55" t="str">
+      <c r="I49" s="54" t="str">
         <v>Mob.No.</v>
       </c>
     </row>
     <row r="50" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B50" s="56">
+      <c r="B50" s="55">
         <v>20017</v>
       </c>
       <c r="C50" t="str">
@@ -3366,12 +3303,12 @@
       <c r="H50" t="str">
         <v>Bhopal</v>
       </c>
-      <c r="I50" s="119">
+      <c r="I50" s="114">
         <v>9874563214</v>
       </c>
     </row>
     <row r="51" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B51" s="56">
+      <c r="B51" s="55">
         <v>20019</v>
       </c>
       <c r="C51" t="str">
@@ -3392,33 +3329,33 @@
       <c r="H51" t="str">
         <v>Bhopal</v>
       </c>
-      <c r="I51" s="119">
+      <c r="I51" s="114">
         <v>8745968745</v>
       </c>
     </row>
     <row r="52" spans="2:9" ht="14.25" customHeight="1" thickBot="1">
-      <c r="B52" s="57">
+      <c r="B52" s="56">
         <v>20020</v>
       </c>
-      <c r="C52" s="58" t="str">
+      <c r="C52" s="57" t="str">
         <v>Vikas Patel</v>
       </c>
-      <c r="D52" s="58">
+      <c r="D52" s="57">
         <v>28</v>
       </c>
-      <c r="E52" s="58" t="str">
+      <c r="E52" s="57" t="str">
         <v>Accountant</v>
       </c>
-      <c r="F52" s="58" t="str">
+      <c r="F52" s="57" t="str">
         <v>Finance</v>
       </c>
-      <c r="G52" s="58">
+      <c r="G52" s="57">
         <v>40500</v>
       </c>
-      <c r="H52" s="58" t="str">
+      <c r="H52" s="57" t="str">
         <v>Indore</v>
       </c>
-      <c r="I52" s="59">
+      <c r="I52" s="58">
         <v>9874569874</v>
       </c>
     </row>
@@ -3476,89 +3413,89 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="41.25" customHeight="1">
-      <c r="B1" s="64" t="s">
-        <v>103</v>
-      </c>
-      <c r="C1" s="54">
+      <c r="B1" s="63" t="s">
+        <v>86</v>
+      </c>
+      <c r="C1" s="53">
         <f>VLOOKUP(B2,employee!A3:H15,6,0)</f>
         <v>20000</v>
       </c>
       <c r="D1" s="12"/>
     </row>
     <row r="2" spans="2:10" ht="14.25" customHeight="1" thickBot="1">
-      <c r="B2" s="65">
+      <c r="B2" s="64">
         <v>20016</v>
       </c>
-      <c r="C2" s="105"/>
+      <c r="C2" s="100"/>
     </row>
     <row r="3" spans="2:10" ht="27.75" customHeight="1">
-      <c r="B3" s="64" t="s">
-        <v>104</v>
-      </c>
-      <c r="C3" s="79" t="str">
+      <c r="B3" s="63" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" s="74" t="str">
         <f t="array" ref="C3:I3">VLOOKUP(B4,Vlookup!A3:H15,{2,3,4,5,6,7,8},0)</f>
         <v>Sunil Grover</v>
       </c>
-      <c r="D3" s="79">
+      <c r="D3" s="74">
         <v>25</v>
       </c>
-      <c r="E3" s="79" t="str">
+      <c r="E3" s="74" t="str">
         <v>Accountant</v>
       </c>
-      <c r="F3" s="79" t="str">
+      <c r="F3" s="74" t="str">
         <v>Finance</v>
       </c>
-      <c r="G3" s="79">
+      <c r="G3" s="74">
         <v>13000</v>
       </c>
-      <c r="H3" s="79" t="str">
+      <c r="H3" s="74" t="str">
         <v>Bhopal</v>
       </c>
-      <c r="I3" s="106">
+      <c r="I3" s="101">
         <v>8569741235</v>
       </c>
       <c r="J3" s="12"/>
     </row>
     <row r="4" spans="2:10" ht="14.25" customHeight="1">
-      <c r="B4" s="65">
+      <c r="B4" s="64">
         <v>20013</v>
       </c>
-      <c r="I4" s="55"/>
+      <c r="I4" s="54"/>
     </row>
     <row r="5" spans="2:10" ht="14.25" customHeight="1" thickBot="1">
-      <c r="B5" s="57"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="60"/>
+      <c r="B5" s="56"/>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="59"/>
     </row>
     <row r="6" spans="2:10" ht="14.25" customHeight="1">
-      <c r="B6" s="115" t="s">
-        <v>105</v>
-      </c>
-      <c r="C6" s="55">
+      <c r="B6" s="110" t="s">
+        <v>88</v>
+      </c>
+      <c r="C6" s="54">
         <f>VLOOKUP(B7,Vlookup!B3:H15,MATCH(' hlookup(employee_table)'!B8,Vlookup!B3:H3,0),0)</f>
         <v>25500</v>
       </c>
     </row>
     <row r="7" spans="2:10">
-      <c r="B7" s="65" t="s">
+      <c r="B7" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="55"/>
+      <c r="C7" s="54"/>
     </row>
     <row r="8" spans="2:10">
-      <c r="B8" s="116" t="s">
+      <c r="B8" s="111" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="55"/>
+      <c r="C8" s="54"/>
     </row>
     <row r="9" spans="2:10" ht="15" thickBot="1">
-      <c r="B9" s="57"/>
-      <c r="C9" s="60"/>
+      <c r="B9" s="56"/>
+      <c r="C9" s="59"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -3577,16 +3514,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="14.25" customHeight="1">
-      <c r="A1" s="129" t="s">
+      <c r="A1" s="125" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="129"/>
-      <c r="C1" s="129"/>
-      <c r="D1" s="129"/>
-      <c r="E1" s="129"/>
-      <c r="F1" s="129"/>
-      <c r="G1" s="129"/>
-      <c r="H1" s="129"/>
+      <c r="B1" s="125"/>
+      <c r="C1" s="125"/>
+      <c r="D1" s="125"/>
+      <c r="E1" s="125"/>
+      <c r="F1" s="125"/>
+      <c r="G1" s="125"/>
+      <c r="H1" s="125"/>
       <c r="J1" s="1" t="s">
         <v>36</v>
       </c>
@@ -3595,14 +3532,14 @@
       </c>
     </row>
     <row r="2" spans="1:11" ht="14.25" customHeight="1">
-      <c r="A2" s="129"/>
-      <c r="B2" s="129"/>
-      <c r="C2" s="129"/>
-      <c r="D2" s="129"/>
-      <c r="E2" s="129"/>
-      <c r="F2" s="129"/>
-      <c r="G2" s="129"/>
-      <c r="H2" s="129"/>
+      <c r="A2" s="125"/>
+      <c r="B2" s="125"/>
+      <c r="C2" s="125"/>
+      <c r="D2" s="125"/>
+      <c r="E2" s="125"/>
+      <c r="F2" s="125"/>
+      <c r="G2" s="125"/>
+      <c r="H2" s="125"/>
       <c r="J2" s="9" t="s">
         <v>60</v>
       </c>
@@ -4028,619 +3965,619 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:26" ht="23.25" customHeight="1">
-      <c r="B3" s="41" t="s">
+      <c r="B3" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="41" t="s">
+      <c r="C3" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="41" t="s">
+      <c r="D3" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="41" t="s">
+      <c r="F3" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="41" t="s">
+      <c r="G3" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="41" t="s">
+      <c r="H3" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="I3" s="45"/>
-      <c r="J3" s="22"/>
-      <c r="K3" s="41" t="s">
+      <c r="I3" s="44"/>
+      <c r="J3" s="21"/>
+      <c r="K3" s="40" t="s">
         <v>2</v>
       </c>
-      <c r="L3" s="41" t="s">
+      <c r="L3" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="M3" s="41" t="s">
+      <c r="M3" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="N3" s="41" t="s">
+      <c r="N3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="O3" s="41" t="s">
+      <c r="O3" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="P3" s="41" t="s">
+      <c r="P3" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="Q3" s="41" t="s">
+      <c r="Q3" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="T3" s="52" t="s">
+      <c r="T3" s="51" t="s">
         <v>66</v>
       </c>
-      <c r="U3" s="47"/>
-      <c r="V3" s="32">
+      <c r="U3" s="46"/>
+      <c r="V3" s="31">
         <f>VLOOKUP(B7,CHOOSE({1,2},B3:B15,L3:L15),2,0)</f>
         <v>27</v>
       </c>
-      <c r="W3" s="23"/>
-      <c r="X3" s="23"/>
-      <c r="Y3" s="23"/>
-      <c r="Z3" s="24"/>
+      <c r="W3" s="22"/>
+      <c r="X3" s="22"/>
+      <c r="Y3" s="22"/>
+      <c r="Z3" s="23"/>
     </row>
     <row r="4" spans="2:26" ht="21" customHeight="1">
-      <c r="B4" s="43">
+      <c r="B4" s="42">
         <v>20012</v>
       </c>
-      <c r="C4" s="42" t="s">
+      <c r="C4" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="D4" s="43" t="s">
+      <c r="D4" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="43" t="s">
+      <c r="E4" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="F4" s="43">
+      <c r="F4" s="42">
         <v>26500</v>
       </c>
-      <c r="G4" s="43" t="s">
+      <c r="G4" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="H4" s="44">
+      <c r="H4" s="43">
         <v>8877456987</v>
       </c>
       <c r="I4" s="19"/>
-      <c r="J4" s="21"/>
-      <c r="K4" s="42" t="s">
+      <c r="J4" s="20"/>
+      <c r="K4" s="41" t="s">
         <v>9</v>
       </c>
-      <c r="L4" s="42">
+      <c r="L4" s="41">
         <v>26</v>
       </c>
-      <c r="M4" s="43" t="s">
+      <c r="M4" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="43" t="s">
+      <c r="N4" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="O4" s="43">
+      <c r="O4" s="42">
         <v>26500</v>
       </c>
-      <c r="P4" s="43" t="s">
+      <c r="P4" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="Q4" s="44">
+      <c r="Q4" s="43">
         <v>8877456987</v>
       </c>
-      <c r="T4" s="27"/>
-      <c r="U4" s="28"/>
-      <c r="V4" s="28"/>
-      <c r="W4" s="28"/>
-      <c r="X4" s="28"/>
-      <c r="Y4" s="28"/>
-      <c r="Z4" s="29"/>
+      <c r="T4" s="26"/>
+      <c r="U4" s="27"/>
+      <c r="V4" s="27"/>
+      <c r="W4" s="27"/>
+      <c r="X4" s="27"/>
+      <c r="Y4" s="27"/>
+      <c r="Z4" s="28"/>
     </row>
     <row r="5" spans="2:26" ht="21" customHeight="1">
-      <c r="B5" s="43">
+      <c r="B5" s="42">
         <v>20013</v>
       </c>
-      <c r="C5" s="42" t="s">
+      <c r="C5" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="43" t="s">
+      <c r="D5" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="E5" s="43" t="s">
+      <c r="E5" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="F5" s="43">
+      <c r="F5" s="42">
         <v>13000</v>
       </c>
-      <c r="G5" s="43" t="s">
+      <c r="G5" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="44">
+      <c r="H5" s="43">
         <v>8569741235</v>
       </c>
       <c r="I5" s="19"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="42" t="s">
+      <c r="J5" s="20"/>
+      <c r="K5" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="L5" s="42">
+      <c r="L5" s="41">
         <v>25</v>
       </c>
-      <c r="M5" s="43" t="s">
+      <c r="M5" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="N5" s="43" t="s">
+      <c r="N5" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="O5" s="43">
+      <c r="O5" s="42">
         <v>13000</v>
       </c>
-      <c r="P5" s="43" t="s">
+      <c r="P5" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="Q5" s="44">
+      <c r="Q5" s="43">
         <v>8569741235</v>
       </c>
-      <c r="T5" s="37" t="s">
+      <c r="T5" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="U5" s="30"/>
-      <c r="V5" s="33">
+      <c r="U5" s="29"/>
+      <c r="V5" s="32">
         <f>VLOOKUP(VLOOKUP(B4,B3:H15,2,0),K3:Q15,2,0)</f>
         <v>26</v>
       </c>
-      <c r="W5" s="30"/>
-      <c r="X5" s="30"/>
-      <c r="Y5" s="30"/>
-      <c r="Z5" s="31"/>
+      <c r="W5" s="29"/>
+      <c r="X5" s="29"/>
+      <c r="Y5" s="29"/>
+      <c r="Z5" s="30"/>
     </row>
     <row r="6" spans="2:26" ht="21" customHeight="1">
-      <c r="B6" s="43">
+      <c r="B6" s="42">
         <v>20014</v>
       </c>
-      <c r="C6" s="42" t="s">
+      <c r="C6" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="43" t="s">
+      <c r="D6" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="43">
+      <c r="F6" s="42">
         <v>20000</v>
       </c>
-      <c r="G6" s="43" t="s">
+      <c r="G6" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="H6" s="44">
+      <c r="H6" s="43">
         <v>7584963214</v>
       </c>
       <c r="I6" s="19"/>
-      <c r="J6" s="21"/>
-      <c r="K6" s="42" t="s">
+      <c r="J6" s="20"/>
+      <c r="K6" s="41" t="s">
         <v>17</v>
       </c>
-      <c r="L6" s="42">
+      <c r="L6" s="41">
         <v>28</v>
       </c>
-      <c r="M6" s="43" t="s">
+      <c r="M6" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="N6" s="43" t="s">
+      <c r="N6" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="O6" s="43">
+      <c r="O6" s="42">
         <v>20000</v>
       </c>
-      <c r="P6" s="43" t="s">
+      <c r="P6" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="Q6" s="44">
+      <c r="Q6" s="43">
         <v>7584963214</v>
       </c>
-      <c r="T6" s="46" t="s">
+      <c r="T6" s="45" t="s">
         <v>69</v>
       </c>
-      <c r="U6" s="47"/>
-      <c r="V6" s="47"/>
-      <c r="W6" s="47"/>
-      <c r="X6" s="47"/>
-      <c r="Y6" s="47"/>
-      <c r="Z6" s="48"/>
+      <c r="U6" s="46"/>
+      <c r="V6" s="46"/>
+      <c r="W6" s="46"/>
+      <c r="X6" s="46"/>
+      <c r="Y6" s="46"/>
+      <c r="Z6" s="47"/>
     </row>
     <row r="7" spans="2:26" ht="21" customHeight="1">
-      <c r="B7" s="43">
+      <c r="B7" s="42">
         <v>20015</v>
       </c>
-      <c r="C7" s="42" t="s">
+      <c r="C7" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="D7" s="43" t="s">
+      <c r="D7" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="F7" s="43">
+      <c r="F7" s="42">
         <v>15000</v>
       </c>
-      <c r="G7" s="43" t="s">
+      <c r="G7" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="44">
+      <c r="H7" s="43">
         <v>7788994455</v>
       </c>
       <c r="I7" s="19"/>
-      <c r="J7" s="21"/>
-      <c r="K7" s="42" t="s">
+      <c r="J7" s="20"/>
+      <c r="K7" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="L7" s="42">
+      <c r="L7" s="41">
         <v>27</v>
       </c>
-      <c r="M7" s="43" t="s">
+      <c r="M7" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="N7" s="43" t="s">
+      <c r="N7" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="O7" s="43">
+      <c r="O7" s="42">
         <v>15000</v>
       </c>
-      <c r="P7" s="43" t="s">
+      <c r="P7" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="Q7" s="44">
+      <c r="Q7" s="43">
         <v>7788994455</v>
       </c>
-      <c r="T7" s="27"/>
-      <c r="U7" s="34" cm="1">
+      <c r="T7" s="26"/>
+      <c r="U7" s="33" cm="1">
         <f t="array" ref="U7:Z7">VLOOKUP(VLOOKUP(B4,B3:H15,2,0),K3:Q15,{2,3,4,5,6,7},0)</f>
         <v>26</v>
       </c>
-      <c r="V7" s="34" t="str">
+      <c r="V7" s="33" t="str">
         <v>Engineer</v>
       </c>
-      <c r="W7" s="34" t="str">
+      <c r="W7" s="33" t="str">
         <v>Technical</v>
       </c>
-      <c r="X7" s="34">
+      <c r="X7" s="33">
         <v>26500</v>
       </c>
-      <c r="Y7" s="34" t="str">
+      <c r="Y7" s="33" t="str">
         <v>Indore</v>
       </c>
-      <c r="Z7" s="35">
+      <c r="Z7" s="34">
         <v>8877456987</v>
       </c>
     </row>
     <row r="8" spans="2:26" ht="21" customHeight="1">
-      <c r="B8" s="43">
+      <c r="B8" s="42">
         <v>20016</v>
       </c>
-      <c r="C8" s="42" t="s">
+      <c r="C8" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="43" t="s">
+      <c r="D8" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="43" t="s">
+      <c r="E8" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="43">
+      <c r="F8" s="42">
         <v>20000</v>
       </c>
-      <c r="G8" s="43" t="s">
+      <c r="G8" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="H8" s="44">
+      <c r="H8" s="43">
         <v>8798654512</v>
       </c>
       <c r="I8" s="19"/>
-      <c r="J8" s="21"/>
-      <c r="K8" s="42" t="s">
+      <c r="J8" s="20"/>
+      <c r="K8" s="41" t="s">
         <v>20</v>
       </c>
-      <c r="L8" s="42">
+      <c r="L8" s="41">
         <v>25</v>
       </c>
-      <c r="M8" s="43" t="s">
+      <c r="M8" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="N8" s="43" t="s">
+      <c r="N8" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="O8" s="43">
+      <c r="O8" s="42">
         <v>20000</v>
       </c>
-      <c r="P8" s="43" t="s">
+      <c r="P8" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="Q8" s="44">
+      <c r="Q8" s="43">
         <v>8798654512</v>
       </c>
-      <c r="T8" s="25"/>
-      <c r="Z8" s="26"/>
+      <c r="T8" s="24"/>
+      <c r="Z8" s="25"/>
     </row>
     <row r="9" spans="2:26" ht="21" customHeight="1">
-      <c r="B9" s="43">
+      <c r="B9" s="42">
         <v>20017</v>
       </c>
-      <c r="C9" s="42" t="s">
+      <c r="C9" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="43" t="s">
+      <c r="D9" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="E9" s="43" t="s">
+      <c r="E9" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="43">
+      <c r="F9" s="42">
         <v>33000</v>
       </c>
-      <c r="G9" s="43" t="s">
+      <c r="G9" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="H9" s="44">
+      <c r="H9" s="43">
         <v>9874563214</v>
       </c>
       <c r="I9" s="19"/>
-      <c r="J9" s="21"/>
-      <c r="K9" s="42" t="s">
+      <c r="J9" s="20"/>
+      <c r="K9" s="41" t="s">
         <v>22</v>
       </c>
-      <c r="L9" s="42">
+      <c r="L9" s="41">
         <v>26</v>
       </c>
-      <c r="M9" s="43" t="s">
+      <c r="M9" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="N9" s="43" t="s">
+      <c r="N9" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="O9" s="43">
+      <c r="O9" s="42">
         <v>33000</v>
       </c>
-      <c r="P9" s="43" t="s">
+      <c r="P9" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="Q9" s="44">
+      <c r="Q9" s="43">
         <v>9874563214</v>
       </c>
-      <c r="T9" s="49" t="s">
+      <c r="T9" s="48" t="s">
         <v>71</v>
       </c>
       <c r="U9" s="2"/>
       <c r="V9" s="2"/>
-      <c r="W9" s="36" t="str">
+      <c r="W9" s="35" t="str">
         <f>IFERROR(VLOOKUP(VLOOKUP(B5,B3:H15,2,0),K3:Q15,MATCH(V11,K3:Q3,0),0),"Not available")</f>
         <v>Accountant</v>
       </c>
-      <c r="Z9" s="26"/>
+      <c r="Z9" s="25"/>
     </row>
     <row r="10" spans="2:26" ht="21" customHeight="1">
-      <c r="B10" s="43">
+      <c r="B10" s="42">
         <v>20018</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="43" t="s">
+      <c r="D10" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="43" t="s">
+      <c r="E10" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="43">
+      <c r="F10" s="42">
         <v>21000</v>
       </c>
-      <c r="G10" s="43" t="s">
+      <c r="G10" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="H10" s="44">
+      <c r="H10" s="43">
         <v>8974563214</v>
       </c>
       <c r="I10" s="19"/>
-      <c r="J10" s="21"/>
-      <c r="K10" s="42" t="s">
+      <c r="J10" s="20"/>
+      <c r="K10" s="41" t="s">
         <v>23</v>
       </c>
-      <c r="L10" s="42">
+      <c r="L10" s="41">
         <v>25</v>
       </c>
-      <c r="M10" s="43" t="s">
+      <c r="M10" s="42" t="s">
         <v>18</v>
       </c>
-      <c r="N10" s="43" t="s">
+      <c r="N10" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="O10" s="43">
+      <c r="O10" s="42">
         <v>21000</v>
       </c>
-      <c r="P10" s="43" t="s">
+      <c r="P10" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="Q10" s="44">
+      <c r="Q10" s="43">
         <v>8974563214</v>
       </c>
-      <c r="T10" s="27"/>
-      <c r="U10" s="28"/>
-      <c r="V10" s="28"/>
-      <c r="W10" s="28"/>
-      <c r="X10" s="28"/>
-      <c r="Y10" s="28"/>
-      <c r="Z10" s="29"/>
+      <c r="T10" s="26"/>
+      <c r="U10" s="27"/>
+      <c r="V10" s="27"/>
+      <c r="W10" s="27"/>
+      <c r="X10" s="27"/>
+      <c r="Y10" s="27"/>
+      <c r="Z10" s="28"/>
     </row>
     <row r="11" spans="2:26" ht="15.5">
-      <c r="B11" s="43">
+      <c r="B11" s="42">
         <v>20019</v>
       </c>
-      <c r="C11" s="42" t="s">
+      <c r="C11" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="43" t="s">
+      <c r="D11" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="E11" s="43" t="s">
+      <c r="E11" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="F11" s="43">
+      <c r="F11" s="42">
         <v>31500</v>
       </c>
-      <c r="G11" s="43" t="s">
+      <c r="G11" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="H11" s="44">
+      <c r="H11" s="43">
         <v>8745968745</v>
       </c>
       <c r="I11" s="19"/>
-      <c r="J11" s="21"/>
-      <c r="K11" s="42" t="s">
+      <c r="J11" s="20"/>
+      <c r="K11" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="L11" s="42">
+      <c r="L11" s="41">
         <v>26</v>
       </c>
-      <c r="M11" s="43" t="s">
+      <c r="M11" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="N11" s="43" t="s">
+      <c r="N11" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="O11" s="43">
+      <c r="O11" s="42">
         <v>31500</v>
       </c>
-      <c r="P11" s="43" t="s">
+      <c r="P11" s="42" t="s">
         <v>16</v>
       </c>
-      <c r="Q11" s="44">
+      <c r="Q11" s="43">
         <v>8745968745</v>
       </c>
-      <c r="T11" s="39" t="s">
+      <c r="T11" s="38" t="s">
         <v>65</v>
       </c>
-      <c r="U11" s="50">
+      <c r="U11" s="49">
         <v>20019</v>
       </c>
-      <c r="V11" s="51" t="s">
+      <c r="V11" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="W11" s="23"/>
-      <c r="X11" s="23"/>
-      <c r="Y11" s="23"/>
-      <c r="Z11" s="24"/>
+      <c r="W11" s="22"/>
+      <c r="X11" s="22"/>
+      <c r="Y11" s="22"/>
+      <c r="Z11" s="23"/>
     </row>
     <row r="12" spans="2:26" ht="21" customHeight="1">
-      <c r="B12" s="43">
+      <c r="B12" s="42">
         <v>20020</v>
       </c>
-      <c r="C12" s="42" t="s">
+      <c r="C12" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="D12" s="43" t="s">
+      <c r="D12" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="E12" s="43" t="s">
+      <c r="E12" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="F12" s="43">
+      <c r="F12" s="42">
         <v>40500</v>
       </c>
-      <c r="G12" s="43" t="s">
+      <c r="G12" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="H12" s="44">
+      <c r="H12" s="43">
         <v>9874569874</v>
       </c>
       <c r="I12" s="19"/>
-      <c r="J12" s="21"/>
-      <c r="K12" s="42" t="s">
+      <c r="J12" s="20"/>
+      <c r="K12" s="41" t="s">
         <v>26</v>
       </c>
-      <c r="L12" s="42">
+      <c r="L12" s="41">
         <v>28</v>
       </c>
-      <c r="M12" s="43" t="s">
+      <c r="M12" s="42" t="s">
         <v>14</v>
       </c>
-      <c r="N12" s="43" t="s">
+      <c r="N12" s="42" t="s">
         <v>15</v>
       </c>
-      <c r="O12" s="43">
+      <c r="O12" s="42">
         <v>40500</v>
       </c>
-      <c r="P12" s="43" t="s">
+      <c r="P12" s="42" t="s">
         <v>12</v>
       </c>
-      <c r="Q12" s="44">
+      <c r="Q12" s="43">
         <v>9874569874</v>
       </c>
-      <c r="T12" s="38" t="s">
+      <c r="T12" s="37" t="s">
         <v>67</v>
       </c>
       <c r="V12" s="2"/>
       <c r="W12" s="2"/>
       <c r="X12" s="2"/>
-      <c r="Z12" s="26"/>
+      <c r="Z12" s="25"/>
     </row>
     <row r="13" spans="2:26" ht="21" customHeight="1">
-      <c r="B13" s="43">
+      <c r="B13" s="42">
         <v>20021</v>
       </c>
-      <c r="C13" s="42" t="s">
+      <c r="C13" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="D13" s="43" t="s">
+      <c r="D13" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="43" t="s">
+      <c r="E13" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="F13" s="43">
+      <c r="F13" s="42">
         <v>25500</v>
       </c>
-      <c r="G13" s="43" t="s">
+      <c r="G13" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="H13" s="44">
+      <c r="H13" s="43">
         <v>8574965874</v>
       </c>
       <c r="I13" s="19"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="42" t="s">
+      <c r="J13" s="20"/>
+      <c r="K13" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="L13" s="42">
+      <c r="L13" s="41">
         <v>27</v>
       </c>
-      <c r="M13" s="43" t="s">
+      <c r="M13" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="N13" s="43" t="s">
+      <c r="N13" s="42" t="s">
         <v>11</v>
       </c>
-      <c r="O13" s="43">
+      <c r="O13" s="42">
         <v>25500</v>
       </c>
-      <c r="P13" s="43" t="s">
+      <c r="P13" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="Q13" s="44">
+      <c r="Q13" s="43">
         <v>8574965874</v>
       </c>
-      <c r="T13" s="27"/>
-      <c r="U13" s="28"/>
-      <c r="V13" s="34" t="str">
+      <c r="T13" s="26"/>
+      <c r="U13" s="27"/>
+      <c r="V13" s="33" t="str">
         <f>VLOOKUP(VLOOKUP(U11,B3:H15,2,0),K3:Q15,MATCH(V11,K3:Q3,0),0)</f>
         <v>Accountant</v>
       </c>
-      <c r="W13" s="28"/>
-      <c r="X13" s="28"/>
-      <c r="Y13" s="28"/>
-      <c r="Z13" s="29"/>
+      <c r="W13" s="27"/>
+      <c r="X13" s="27"/>
+      <c r="Y13" s="27"/>
+      <c r="Z13" s="28"/>
     </row>
     <row r="14" spans="2:26">
       <c r="B14" s="16">
@@ -4685,18 +4622,18 @@
       <c r="Q14" s="15">
         <v>8521479632</v>
       </c>
-      <c r="T14" s="40" t="s">
+      <c r="T14" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="U14" s="23"/>
-      <c r="V14" s="32" t="str">
+      <c r="U14" s="22"/>
+      <c r="V14" s="31" t="str">
         <f>IFERROR(VLOOKUP(B5,B3:H15,8,0),"not available")</f>
         <v>not available</v>
       </c>
-      <c r="W14" s="23"/>
-      <c r="X14" s="23"/>
-      <c r="Y14" s="23"/>
-      <c r="Z14" s="24"/>
+      <c r="W14" s="22"/>
+      <c r="X14" s="22"/>
+      <c r="Y14" s="22"/>
+      <c r="Z14" s="23"/>
     </row>
     <row r="15" spans="2:26" ht="21" customHeight="1">
       <c r="B15" s="16">
@@ -4741,13 +4678,13 @@
       <c r="Q15" s="15">
         <v>8569745623</v>
       </c>
-      <c r="T15" s="27"/>
-      <c r="U15" s="28"/>
-      <c r="V15" s="28"/>
-      <c r="W15" s="28"/>
-      <c r="X15" s="28"/>
-      <c r="Y15" s="28"/>
-      <c r="Z15" s="29"/>
+      <c r="T15" s="26"/>
+      <c r="U15" s="27"/>
+      <c r="V15" s="27"/>
+      <c r="W15" s="27"/>
+      <c r="X15" s="27"/>
+      <c r="Y15" s="27"/>
+      <c r="Z15" s="28"/>
     </row>
     <row r="17" spans="10:12" ht="18" customHeight="1"/>
     <row r="18" spans="10:12" ht="54.75" customHeight="1"/>
@@ -4755,9 +4692,9 @@
     <row r="20" spans="10:12" ht="14.25" customHeight="1"/>
     <row r="21" spans="10:12" ht="27.75" customHeight="1"/>
     <row r="22" spans="10:12" ht="36" customHeight="1">
-      <c r="J22" s="134"/>
-      <c r="K22" s="134"/>
-      <c r="L22" s="134"/>
+      <c r="J22" s="130"/>
+      <c r="K22" s="130"/>
+      <c r="L22" s="130"/>
     </row>
     <row r="24" spans="10:12" ht="41.25" customHeight="1"/>
     <row r="25" spans="10:12" ht="14.25" customHeight="1"/>
@@ -4888,11 +4825,11 @@
       <c r="O2" s="5">
         <v>8877456987</v>
       </c>
-      <c r="Q2" s="62" t="s">
+      <c r="Q2" s="61" t="s">
         <v>72</v>
       </c>
-      <c r="R2" s="53"/>
-      <c r="S2" s="54">
+      <c r="R2" s="52"/>
+      <c r="S2" s="53">
         <f>VLOOKUP(VLOOKUP(R3,CHOOSE({1,2},B1:B13,A1:A13),2,0),I1:O13,2,0)</f>
         <v>25</v>
       </c>
@@ -4943,13 +4880,13 @@
       <c r="O3" s="5">
         <v>8569741235</v>
       </c>
-      <c r="Q3" s="61" t="s">
+      <c r="Q3" s="60" t="s">
         <v>73</v>
       </c>
-      <c r="R3" s="63">
+      <c r="R3" s="62">
         <v>20013</v>
       </c>
-      <c r="S3" s="55"/>
+      <c r="S3" s="54"/>
     </row>
     <row r="4" spans="1:22" ht="21" customHeight="1" thickBot="1">
       <c r="A4" s="4" t="s">
@@ -4994,9 +4931,9 @@
       <c r="O4" s="5">
         <v>7584963214</v>
       </c>
-      <c r="Q4" s="57"/>
-      <c r="R4" s="58"/>
-      <c r="S4" s="60"/>
+      <c r="Q4" s="56"/>
+      <c r="R4" s="57"/>
+      <c r="S4" s="59"/>
     </row>
     <row r="5" spans="1:22" ht="21" customHeight="1">
       <c r="A5" s="4" t="s">
@@ -5041,11 +4978,11 @@
       <c r="O5" s="5">
         <v>7788994455</v>
       </c>
-      <c r="Q5" s="135" t="s">
+      <c r="Q5" s="131" t="s">
         <v>74</v>
       </c>
-      <c r="R5" s="136"/>
-      <c r="S5" s="137"/>
+      <c r="R5" s="132"/>
+      <c r="S5" s="133"/>
     </row>
     <row r="6" spans="1:22" ht="21" customHeight="1" thickBot="1">
       <c r="A6" s="4" t="s">
@@ -5090,14 +5027,14 @@
       <c r="O6" s="5">
         <v>8798654512</v>
       </c>
-      <c r="Q6" s="57">
+      <c r="Q6" s="56">
         <f t="array" ref="Q6:S6">IFERROR(VLOOKUP(VLOOKUP(R3,CHOOSE({1,2},B:B,A:A),2,0),I1:O13,{2,4,7},0),"NOT AVAILABLE")</f>
         <v>25</v>
       </c>
-      <c r="R6" s="58" t="str">
+      <c r="R6" s="57" t="str">
         <v>Finance</v>
       </c>
-      <c r="S6" s="59">
+      <c r="S6" s="58">
         <v>8569741235</v>
       </c>
     </row>
@@ -5430,159 +5367,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
-  <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
-    <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="70.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10" customWidth="1"/>
-    <col min="6" max="6" width="68.08984375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="4" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="51" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B1" s="20" t="s">
-        <v>76</v>
-      </c>
-      <c r="C1" s="69" t="s">
-        <v>77</v>
-      </c>
-      <c r="D1" s="54" t="str">
-        <f>VLOOKUP(D2,A1:B6,2,1)</f>
-        <v>B</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A2" s="3">
-        <v>0</v>
-      </c>
-      <c r="B2" s="21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C2" s="67" t="s">
-        <v>79</v>
-      </c>
-      <c r="D2" s="68">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A3" s="3">
-        <v>40</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A4" s="3">
-        <v>60</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A5" s="3">
-        <v>75</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="14.25" customHeight="1">
-      <c r="A6" s="3">
-        <v>90</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" ht="68.25" customHeight="1"/>
-    <row r="9" spans="1:7" ht="14.25" customHeight="1"/>
-    <row r="10" spans="1:7" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A10" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B10" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B11" s="3">
-        <v>110</v>
-      </c>
-      <c r="C11" s="3">
-        <v>105</v>
-      </c>
-      <c r="D11" s="3">
-        <v>106</v>
-      </c>
-      <c r="F11" s="64" t="s">
-        <v>84</v>
-      </c>
-      <c r="G11" s="54">
-        <f>VLOOKUP(F12,A10:D13,MATCH(F13,A10:D10,0),0)</f>
-        <v>110</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B12" s="3">
-        <v>110</v>
-      </c>
-      <c r="C12" s="3">
-        <v>104</v>
-      </c>
-      <c r="D12" s="3">
-        <v>105</v>
-      </c>
-      <c r="F12" s="65" t="s">
-        <v>85</v>
-      </c>
-      <c r="G12" s="55"/>
-    </row>
-    <row r="13" spans="1:7" ht="14.25" customHeight="1" thickBot="1">
-      <c r="A13" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B13" s="3">
-        <v>103</v>
-      </c>
-      <c r="C13" s="3">
-        <v>100</v>
-      </c>
-      <c r="D13" s="3">
-        <v>106</v>
-      </c>
-      <c r="F13" s="66" t="s">
-        <v>86</v>
-      </c>
-      <c r="G13" s="60"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="B2:Q40"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
@@ -5604,10 +5388,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="3:17" ht="21" customHeight="1">
-      <c r="C2" s="138" t="s">
+      <c r="C2" s="134" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="138"/>
+      <c r="D2" s="134"/>
       <c r="E2" s="1" t="s">
         <v>1</v>
       </c>
@@ -5649,8 +5433,8 @@
       </c>
     </row>
     <row r="3" spans="3:17" ht="23.25" customHeight="1">
-      <c r="C3" s="138"/>
-      <c r="D3" s="138"/>
+      <c r="C3" s="134"/>
+      <c r="D3" s="134"/>
       <c r="E3" s="11" t="s">
         <v>2</v>
       </c>
@@ -5692,8 +5476,8 @@
       </c>
     </row>
     <row r="4" spans="3:17" ht="23.25" customHeight="1">
-      <c r="C4" s="138"/>
-      <c r="D4" s="138"/>
+      <c r="C4" s="134"/>
+      <c r="D4" s="134"/>
       <c r="E4" s="11" t="s">
         <v>3</v>
       </c>
@@ -5735,8 +5519,8 @@
       </c>
     </row>
     <row r="5" spans="3:17" ht="21" customHeight="1">
-      <c r="C5" s="138"/>
-      <c r="D5" s="138"/>
+      <c r="C5" s="134"/>
+      <c r="D5" s="134"/>
       <c r="E5" s="11" t="s">
         <v>4</v>
       </c>
@@ -5778,8 +5562,8 @@
       </c>
     </row>
     <row r="6" spans="3:17" ht="21" customHeight="1">
-      <c r="C6" s="138"/>
-      <c r="D6" s="138"/>
+      <c r="C6" s="134"/>
+      <c r="D6" s="134"/>
       <c r="E6" s="11" t="s">
         <v>5</v>
       </c>
@@ -5821,8 +5605,8 @@
       </c>
     </row>
     <row r="7" spans="3:17" ht="21" customHeight="1">
-      <c r="C7" s="138"/>
-      <c r="D7" s="138"/>
+      <c r="C7" s="134"/>
+      <c r="D7" s="134"/>
       <c r="E7" s="11" t="s">
         <v>6</v>
       </c>
@@ -5864,8 +5648,8 @@
       </c>
     </row>
     <row r="8" spans="3:17" ht="21" customHeight="1">
-      <c r="C8" s="138"/>
-      <c r="D8" s="138"/>
+      <c r="C8" s="134"/>
+      <c r="D8" s="134"/>
       <c r="E8" s="11" t="s">
         <v>7</v>
       </c>
@@ -5907,8 +5691,8 @@
       </c>
     </row>
     <row r="9" spans="3:17" ht="21" customHeight="1">
-      <c r="C9" s="138"/>
-      <c r="D9" s="138"/>
+      <c r="C9" s="134"/>
+      <c r="D9" s="134"/>
       <c r="E9" s="11" t="s">
         <v>8</v>
       </c>
@@ -5950,179 +5734,179 @@
       </c>
     </row>
     <row r="12" spans="3:17" ht="15" thickBot="1">
-      <c r="C12" s="75" t="s">
-        <v>92</v>
-      </c>
-      <c r="D12" s="76">
+      <c r="C12" s="70" t="s">
+        <v>75</v>
+      </c>
+      <c r="D12" s="71">
         <v>20014</v>
       </c>
     </row>
     <row r="13" spans="3:17" ht="36" customHeight="1" thickBot="1">
-      <c r="C13" s="73" t="s">
-        <v>93</v>
-      </c>
-      <c r="D13" s="71" t="str">
+      <c r="C13" s="68" t="s">
+        <v>76</v>
+      </c>
+      <c r="D13" s="66" t="str">
         <f>HLOOKUP(D12,C2:Q9,2,0)</f>
         <v>Kapil Singh</v>
       </c>
     </row>
     <row r="14" spans="3:17" ht="14.25" customHeight="1" thickBot="1"/>
     <row r="15" spans="3:17" ht="41.25" customHeight="1" thickBot="1">
-      <c r="C15" s="73" t="s">
-        <v>94</v>
-      </c>
-      <c r="D15" s="72" t="str">
+      <c r="C15" s="68" t="s">
+        <v>77</v>
+      </c>
+      <c r="D15" s="67" t="str">
         <f t="array" ref="D15:F15">HLOOKUP(D12,E2:Q9,{2,3,4},0)</f>
         <v>Kapil Singh</v>
       </c>
-      <c r="E15" s="72">
+      <c r="E15" s="67">
         <v>28</v>
       </c>
-      <c r="F15" s="71" t="str">
+      <c r="F15" s="66" t="str">
         <v>CAD Designer</v>
       </c>
     </row>
     <row r="16" spans="3:17" ht="14.25" customHeight="1"/>
     <row r="17" spans="3:7" ht="14.25" customHeight="1" thickBot="1"/>
     <row r="18" spans="3:7" ht="27.75" customHeight="1">
-      <c r="C18" s="74" t="s">
-        <v>95</v>
-      </c>
-      <c r="D18" s="54">
+      <c r="C18" s="69" t="s">
+        <v>78</v>
+      </c>
+      <c r="D18" s="53">
         <f>HLOOKUP(D12,E2:Q9,MATCH(C19,E2:E9,0),0)</f>
         <v>20000</v>
       </c>
-      <c r="E18" s="70"/>
-      <c r="F18" s="70"/>
+      <c r="E18" s="65"/>
+      <c r="F18" s="65"/>
     </row>
     <row r="19" spans="3:7" ht="14.25" customHeight="1" thickBot="1">
-      <c r="C19" s="77" t="s">
+      <c r="C19" s="72" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="60"/>
+      <c r="D19" s="59"/>
     </row>
     <row r="20" spans="3:7" ht="14.25" customHeight="1"/>
     <row r="21" spans="3:7" ht="14.25" customHeight="1"/>
     <row r="22" spans="3:7" ht="14.25" customHeight="1" thickBot="1"/>
     <row r="23" spans="3:7" ht="14.25" customHeight="1">
-      <c r="C23" s="74" t="s">
-        <v>96</v>
-      </c>
-      <c r="D23" s="54" t="str">
+      <c r="C23" s="69" t="s">
+        <v>79</v>
+      </c>
+      <c r="D23" s="53" t="str">
         <f>HLOOKUP($D$12,$E$2:$Q$9,ROWS($E$2:E3),0)</f>
         <v>Kapil Singh</v>
       </c>
-      <c r="E23" s="70"/>
-      <c r="F23" s="70"/>
-      <c r="G23" s="70"/>
+      <c r="E23" s="65"/>
+      <c r="F23" s="65"/>
+      <c r="G23" s="65"/>
     </row>
     <row r="24" spans="3:7" ht="14.25" customHeight="1">
-      <c r="C24" s="56"/>
-      <c r="D24" s="55">
+      <c r="C24" s="55"/>
+      <c r="D24" s="54">
         <f>HLOOKUP($D$12,$E$2:$Q$9,ROWS($E$2:E4),0)</f>
         <v>28</v>
       </c>
     </row>
     <row r="25" spans="3:7" ht="14.25" customHeight="1">
-      <c r="C25" s="56"/>
-      <c r="D25" s="55" t="str">
+      <c r="C25" s="55"/>
+      <c r="D25" s="54" t="str">
         <f>HLOOKUP($D$12,$E$2:$Q$9,ROWS($E$2:E5),0)</f>
         <v>CAD Designer</v>
       </c>
     </row>
     <row r="26" spans="3:7" ht="27.75" customHeight="1">
-      <c r="C26" s="56"/>
-      <c r="D26" s="55" t="str">
+      <c r="C26" s="55"/>
+      <c r="D26" s="54" t="str">
         <f>HLOOKUP($D$12,$E$2:$Q$9,ROWS($E$2:E6),0)</f>
         <v>Technical</v>
       </c>
     </row>
     <row r="27" spans="3:7" ht="14.25" customHeight="1">
-      <c r="C27" s="56"/>
-      <c r="D27" s="55">
+      <c r="C27" s="55"/>
+      <c r="D27" s="54">
         <f>HLOOKUP($D$12,$E$2:$Q$9,ROWS($E$2:E7),0)</f>
         <v>20000</v>
       </c>
     </row>
     <row r="28" spans="3:7" ht="14.25" customHeight="1">
-      <c r="C28" s="56"/>
-      <c r="D28" s="55" t="str">
+      <c r="C28" s="55"/>
+      <c r="D28" s="54" t="str">
         <f>HLOOKUP($D$12,$E$2:$Q$9,ROWS($E$2:E8),0)</f>
         <v>Indore</v>
       </c>
     </row>
     <row r="29" spans="3:7" ht="14.25" customHeight="1" thickBot="1">
-      <c r="C29" s="57"/>
-      <c r="D29" s="59">
+      <c r="C29" s="56"/>
+      <c r="D29" s="58">
         <f>HLOOKUP($D$12,$E$2:$Q$9,ROWS($E$2:E9),0)</f>
         <v>7584963214</v>
       </c>
-      <c r="F29" s="70"/>
-      <c r="G29" s="70"/>
+      <c r="F29" s="65"/>
+      <c r="G29" s="65"/>
     </row>
     <row r="30" spans="3:7" ht="14.25" customHeight="1"/>
     <row r="31" spans="3:7" ht="14.25" customHeight="1"/>
     <row r="32" spans="3:7" ht="14.25" customHeight="1"/>
     <row r="33" spans="2:9" ht="14.25" customHeight="1" thickBot="1"/>
     <row r="34" spans="2:9" ht="68.25" customHeight="1">
-      <c r="B34" s="126" t="s">
-        <v>97</v>
-      </c>
-      <c r="C34" s="127"/>
-      <c r="D34" s="127"/>
-      <c r="E34" s="127"/>
-      <c r="F34" s="127"/>
-      <c r="G34" s="127"/>
-      <c r="H34" s="127"/>
-      <c r="I34" s="54" t="str">
+      <c r="B34" s="122" t="s">
+        <v>80</v>
+      </c>
+      <c r="C34" s="123"/>
+      <c r="D34" s="123"/>
+      <c r="E34" s="123"/>
+      <c r="F34" s="123"/>
+      <c r="G34" s="123"/>
+      <c r="H34" s="123"/>
+      <c r="I34" s="53" t="str">
         <f t="shared" ref="I34:I40" si="0">HLOOKUP($D$12,$E$2:$Q$9,ROW(E2),0)</f>
         <v>Kapil Singh</v>
       </c>
     </row>
     <row r="35" spans="2:9">
-      <c r="B35" s="56"/>
-      <c r="I35" s="55">
+      <c r="B35" s="55"/>
+      <c r="I35" s="54">
         <f t="shared" si="0"/>
         <v>28</v>
       </c>
     </row>
     <row r="36" spans="2:9">
-      <c r="B36" s="56"/>
-      <c r="I36" s="55" t="str">
+      <c r="B36" s="55"/>
+      <c r="I36" s="54" t="str">
         <f t="shared" si="0"/>
         <v>CAD Designer</v>
       </c>
     </row>
     <row r="37" spans="2:9">
-      <c r="B37" s="56"/>
-      <c r="I37" s="55" t="str">
+      <c r="B37" s="55"/>
+      <c r="I37" s="54" t="str">
         <f t="shared" si="0"/>
         <v>Technical</v>
       </c>
     </row>
     <row r="38" spans="2:9">
-      <c r="B38" s="56"/>
-      <c r="I38" s="55">
+      <c r="B38" s="55"/>
+      <c r="I38" s="54">
         <f t="shared" si="0"/>
         <v>20000</v>
       </c>
     </row>
     <row r="39" spans="2:9">
-      <c r="B39" s="56"/>
-      <c r="I39" s="55" t="str">
+      <c r="B39" s="55"/>
+      <c r="I39" s="54" t="str">
         <f t="shared" si="0"/>
         <v>Indore</v>
       </c>
     </row>
     <row r="40" spans="2:9" ht="15" thickBot="1">
-      <c r="B40" s="57"/>
-      <c r="C40" s="58"/>
-      <c r="D40" s="58"/>
-      <c r="E40" s="58"/>
-      <c r="F40" s="58"/>
-      <c r="G40" s="58"/>
-      <c r="H40" s="58"/>
-      <c r="I40" s="60">
+      <c r="B40" s="56"/>
+      <c r="C40" s="57"/>
+      <c r="D40" s="57"/>
+      <c r="E40" s="57"/>
+      <c r="F40" s="57"/>
+      <c r="G40" s="57"/>
+      <c r="H40" s="57"/>
+      <c r="I40" s="59">
         <f t="shared" si="0"/>
         <v>7584963214</v>
       </c>
@@ -6144,7 +5928,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:S21"/>
   <sheetFormatPr defaultColWidth="8.6328125" defaultRowHeight="14.5"/>
@@ -6172,26 +5956,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="14.25" customHeight="1">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="121" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="139"/>
-      <c r="C1" s="139"/>
-      <c r="D1" s="139"/>
-      <c r="E1" s="139"/>
-      <c r="F1" s="139"/>
-      <c r="G1" s="139"/>
-      <c r="H1" s="139"/>
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
     </row>
     <row r="2" spans="1:19" ht="14.25" customHeight="1">
-      <c r="A2" s="139"/>
-      <c r="B2" s="139"/>
-      <c r="C2" s="139"/>
-      <c r="D2" s="139"/>
-      <c r="E2" s="139"/>
-      <c r="F2" s="139"/>
-      <c r="G2" s="139"/>
-      <c r="H2" s="139"/>
+      <c r="A2" s="121"/>
+      <c r="B2" s="121"/>
+      <c r="C2" s="121"/>
+      <c r="D2" s="121"/>
+      <c r="E2" s="121"/>
+      <c r="F2" s="121"/>
+      <c r="G2" s="121"/>
+      <c r="H2" s="121"/>
     </row>
     <row r="3" spans="1:19" ht="23.25" customHeight="1" thickBot="1">
       <c r="A3" s="1" t="s">
@@ -6218,14 +6002,14 @@
       <c r="H3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="83"/>
-      <c r="M3" s="83"/>
-      <c r="N3" s="83"/>
-      <c r="O3" s="83"/>
-      <c r="P3" s="83"/>
-      <c r="Q3" s="83"/>
-      <c r="R3" s="83"/>
-      <c r="S3" s="83"/>
+      <c r="L3" s="78"/>
+      <c r="M3" s="78"/>
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
     </row>
     <row r="4" spans="1:19" ht="21" customHeight="1">
       <c r="A4" s="3">
@@ -6252,16 +6036,16 @@
       <c r="H4" s="5">
         <v>8877456987</v>
       </c>
-      <c r="L4" s="87" t="s">
-        <v>98</v>
-      </c>
-      <c r="M4" s="88"/>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="88"/>
-      <c r="S4" s="89"/>
+      <c r="L4" s="82" t="s">
+        <v>81</v>
+      </c>
+      <c r="M4" s="83"/>
+      <c r="N4" s="83"/>
+      <c r="O4" s="83"/>
+      <c r="P4" s="83"/>
+      <c r="Q4" s="83"/>
+      <c r="R4" s="83"/>
+      <c r="S4" s="84"/>
     </row>
     <row r="5" spans="1:19" ht="21" customHeight="1">
       <c r="A5" s="3">
@@ -6288,8 +6072,8 @@
       <c r="H5" s="5">
         <v>8569741235</v>
       </c>
-      <c r="L5" s="61" t="s">
-        <v>92</v>
+      <c r="L5" s="60" t="s">
+        <v>75</v>
       </c>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
@@ -6297,7 +6081,7 @@
       <c r="P5" s="3"/>
       <c r="Q5" s="3"/>
       <c r="R5" s="3"/>
-      <c r="S5" s="90"/>
+      <c r="S5" s="85"/>
     </row>
     <row r="6" spans="1:19" ht="21" customHeight="1" thickBot="1">
       <c r="A6" s="3">
@@ -6324,34 +6108,34 @@
       <c r="H6" s="5">
         <v>7584963214</v>
       </c>
-      <c r="L6" s="91">
+      <c r="L6" s="86">
         <v>20015</v>
       </c>
-      <c r="M6" s="92" t="str">
+      <c r="M6" s="87" t="str">
         <f>VLOOKUP(L6,A3:H15,2,0)</f>
         <v>Ali Asgar</v>
       </c>
-      <c r="N6" s="92">
+      <c r="N6" s="87">
         <f>VLOOKUP(L6,A3:H15,3,0)</f>
         <v>27</v>
       </c>
-      <c r="O6" s="92" t="str">
+      <c r="O6" s="87" t="str">
         <f>VLOOKUP(L6,A3:H15,4,0)</f>
         <v>Accountant</v>
       </c>
-      <c r="P6" s="92" t="str">
+      <c r="P6" s="87" t="str">
         <f>VLOOKUP(L6,A3:H15,5,0)</f>
         <v>Finance</v>
       </c>
-      <c r="Q6" s="92">
+      <c r="Q6" s="87">
         <f>VLOOKUP(L6,A3:H15,6,0)</f>
         <v>15000</v>
       </c>
-      <c r="R6" s="92" t="str">
+      <c r="R6" s="87" t="str">
         <f>VLOOKUP(L6,A3:H15,7,0)</f>
         <v>Bhopal</v>
       </c>
-      <c r="S6" s="93">
+      <c r="S6" s="88">
         <f>VLOOKUP(L6,A3:H15,8,0)</f>
         <v>7788994455</v>
       </c>
@@ -6382,19 +6166,19 @@
         <v>7788994455</v>
       </c>
       <c r="J7" s="2"/>
-      <c r="L7" s="94" t="s">
-        <v>99</v>
-      </c>
-      <c r="M7" s="82">
+      <c r="L7" s="89" t="s">
+        <v>82</v>
+      </c>
+      <c r="M7" s="77">
         <f>VLOOKUP(B8,B3:H15,5,0)</f>
         <v>20000</v>
       </c>
-      <c r="N7" s="98"/>
-      <c r="O7" s="98"/>
-      <c r="P7" s="98"/>
-      <c r="Q7" s="98"/>
-      <c r="R7" s="99"/>
-      <c r="S7" s="100"/>
+      <c r="N7" s="93"/>
+      <c r="O7" s="93"/>
+      <c r="P7" s="93"/>
+      <c r="Q7" s="93"/>
+      <c r="R7" s="94"/>
+      <c r="S7" s="95"/>
     </row>
     <row r="8" spans="1:19" ht="21" customHeight="1" thickBot="1">
       <c r="A8" s="3">
@@ -6447,16 +6231,16 @@
       <c r="H9" s="5">
         <v>9874563214</v>
       </c>
-      <c r="L9" s="84" t="s">
-        <v>106</v>
-      </c>
-      <c r="M9" s="85"/>
-      <c r="N9" s="85"/>
-      <c r="O9" s="85"/>
-      <c r="P9" s="85"/>
-      <c r="Q9" s="85"/>
-      <c r="R9" s="85"/>
-      <c r="S9" s="86"/>
+      <c r="L9" s="79" t="s">
+        <v>89</v>
+      </c>
+      <c r="M9" s="80"/>
+      <c r="N9" s="80"/>
+      <c r="O9" s="80"/>
+      <c r="P9" s="80"/>
+      <c r="Q9" s="80"/>
+      <c r="R9" s="80"/>
+      <c r="S9" s="81"/>
     </row>
     <row r="10" spans="1:19" ht="21" customHeight="1">
       <c r="A10" s="3">
@@ -6483,7 +6267,7 @@
       <c r="H10" s="5">
         <v>8974563214</v>
       </c>
-      <c r="L10" s="56">
+      <c r="L10" s="55">
         <v>20016</v>
       </c>
       <c r="M10" s="3" t="str">
@@ -6501,7 +6285,7 @@
       </c>
       <c r="Q10" s="3"/>
       <c r="R10" s="3"/>
-      <c r="S10" s="90"/>
+      <c r="S10" s="85"/>
     </row>
     <row r="11" spans="1:19" ht="21" customHeight="1">
       <c r="A11" s="3">
@@ -6528,7 +6312,7 @@
       <c r="H11" s="5">
         <v>8745968745</v>
       </c>
-      <c r="L11" s="56">
+      <c r="L11" s="55">
         <v>20017</v>
       </c>
       <c r="M11" s="3" t="str">
@@ -6544,7 +6328,7 @@
       <c r="P11" s="5">
         <v>9874563214</v>
       </c>
-      <c r="S11" s="55"/>
+      <c r="S11" s="54"/>
     </row>
     <row r="12" spans="1:19" ht="21" customHeight="1" thickBot="1">
       <c r="A12" s="3">
@@ -6571,25 +6355,25 @@
       <c r="H12" s="5">
         <v>9874569874</v>
       </c>
-      <c r="L12" s="57">
+      <c r="L12" s="56">
         <v>20020</v>
       </c>
-      <c r="M12" s="92" t="str">
+      <c r="M12" s="87" t="str">
         <f t="array" ref="M12:P12">VLOOKUP(A10,A5:H17,{2,4,6,8},0)</f>
         <v>Ravi Verma</v>
       </c>
-      <c r="N12" s="92" t="str">
+      <c r="N12" s="87" t="str">
         <v>CAD Designer</v>
       </c>
-      <c r="O12" s="92">
+      <c r="O12" s="87">
         <v>21000</v>
       </c>
-      <c r="P12" s="95">
+      <c r="P12" s="90">
         <v>8974563214</v>
       </c>
-      <c r="Q12" s="92"/>
-      <c r="R12" s="92"/>
-      <c r="S12" s="96"/>
+      <c r="Q12" s="87"/>
+      <c r="R12" s="87"/>
+      <c r="S12" s="91"/>
     </row>
     <row r="13" spans="1:19" ht="21" customHeight="1" thickBot="1">
       <c r="A13" s="3">
@@ -6616,13 +6400,13 @@
       <c r="H13" s="5">
         <v>8574965874</v>
       </c>
-      <c r="M13" s="101"/>
-      <c r="N13" s="101"/>
-      <c r="O13" s="101"/>
-      <c r="P13" s="101"/>
-      <c r="Q13" s="101"/>
-      <c r="R13" s="101"/>
-      <c r="S13" s="97"/>
+      <c r="M13" s="96"/>
+      <c r="N13" s="96"/>
+      <c r="O13" s="96"/>
+      <c r="P13" s="96"/>
+      <c r="Q13" s="96"/>
+      <c r="R13" s="96"/>
+      <c r="S13" s="92"/>
     </row>
     <row r="14" spans="1:19" ht="21" customHeight="1" thickBot="1">
       <c r="A14" s="3">
@@ -6649,26 +6433,26 @@
       <c r="H14" s="5">
         <v>8521479632</v>
       </c>
-      <c r="L14" s="73" t="s">
-        <v>100</v>
-      </c>
-      <c r="M14" s="72">
+      <c r="L14" s="68" t="s">
+        <v>83</v>
+      </c>
+      <c r="M14" s="67">
         <f t="array" ref="M14:R14">VLOOKUP(B12,B3:H15,{2,3,4,5,6,7},0)</f>
         <v>28</v>
       </c>
-      <c r="N14" s="72" t="str">
+      <c r="N14" s="67" t="str">
         <v>Accountant</v>
       </c>
-      <c r="O14" s="72" t="str">
+      <c r="O14" s="67" t="str">
         <v>Finance</v>
       </c>
-      <c r="P14" s="72">
+      <c r="P14" s="67">
         <v>40500</v>
       </c>
-      <c r="Q14" s="72" t="str">
+      <c r="Q14" s="67" t="str">
         <v>Indore</v>
       </c>
-      <c r="R14" s="102">
+      <c r="R14" s="97">
         <v>9874569874</v>
       </c>
     </row>
@@ -6700,53 +6484,53 @@
       <c r="S15" s="3"/>
     </row>
     <row r="16" spans="1:19">
-      <c r="L16" s="74" t="s">
-        <v>101</v>
-      </c>
-      <c r="M16" s="78"/>
-      <c r="N16" s="78"/>
-      <c r="O16" s="79"/>
-      <c r="P16" s="79"/>
-      <c r="Q16" s="79"/>
-      <c r="R16" s="79"/>
-      <c r="S16" s="54"/>
+      <c r="L16" s="69" t="s">
+        <v>84</v>
+      </c>
+      <c r="M16" s="73"/>
+      <c r="N16" s="73"/>
+      <c r="O16" s="74"/>
+      <c r="P16" s="74"/>
+      <c r="Q16" s="74"/>
+      <c r="R16" s="74"/>
+      <c r="S16" s="53"/>
     </row>
     <row r="17" spans="12:19" ht="27.75" customHeight="1">
-      <c r="L17" s="56"/>
-      <c r="M17" s="80" t="s">
-        <v>92</v>
-      </c>
-      <c r="N17" s="81" t="s">
+      <c r="L17" s="55"/>
+      <c r="M17" s="75" t="s">
+        <v>75</v>
+      </c>
+      <c r="N17" s="76" t="s">
         <v>2</v>
       </c>
-      <c r="S17" s="55"/>
+      <c r="S17" s="54"/>
     </row>
     <row r="18" spans="12:19" ht="36" customHeight="1" thickBot="1">
-      <c r="L18" s="57"/>
-      <c r="M18" s="58">
+      <c r="L18" s="56"/>
+      <c r="M18" s="57">
         <v>20017</v>
       </c>
-      <c r="N18" s="58" t="str">
+      <c r="N18" s="57" t="str">
         <f>VLOOKUP(M18,A3:H15,MATCH(N17,A3:H3,0),0)</f>
         <v>Mohan Patel</v>
       </c>
-      <c r="O18" s="58"/>
-      <c r="P18" s="58"/>
-      <c r="Q18" s="58"/>
-      <c r="R18" s="58"/>
-      <c r="S18" s="60"/>
+      <c r="O18" s="57"/>
+      <c r="P18" s="57"/>
+      <c r="Q18" s="57"/>
+      <c r="R18" s="57"/>
+      <c r="S18" s="59"/>
     </row>
     <row r="19" spans="12:19" ht="14.25" customHeight="1"/>
     <row r="20" spans="12:19" ht="14.25" customHeight="1" thickBot="1"/>
     <row r="21" spans="12:19" ht="36" customHeight="1" thickBot="1">
-      <c r="L21" s="104" t="s">
-        <v>102</v>
-      </c>
-      <c r="M21" s="72">
+      <c r="L21" s="99" t="s">
+        <v>85</v>
+      </c>
+      <c r="M21" s="67">
         <f>MATCH(B3,A3:H3,0)</f>
         <v>2</v>
       </c>
-      <c r="N21" s="103"/>
+      <c r="N21" s="98"/>
       <c r="O21" s="2"/>
       <c r="P21" s="2"/>
     </row>

--- a/Data_analysis_using_excel/Employee_Table.xlsx
+++ b/Data_analysis_using_excel/Employee_Table.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VISHWAS SHARMA\Documents\Xcel_portfolio\Data_analysis_using_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21B3050D-4567-43B2-A761-D1812C1A7BC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E3B31B-2A4B-42A2-8A31-CE9892039737}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" firstSheet="3" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" tabRatio="500" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="employee" sheetId="1" r:id="rId1"/>
@@ -285,7 +285,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -1871,13 +1871,13 @@
     <col min="6" max="6" width="11.453125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="7.453125" bestFit="1" customWidth="1"/>
     <col min="8" max="9" width="12.90625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="82.81640625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.7265625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="10.6328125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="7.1796875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="7.36328125" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="72.54296875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.453125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.6328125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.26953125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="6.54296875" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="10.81640625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="3.81640625" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="94" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="7.1796875" bestFit="1" customWidth="1"/>
@@ -2031,7 +2031,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:25" ht="21" customHeight="1">
+    <row r="5" spans="1:25" ht="21" customHeight="1" thickBot="1">
       <c r="A5" s="3">
         <v>20013</v>
       </c>
@@ -2056,6 +2056,14 @@
       <c r="H5" s="5">
         <v>8569741235</v>
       </c>
+      <c r="K5" s="108" t="s">
+        <v>25</v>
+      </c>
+      <c r="L5" s="109"/>
+      <c r="M5" s="109"/>
+      <c r="N5" s="109"/>
+      <c r="O5" s="109"/>
+      <c r="P5" s="109"/>
       <c r="U5" s="6">
         <v>3</v>
       </c>
@@ -2094,6 +2102,19 @@
       <c r="H6" s="5">
         <v>7584963214</v>
       </c>
+      <c r="K6" s="55"/>
+      <c r="L6" s="117" t="str">
+        <f t="array" ref="L6:N18">CHOOSE({1,2,3},F3:F15,C3:C15,A3:A15)</f>
+        <v>Salary</v>
+      </c>
+      <c r="M6" s="118" t="str">
+        <v>Age</v>
+      </c>
+      <c r="N6" s="118" t="str">
+        <v>Emp. ID</v>
+      </c>
+      <c r="O6" s="119"/>
+      <c r="P6" s="120"/>
       <c r="U6" s="6">
         <v>4</v>
       </c>
@@ -2132,6 +2153,18 @@
       <c r="H7" s="5">
         <v>7788994455</v>
       </c>
+      <c r="K7" s="55"/>
+      <c r="L7" s="102">
+        <v>26500</v>
+      </c>
+      <c r="M7" s="103">
+        <v>26</v>
+      </c>
+      <c r="N7" s="103">
+        <v>20012</v>
+      </c>
+      <c r="O7" s="103"/>
+      <c r="P7" s="104"/>
       <c r="U7" s="6">
         <v>5</v>
       </c>
@@ -2170,6 +2203,18 @@
       <c r="H8" s="5">
         <v>8798654512</v>
       </c>
+      <c r="K8" s="55"/>
+      <c r="L8" s="102">
+        <v>13000</v>
+      </c>
+      <c r="M8" s="103">
+        <v>25</v>
+      </c>
+      <c r="N8" s="103">
+        <v>20013</v>
+      </c>
+      <c r="O8" s="103"/>
+      <c r="P8" s="104"/>
       <c r="U8" s="6">
         <v>6</v>
       </c>
@@ -2208,6 +2253,18 @@
       <c r="H9" s="5">
         <v>9874563214</v>
       </c>
+      <c r="K9" s="55"/>
+      <c r="L9" s="102">
+        <v>20000</v>
+      </c>
+      <c r="M9" s="103">
+        <v>28</v>
+      </c>
+      <c r="N9" s="103">
+        <v>20014</v>
+      </c>
+      <c r="O9" s="103"/>
+      <c r="P9" s="104"/>
       <c r="U9" s="6">
         <v>7</v>
       </c>
@@ -2221,7 +2278,7 @@
         <v>231000</v>
       </c>
     </row>
-    <row r="10" spans="1:25" ht="21" customHeight="1" thickBot="1">
+    <row r="10" spans="1:25" ht="21" customHeight="1">
       <c r="A10" s="3">
         <v>20018</v>
       </c>
@@ -2246,6 +2303,18 @@
       <c r="H10" s="5">
         <v>8974563214</v>
       </c>
+      <c r="K10" s="55"/>
+      <c r="L10" s="102">
+        <v>15000</v>
+      </c>
+      <c r="M10" s="103">
+        <v>27</v>
+      </c>
+      <c r="N10" s="103">
+        <v>20015</v>
+      </c>
+      <c r="O10" s="103"/>
+      <c r="P10" s="104"/>
       <c r="U10" s="6">
         <v>8</v>
       </c>
@@ -2259,7 +2328,7 @@
         <v>167000</v>
       </c>
     </row>
-    <row r="11" spans="1:25" ht="21" customHeight="1" thickBot="1">
+    <row r="11" spans="1:25" ht="21" customHeight="1">
       <c r="A11" s="3">
         <v>20019</v>
       </c>
@@ -2284,14 +2353,18 @@
       <c r="H11" s="5">
         <v>8745968745</v>
       </c>
-      <c r="K11" s="108" t="s">
+      <c r="K11" s="55"/>
+      <c r="L11" s="102">
+        <v>20000</v>
+      </c>
+      <c r="M11" s="103">
         <v>25</v>
       </c>
-      <c r="L11" s="109"/>
-      <c r="M11" s="109"/>
-      <c r="N11" s="109"/>
-      <c r="O11" s="109"/>
-      <c r="P11" s="109"/>
+      <c r="N11" s="103">
+        <v>20016</v>
+      </c>
+      <c r="O11" s="103"/>
+      <c r="P11" s="104"/>
       <c r="Q11" s="24"/>
       <c r="U11" s="6">
         <v>9</v>
@@ -2332,18 +2405,17 @@
         <v>9874569874</v>
       </c>
       <c r="K12" s="55"/>
-      <c r="L12" s="117" t="str">
-        <f t="array" ref="L12:N24">CHOOSE({1,2,3},F3:F15,C3:C15,A3:A15)</f>
-        <v>Salary</v>
-      </c>
-      <c r="M12" s="118" t="str">
-        <v>Age</v>
-      </c>
-      <c r="N12" s="118" t="str">
-        <v>Emp. ID</v>
-      </c>
-      <c r="O12" s="119"/>
-      <c r="P12" s="120"/>
+      <c r="L12" s="102">
+        <v>33000</v>
+      </c>
+      <c r="M12" s="103">
+        <v>26</v>
+      </c>
+      <c r="N12" s="103">
+        <v>20017</v>
+      </c>
+      <c r="O12" s="103"/>
+      <c r="P12" s="104"/>
       <c r="U12" s="6">
         <v>10</v>
       </c>
@@ -2384,13 +2456,13 @@
       </c>
       <c r="K13" s="55"/>
       <c r="L13" s="102">
-        <v>26500</v>
+        <v>21000</v>
       </c>
       <c r="M13" s="103">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="N13" s="103">
-        <v>20012</v>
+        <v>20018</v>
       </c>
       <c r="O13" s="103"/>
       <c r="P13" s="104"/>
@@ -2434,13 +2506,13 @@
       </c>
       <c r="K14" s="55"/>
       <c r="L14" s="102">
-        <v>13000</v>
+        <v>31500</v>
       </c>
       <c r="M14" s="103">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N14" s="103">
-        <v>20013</v>
+        <v>20019</v>
       </c>
       <c r="O14" s="103"/>
       <c r="P14" s="104"/>
@@ -2484,13 +2556,13 @@
       </c>
       <c r="K15" s="55"/>
       <c r="L15" s="102">
-        <v>20000</v>
+        <v>40500</v>
       </c>
       <c r="M15" s="103">
         <v>28</v>
       </c>
       <c r="N15" s="103">
-        <v>20014</v>
+        <v>20020</v>
       </c>
       <c r="O15" s="103"/>
       <c r="P15" s="104"/>
@@ -2512,13 +2584,13 @@
     <row r="16" spans="1:25" ht="14.25" customHeight="1">
       <c r="K16" s="55"/>
       <c r="L16" s="102">
-        <v>15000</v>
+        <v>25500</v>
       </c>
       <c r="M16" s="103">
         <v>27</v>
       </c>
       <c r="N16" s="103">
-        <v>20015</v>
+        <v>20021</v>
       </c>
       <c r="O16" s="103"/>
       <c r="P16" s="104"/>
@@ -2535,16 +2607,16 @@
         <v>20013</v>
       </c>
     </row>
-    <row r="17" spans="2:25" ht="14.25" customHeight="1">
+    <row r="17" spans="11:25" ht="14.25" customHeight="1">
       <c r="K17" s="55"/>
       <c r="L17" s="102">
-        <v>20000</v>
+        <v>18000</v>
       </c>
       <c r="M17" s="103">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="N17" s="103">
-        <v>20016</v>
+        <v>20022</v>
       </c>
       <c r="O17" s="103"/>
       <c r="P17" s="104"/>
@@ -2561,814 +2633,737 @@
         <v>167000</v>
       </c>
     </row>
-    <row r="18" spans="2:25" ht="14.25" customHeight="1">
-      <c r="K18" s="55"/>
-      <c r="L18" s="102">
+    <row r="18" spans="11:25" ht="14.25" customHeight="1" thickBot="1">
+      <c r="K18" s="56"/>
+      <c r="L18" s="105">
+        <v>21000</v>
+      </c>
+      <c r="M18" s="106">
+        <v>27</v>
+      </c>
+      <c r="N18" s="106">
+        <v>20023</v>
+      </c>
+      <c r="O18" s="106"/>
+      <c r="P18" s="107"/>
+    </row>
+    <row r="19" spans="11:25" ht="14.25" customHeight="1">
+      <c r="K19" s="122" t="s">
+        <v>31</v>
+      </c>
+      <c r="L19" s="123"/>
+      <c r="M19" s="123"/>
+      <c r="N19" s="123"/>
+      <c r="O19" s="123"/>
+      <c r="P19" s="123"/>
+      <c r="Q19" s="123"/>
+      <c r="R19" s="124"/>
+    </row>
+    <row r="20" spans="11:25" ht="14.25" customHeight="1">
+      <c r="K20" s="55" t="str">
+        <f t="array" ref="K20:R29">_xlfn._xlws.FILTER(A3:H15,C3:C15&gt;25)</f>
+        <v>Emp. ID</v>
+      </c>
+      <c r="L20" t="str">
+        <v>Name</v>
+      </c>
+      <c r="M20" t="str">
+        <v>Age</v>
+      </c>
+      <c r="N20" t="str">
+        <v>Designation</v>
+      </c>
+      <c r="O20" t="str">
+        <v>Department</v>
+      </c>
+      <c r="P20" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="Q20" t="str">
+        <v>Place</v>
+      </c>
+      <c r="R20" s="54" t="str">
+        <v>Mob.No.</v>
+      </c>
+    </row>
+    <row r="21" spans="11:25" ht="21" customHeight="1">
+      <c r="K21" s="55">
+        <v>20012</v>
+      </c>
+      <c r="L21" t="str">
+        <v>Kapil Sharma</v>
+      </c>
+      <c r="M21">
+        <v>26</v>
+      </c>
+      <c r="N21" t="str">
+        <v>Engineer</v>
+      </c>
+      <c r="O21" t="str">
+        <v>Technical</v>
+      </c>
+      <c r="P21">
+        <v>26500</v>
+      </c>
+      <c r="Q21" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R21" s="114">
+        <v>8877456987</v>
+      </c>
+    </row>
+    <row r="22" spans="11:25" ht="14.25" customHeight="1">
+      <c r="K22" s="55">
+        <v>20014</v>
+      </c>
+      <c r="L22" t="str">
+        <v>Kapil Singh</v>
+      </c>
+      <c r="M22">
+        <v>28</v>
+      </c>
+      <c r="N22" t="str">
+        <v>CAD Designer</v>
+      </c>
+      <c r="O22" t="str">
+        <v>Technical</v>
+      </c>
+      <c r="P22">
+        <v>20000</v>
+      </c>
+      <c r="Q22" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R22" s="114">
+        <v>7584963214</v>
+      </c>
+    </row>
+    <row r="23" spans="11:25" ht="14.25" customHeight="1">
+      <c r="K23" s="55">
+        <v>20015</v>
+      </c>
+      <c r="L23" t="str">
+        <v>Ali Asgar</v>
+      </c>
+      <c r="M23">
+        <v>27</v>
+      </c>
+      <c r="N23" t="str">
+        <v>Accountant</v>
+      </c>
+      <c r="O23" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="P23">
+        <v>15000</v>
+      </c>
+      <c r="Q23" t="str">
+        <v>Bhopal</v>
+      </c>
+      <c r="R23" s="114">
+        <v>7788994455</v>
+      </c>
+    </row>
+    <row r="24" spans="11:25" ht="21" customHeight="1">
+      <c r="K24" s="55">
+        <v>20017</v>
+      </c>
+      <c r="L24" t="str">
+        <v>Mohan Patel</v>
+      </c>
+      <c r="M24">
+        <v>26</v>
+      </c>
+      <c r="N24" t="str">
+        <v>Engineer</v>
+      </c>
+      <c r="O24" t="str">
+        <v>Technical</v>
+      </c>
+      <c r="P24">
         <v>33000</v>
       </c>
-      <c r="M18" s="103">
+      <c r="Q24" t="str">
+        <v>Bhopal</v>
+      </c>
+      <c r="R24" s="114">
+        <v>9874563214</v>
+      </c>
+    </row>
+    <row r="25" spans="11:25" ht="14.25" customHeight="1">
+      <c r="K25" s="55">
+        <v>20019</v>
+      </c>
+      <c r="L25" t="str">
+        <v>Deepak Singh</v>
+      </c>
+      <c r="M25">
         <v>26</v>
       </c>
-      <c r="N18" s="103">
+      <c r="N25" t="str">
+        <v>Accountant</v>
+      </c>
+      <c r="O25" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="P25">
+        <v>31500</v>
+      </c>
+      <c r="Q25" t="str">
+        <v>Bhopal</v>
+      </c>
+      <c r="R25" s="114">
+        <v>8745968745</v>
+      </c>
+    </row>
+    <row r="26" spans="11:25" ht="14.25" customHeight="1">
+      <c r="K26" s="55">
+        <v>20020</v>
+      </c>
+      <c r="L26" t="str">
+        <v>Vikas Patel</v>
+      </c>
+      <c r="M26">
+        <v>28</v>
+      </c>
+      <c r="N26" t="str">
+        <v>Accountant</v>
+      </c>
+      <c r="O26" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="P26">
+        <v>40500</v>
+      </c>
+      <c r="Q26" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R26" s="114">
+        <v>9874569874</v>
+      </c>
+    </row>
+    <row r="27" spans="11:25" ht="14.25" customHeight="1">
+      <c r="K27" s="55">
+        <v>20021</v>
+      </c>
+      <c r="L27" t="str">
+        <v>Gopal Jat</v>
+      </c>
+      <c r="M27">
+        <v>27</v>
+      </c>
+      <c r="N27" t="str">
+        <v>Engineer</v>
+      </c>
+      <c r="O27" t="str">
+        <v>Technical</v>
+      </c>
+      <c r="P27">
+        <v>25500</v>
+      </c>
+      <c r="Q27" t="str">
+        <v>ujjain</v>
+      </c>
+      <c r="R27" s="114">
+        <v>8574965874</v>
+      </c>
+    </row>
+    <row r="28" spans="11:25" ht="14.25" customHeight="1">
+      <c r="K28" s="55">
+        <v>20022</v>
+      </c>
+      <c r="L28" t="str">
+        <v>Rohan Yadav</v>
+      </c>
+      <c r="M28">
+        <v>26</v>
+      </c>
+      <c r="N28" t="str">
+        <v>Accountant</v>
+      </c>
+      <c r="O28" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="P28">
+        <v>18000</v>
+      </c>
+      <c r="Q28" t="str">
+        <v>ujjain</v>
+      </c>
+      <c r="R28" s="114">
+        <v>8521479632</v>
+      </c>
+    </row>
+    <row r="29" spans="11:25" ht="14.25" customHeight="1" thickBot="1">
+      <c r="K29" s="56">
+        <v>20023</v>
+      </c>
+      <c r="L29" s="57" t="str">
+        <v>Janwi Rai</v>
+      </c>
+      <c r="M29" s="57">
+        <v>27</v>
+      </c>
+      <c r="N29" s="57" t="str">
+        <v>CAD Designer</v>
+      </c>
+      <c r="O29" s="57" t="str">
+        <v>Technical</v>
+      </c>
+      <c r="P29" s="57">
+        <v>21000</v>
+      </c>
+      <c r="Q29" s="57" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R29" s="58">
+        <v>8569745623</v>
+      </c>
+    </row>
+    <row r="30" spans="11:25" ht="14.25" customHeight="1">
+      <c r="K30" s="122" t="s">
+        <v>32</v>
+      </c>
+      <c r="L30" s="123"/>
+      <c r="M30" s="123"/>
+      <c r="N30" s="123"/>
+      <c r="O30" s="123"/>
+      <c r="P30" s="123"/>
+      <c r="Q30" s="123"/>
+      <c r="R30" s="124"/>
+    </row>
+    <row r="31" spans="11:25" ht="14.25" customHeight="1">
+      <c r="K31" s="55">
+        <f t="array" ref="K31:R37">_xlfn._xlws.FILTER(A3:H15,E3:E15="Technical")</f>
+        <v>20012</v>
+      </c>
+      <c r="L31" t="str">
+        <v>Kapil Sharma</v>
+      </c>
+      <c r="M31">
+        <v>26</v>
+      </c>
+      <c r="N31" t="str">
+        <v>Engineer</v>
+      </c>
+      <c r="O31" t="str">
+        <v>Technical</v>
+      </c>
+      <c r="P31">
+        <v>26500</v>
+      </c>
+      <c r="Q31" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R31" s="114">
+        <v>8877456987</v>
+      </c>
+    </row>
+    <row r="32" spans="11:25" ht="14.25" customHeight="1">
+      <c r="K32" s="55">
+        <v>20014</v>
+      </c>
+      <c r="L32" t="str">
+        <v>Kapil Singh</v>
+      </c>
+      <c r="M32">
+        <v>28</v>
+      </c>
+      <c r="N32" t="str">
+        <v>CAD Designer</v>
+      </c>
+      <c r="O32" t="str">
+        <v>Technical</v>
+      </c>
+      <c r="P32">
+        <v>20000</v>
+      </c>
+      <c r="Q32" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R32" s="114">
+        <v>7584963214</v>
+      </c>
+    </row>
+    <row r="33" spans="11:18" ht="14.25" customHeight="1">
+      <c r="K33" s="55">
+        <v>20016</v>
+      </c>
+      <c r="L33" t="str">
+        <v>Sunil Singh</v>
+      </c>
+      <c r="M33">
+        <v>25</v>
+      </c>
+      <c r="N33" t="str">
+        <v>Engineer</v>
+      </c>
+      <c r="O33" t="str">
+        <v>Technical</v>
+      </c>
+      <c r="P33">
+        <v>20000</v>
+      </c>
+      <c r="Q33" t="str">
+        <v>ujjain</v>
+      </c>
+      <c r="R33" s="114">
+        <v>8798654512</v>
+      </c>
+    </row>
+    <row r="34" spans="11:18" ht="14.25" customHeight="1">
+      <c r="K34" s="55">
         <v>20017</v>
       </c>
-      <c r="O18" s="103"/>
-      <c r="P18" s="104"/>
-    </row>
-    <row r="19" spans="2:25" ht="14.25" customHeight="1">
-      <c r="K19" s="55"/>
-      <c r="L19" s="102">
+      <c r="L34" t="str">
+        <v>Mohan Patel</v>
+      </c>
+      <c r="M34">
+        <v>26</v>
+      </c>
+      <c r="N34" t="str">
+        <v>Engineer</v>
+      </c>
+      <c r="O34" t="str">
+        <v>Technical</v>
+      </c>
+      <c r="P34">
+        <v>33000</v>
+      </c>
+      <c r="Q34" t="str">
+        <v>Bhopal</v>
+      </c>
+      <c r="R34" s="114">
+        <v>9874563214</v>
+      </c>
+    </row>
+    <row r="35" spans="11:18" ht="21" customHeight="1">
+      <c r="K35" s="55">
+        <v>20018</v>
+      </c>
+      <c r="L35" t="str">
+        <v>Ravi Verma</v>
+      </c>
+      <c r="M35">
+        <v>25</v>
+      </c>
+      <c r="N35" t="str">
+        <v>CAD Designer</v>
+      </c>
+      <c r="O35" t="str">
+        <v>Technical</v>
+      </c>
+      <c r="P35">
         <v>21000</v>
       </c>
-      <c r="M19" s="103">
+      <c r="Q35" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R35" s="114">
+        <v>8974563214</v>
+      </c>
+    </row>
+    <row r="36" spans="11:18" ht="14.25" customHeight="1">
+      <c r="K36" s="55">
+        <v>20021</v>
+      </c>
+      <c r="L36" t="str">
+        <v>Gopal Jat</v>
+      </c>
+      <c r="M36">
+        <v>27</v>
+      </c>
+      <c r="N36" t="str">
+        <v>Engineer</v>
+      </c>
+      <c r="O36" t="str">
+        <v>Technical</v>
+      </c>
+      <c r="P36">
+        <v>25500</v>
+      </c>
+      <c r="Q36" t="str">
+        <v>ujjain</v>
+      </c>
+      <c r="R36" s="114">
+        <v>8574965874</v>
+      </c>
+    </row>
+    <row r="37" spans="11:18" ht="14.25" customHeight="1" thickBot="1">
+      <c r="K37" s="56">
+        <v>20023</v>
+      </c>
+      <c r="L37" s="57" t="str">
+        <v>Janwi Rai</v>
+      </c>
+      <c r="M37" s="57">
+        <v>27</v>
+      </c>
+      <c r="N37" s="57" t="str">
+        <v>CAD Designer</v>
+      </c>
+      <c r="O37" s="57" t="str">
+        <v>Technical</v>
+      </c>
+      <c r="P37" s="57">
+        <v>21000</v>
+      </c>
+      <c r="Q37" s="57" t="str">
+        <v>Indore</v>
+      </c>
+      <c r="R37" s="58">
+        <v>8569745623</v>
+      </c>
+    </row>
+    <row r="38" spans="11:18" ht="14.25" customHeight="1">
+      <c r="K38" s="122" t="s">
+        <v>33</v>
+      </c>
+      <c r="L38" s="123"/>
+      <c r="M38" s="123"/>
+      <c r="N38" s="123"/>
+      <c r="O38" s="123"/>
+      <c r="P38" s="123"/>
+      <c r="Q38" s="123"/>
+      <c r="R38" s="124"/>
+    </row>
+    <row r="39" spans="11:18" ht="14.25" customHeight="1">
+      <c r="K39" s="55">
+        <f t="array" ref="K39:R42">_xlfn._xlws.FILTER(A3:H15,G3:G15="Bhopal")</f>
+        <v>20013</v>
+      </c>
+      <c r="L39" t="str">
+        <v>Sunil Grover</v>
+      </c>
+      <c r="M39">
         <v>25</v>
       </c>
-      <c r="N19" s="103">
-        <v>20018</v>
-      </c>
-      <c r="O19" s="103"/>
-      <c r="P19" s="104"/>
-    </row>
-    <row r="20" spans="2:25" ht="14.25" customHeight="1">
-      <c r="K20" s="55"/>
-      <c r="L20" s="102">
+      <c r="N39" t="str">
+        <v>Accountant</v>
+      </c>
+      <c r="O39" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="P39">
+        <v>13000</v>
+      </c>
+      <c r="Q39" t="str">
+        <v>Bhopal</v>
+      </c>
+      <c r="R39" s="114">
+        <v>8569741235</v>
+      </c>
+    </row>
+    <row r="40" spans="11:18" ht="14.25" customHeight="1">
+      <c r="K40" s="55">
+        <v>20015</v>
+      </c>
+      <c r="L40" t="str">
+        <v>Ali Asgar</v>
+      </c>
+      <c r="M40">
+        <v>27</v>
+      </c>
+      <c r="N40" t="str">
+        <v>Accountant</v>
+      </c>
+      <c r="O40" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="P40">
+        <v>15000</v>
+      </c>
+      <c r="Q40" t="str">
+        <v>Bhopal</v>
+      </c>
+      <c r="R40" s="114">
+        <v>7788994455</v>
+      </c>
+    </row>
+    <row r="41" spans="11:18" ht="14.25" customHeight="1">
+      <c r="K41" s="55">
+        <v>20017</v>
+      </c>
+      <c r="L41" t="str">
+        <v>Mohan Patel</v>
+      </c>
+      <c r="M41">
+        <v>26</v>
+      </c>
+      <c r="N41" t="str">
+        <v>Engineer</v>
+      </c>
+      <c r="O41" t="str">
+        <v>Technical</v>
+      </c>
+      <c r="P41">
+        <v>33000</v>
+      </c>
+      <c r="Q41" t="str">
+        <v>Bhopal</v>
+      </c>
+      <c r="R41" s="114">
+        <v>9874563214</v>
+      </c>
+    </row>
+    <row r="42" spans="11:18" ht="14.25" customHeight="1" thickBot="1">
+      <c r="K42" s="56">
+        <v>20019</v>
+      </c>
+      <c r="L42" s="57" t="str">
+        <v>Deepak Singh</v>
+      </c>
+      <c r="M42" s="57">
+        <v>26</v>
+      </c>
+      <c r="N42" s="57" t="str">
+        <v>Accountant</v>
+      </c>
+      <c r="O42" s="57" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="P42" s="57">
         <v>31500</v>
       </c>
-      <c r="M20" s="103">
+      <c r="Q42" s="57" t="str">
+        <v>Bhopal</v>
+      </c>
+      <c r="R42" s="58">
+        <v>8745968745</v>
+      </c>
+    </row>
+    <row r="43" spans="11:18" ht="21" customHeight="1">
+      <c r="K43" s="122" t="s">
+        <v>34</v>
+      </c>
+      <c r="L43" s="123"/>
+      <c r="M43" s="123"/>
+      <c r="N43" s="123"/>
+      <c r="O43" s="123"/>
+      <c r="P43" s="123"/>
+      <c r="Q43" s="123"/>
+      <c r="R43" s="124"/>
+    </row>
+    <row r="44" spans="11:18" ht="14.25" customHeight="1">
+      <c r="K44" s="55" t="str">
+        <f t="array" ref="K44:R47">_xlfn._xlws.FILTER(A3:H15,F3:F15&gt;30000)</f>
+        <v>Emp. ID</v>
+      </c>
+      <c r="L44" t="str">
+        <v>Name</v>
+      </c>
+      <c r="M44" t="str">
+        <v>Age</v>
+      </c>
+      <c r="N44" t="str">
+        <v>Designation</v>
+      </c>
+      <c r="O44" t="str">
+        <v>Department</v>
+      </c>
+      <c r="P44" t="str">
+        <v>Salary</v>
+      </c>
+      <c r="Q44" t="str">
+        <v>Place</v>
+      </c>
+      <c r="R44" s="54" t="str">
+        <v>Mob.No.</v>
+      </c>
+    </row>
+    <row r="45" spans="11:18" ht="14.25" customHeight="1">
+      <c r="K45" s="55">
+        <v>20017</v>
+      </c>
+      <c r="L45" t="str">
+        <v>Mohan Patel</v>
+      </c>
+      <c r="M45">
         <v>26</v>
       </c>
-      <c r="N20" s="103">
+      <c r="N45" t="str">
+        <v>Engineer</v>
+      </c>
+      <c r="O45" t="str">
+        <v>Technical</v>
+      </c>
+      <c r="P45">
+        <v>33000</v>
+      </c>
+      <c r="Q45" t="str">
+        <v>Bhopal</v>
+      </c>
+      <c r="R45" s="114">
+        <v>9874563214</v>
+      </c>
+    </row>
+    <row r="46" spans="11:18" ht="14.25" customHeight="1">
+      <c r="K46" s="55">
         <v>20019</v>
       </c>
-      <c r="O20" s="103"/>
-      <c r="P20" s="104"/>
-    </row>
-    <row r="21" spans="2:25" ht="21" customHeight="1">
-      <c r="K21" s="55"/>
-      <c r="L21" s="102">
+      <c r="L46" t="str">
+        <v>Deepak Singh</v>
+      </c>
+      <c r="M46">
+        <v>26</v>
+      </c>
+      <c r="N46" t="str">
+        <v>Accountant</v>
+      </c>
+      <c r="O46" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="P46">
+        <v>31500</v>
+      </c>
+      <c r="Q46" t="str">
+        <v>Bhopal</v>
+      </c>
+      <c r="R46" s="114">
+        <v>8745968745</v>
+      </c>
+    </row>
+    <row r="47" spans="11:18" ht="14.25" customHeight="1" thickBot="1">
+      <c r="K47" s="56">
+        <v>20020</v>
+      </c>
+      <c r="L47" s="57" t="str">
+        <v>Vikas Patel</v>
+      </c>
+      <c r="M47" s="57">
+        <v>28</v>
+      </c>
+      <c r="N47" s="57" t="str">
+        <v>Accountant</v>
+      </c>
+      <c r="O47" s="57" t="str">
+        <v>Finance</v>
+      </c>
+      <c r="P47" s="57">
         <v>40500</v>
       </c>
-      <c r="M21" s="103">
-        <v>28</v>
-      </c>
-      <c r="N21" s="103">
-        <v>20020</v>
-      </c>
-      <c r="O21" s="103"/>
-      <c r="P21" s="104"/>
-    </row>
-    <row r="22" spans="2:25" ht="14.25" customHeight="1">
-      <c r="K22" s="55"/>
-      <c r="L22" s="102">
-        <v>25500</v>
-      </c>
-      <c r="M22" s="103">
-        <v>27</v>
-      </c>
-      <c r="N22" s="103">
-        <v>20021</v>
-      </c>
-      <c r="O22" s="103"/>
-      <c r="P22" s="104"/>
-    </row>
-    <row r="23" spans="2:25" ht="14.25" customHeight="1" thickBot="1">
-      <c r="K23" s="55"/>
-      <c r="L23" s="102">
-        <v>18000</v>
-      </c>
-      <c r="M23" s="103">
-        <v>26</v>
-      </c>
-      <c r="N23" s="103">
-        <v>20022</v>
-      </c>
-      <c r="O23" s="103"/>
-      <c r="P23" s="104"/>
-    </row>
-    <row r="24" spans="2:25" ht="21" customHeight="1" thickBot="1">
-      <c r="B24" s="122" t="s">
-        <v>31</v>
-      </c>
-      <c r="C24" s="123"/>
-      <c r="D24" s="123"/>
-      <c r="E24" s="123"/>
-      <c r="F24" s="123"/>
-      <c r="G24" s="123"/>
-      <c r="H24" s="123"/>
-      <c r="I24" s="124"/>
-      <c r="K24" s="56"/>
-      <c r="L24" s="105">
-        <v>21000</v>
-      </c>
-      <c r="M24" s="106">
-        <v>27</v>
-      </c>
-      <c r="N24" s="106">
-        <v>20023</v>
-      </c>
-      <c r="O24" s="106"/>
-      <c r="P24" s="107"/>
-    </row>
-    <row r="25" spans="2:25" ht="14.25" customHeight="1">
-      <c r="B25" s="55" t="str">
-        <f t="array" ref="B25:I34">_xlfn._xlws.FILTER(A3:H15,C3:C15&gt;25)</f>
-        <v>Emp. ID</v>
-      </c>
-      <c r="C25" t="str">
-        <v>Name</v>
-      </c>
-      <c r="D25" t="str">
-        <v>Age</v>
-      </c>
-      <c r="E25" t="str">
-        <v>Designation</v>
-      </c>
-      <c r="F25" t="str">
-        <v>Department</v>
-      </c>
-      <c r="G25" t="str">
-        <v>Salary</v>
-      </c>
-      <c r="H25" t="str">
-        <v>Place</v>
-      </c>
-      <c r="I25" s="54" t="str">
-        <v>Mob.No.</v>
-      </c>
-    </row>
-    <row r="26" spans="2:25" ht="14.25" customHeight="1">
-      <c r="B26" s="55">
-        <v>20012</v>
-      </c>
-      <c r="C26" t="str">
-        <v>Kapil Sharma</v>
-      </c>
-      <c r="D26">
-        <v>26</v>
-      </c>
-      <c r="E26" t="str">
-        <v>Engineer</v>
-      </c>
-      <c r="F26" t="str">
-        <v>Technical</v>
-      </c>
-      <c r="G26">
-        <v>26500</v>
-      </c>
-      <c r="H26" t="str">
+      <c r="Q47" s="57" t="str">
         <v>Indore</v>
       </c>
-      <c r="I26" s="114">
-        <v>8877456987</v>
-      </c>
-    </row>
-    <row r="27" spans="2:25" ht="14.25" customHeight="1">
-      <c r="B27" s="55">
-        <v>20014</v>
-      </c>
-      <c r="C27" t="str">
-        <v>Kapil Singh</v>
-      </c>
-      <c r="D27">
-        <v>28</v>
-      </c>
-      <c r="E27" t="str">
-        <v>CAD Designer</v>
-      </c>
-      <c r="F27" t="str">
-        <v>Technical</v>
-      </c>
-      <c r="G27">
-        <v>20000</v>
-      </c>
-      <c r="H27" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="I27" s="114">
-        <v>7584963214</v>
-      </c>
-    </row>
-    <row r="28" spans="2:25" ht="14.25" customHeight="1">
-      <c r="B28" s="55">
-        <v>20015</v>
-      </c>
-      <c r="C28" t="str">
-        <v>Ali Asgar</v>
-      </c>
-      <c r="D28">
-        <v>27</v>
-      </c>
-      <c r="E28" t="str">
-        <v>Accountant</v>
-      </c>
-      <c r="F28" t="str">
-        <v>Finance</v>
-      </c>
-      <c r="G28">
-        <v>15000</v>
-      </c>
-      <c r="H28" t="str">
-        <v>Bhopal</v>
-      </c>
-      <c r="I28" s="114">
-        <v>7788994455</v>
-      </c>
-    </row>
-    <row r="29" spans="2:25" ht="14.25" customHeight="1">
-      <c r="B29" s="55">
-        <v>20017</v>
-      </c>
-      <c r="C29" t="str">
-        <v>Mohan Patel</v>
-      </c>
-      <c r="D29">
-        <v>26</v>
-      </c>
-      <c r="E29" t="str">
-        <v>Engineer</v>
-      </c>
-      <c r="F29" t="str">
-        <v>Technical</v>
-      </c>
-      <c r="G29">
-        <v>33000</v>
-      </c>
-      <c r="H29" t="str">
-        <v>Bhopal</v>
-      </c>
-      <c r="I29" s="114">
-        <v>9874563214</v>
-      </c>
-    </row>
-    <row r="30" spans="2:25" ht="14.25" customHeight="1">
-      <c r="B30" s="55">
-        <v>20019</v>
-      </c>
-      <c r="C30" t="str">
-        <v>Deepak Singh</v>
-      </c>
-      <c r="D30">
-        <v>26</v>
-      </c>
-      <c r="E30" t="str">
-        <v>Accountant</v>
-      </c>
-      <c r="F30" t="str">
-        <v>Finance</v>
-      </c>
-      <c r="G30">
-        <v>31500</v>
-      </c>
-      <c r="H30" t="str">
-        <v>Bhopal</v>
-      </c>
-      <c r="I30" s="114">
-        <v>8745968745</v>
-      </c>
-    </row>
-    <row r="31" spans="2:25" ht="14.25" customHeight="1">
-      <c r="B31" s="55">
-        <v>20020</v>
-      </c>
-      <c r="C31" t="str">
-        <v>Vikas Patel</v>
-      </c>
-      <c r="D31">
-        <v>28</v>
-      </c>
-      <c r="E31" t="str">
-        <v>Accountant</v>
-      </c>
-      <c r="F31" t="str">
-        <v>Finance</v>
-      </c>
-      <c r="G31">
-        <v>40500</v>
-      </c>
-      <c r="H31" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="I31" s="114">
+      <c r="R47" s="58">
         <v>9874569874</v>
       </c>
     </row>
-    <row r="32" spans="2:25" ht="14.25" customHeight="1">
-      <c r="B32" s="55">
-        <v>20021</v>
-      </c>
-      <c r="C32" t="str">
-        <v>Gopal Jat</v>
-      </c>
-      <c r="D32">
-        <v>27</v>
-      </c>
-      <c r="E32" t="str">
-        <v>Engineer</v>
-      </c>
-      <c r="F32" t="str">
-        <v>Technical</v>
-      </c>
-      <c r="G32">
-        <v>25500</v>
-      </c>
-      <c r="H32" t="str">
-        <v>ujjain</v>
-      </c>
-      <c r="I32" s="114">
-        <v>8574965874</v>
-      </c>
-    </row>
-    <row r="33" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B33" s="55">
-        <v>20022</v>
-      </c>
-      <c r="C33" t="str">
-        <v>Rohan Yadav</v>
-      </c>
-      <c r="D33">
-        <v>26</v>
-      </c>
-      <c r="E33" t="str">
-        <v>Accountant</v>
-      </c>
-      <c r="F33" t="str">
-        <v>Finance</v>
-      </c>
-      <c r="G33">
-        <v>18000</v>
-      </c>
-      <c r="H33" t="str">
-        <v>ujjain</v>
-      </c>
-      <c r="I33" s="114">
-        <v>8521479632</v>
-      </c>
-    </row>
-    <row r="34" spans="2:9" ht="14.25" customHeight="1" thickBot="1">
-      <c r="B34" s="56">
-        <v>20023</v>
-      </c>
-      <c r="C34" s="57" t="str">
-        <v>Janwi Rai</v>
-      </c>
-      <c r="D34" s="57">
-        <v>27</v>
-      </c>
-      <c r="E34" s="57" t="str">
-        <v>CAD Designer</v>
-      </c>
-      <c r="F34" s="57" t="str">
-        <v>Technical</v>
-      </c>
-      <c r="G34" s="57">
-        <v>21000</v>
-      </c>
-      <c r="H34" s="57" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="I34" s="58">
-        <v>8569745623</v>
-      </c>
-    </row>
-    <row r="35" spans="2:9" ht="21" customHeight="1">
-      <c r="B35" s="122" t="s">
-        <v>32</v>
-      </c>
-      <c r="C35" s="123"/>
-      <c r="D35" s="123"/>
-      <c r="E35" s="123"/>
-      <c r="F35" s="123"/>
-      <c r="G35" s="123"/>
-      <c r="H35" s="123"/>
-      <c r="I35" s="124"/>
-    </row>
-    <row r="36" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B36" s="55">
-        <f t="array" ref="B36:I42">_xlfn._xlws.FILTER(A3:H15,E3:E15="Technical")</f>
-        <v>20012</v>
-      </c>
-      <c r="C36" t="str">
-        <v>Kapil Sharma</v>
-      </c>
-      <c r="D36">
-        <v>26</v>
-      </c>
-      <c r="E36" t="str">
-        <v>Engineer</v>
-      </c>
-      <c r="F36" t="str">
-        <v>Technical</v>
-      </c>
-      <c r="G36">
-        <v>26500</v>
-      </c>
-      <c r="H36" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="I36" s="114">
-        <v>8877456987</v>
-      </c>
-    </row>
-    <row r="37" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B37" s="55">
-        <v>20014</v>
-      </c>
-      <c r="C37" t="str">
-        <v>Kapil Singh</v>
-      </c>
-      <c r="D37">
-        <v>28</v>
-      </c>
-      <c r="E37" t="str">
-        <v>CAD Designer</v>
-      </c>
-      <c r="F37" t="str">
-        <v>Technical</v>
-      </c>
-      <c r="G37">
-        <v>20000</v>
-      </c>
-      <c r="H37" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="I37" s="114">
-        <v>7584963214</v>
-      </c>
-    </row>
-    <row r="38" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B38" s="55">
-        <v>20016</v>
-      </c>
-      <c r="C38" t="str">
-        <v>Sunil Singh</v>
-      </c>
-      <c r="D38">
-        <v>25</v>
-      </c>
-      <c r="E38" t="str">
-        <v>Engineer</v>
-      </c>
-      <c r="F38" t="str">
-        <v>Technical</v>
-      </c>
-      <c r="G38">
-        <v>20000</v>
-      </c>
-      <c r="H38" t="str">
-        <v>ujjain</v>
-      </c>
-      <c r="I38" s="114">
-        <v>8798654512</v>
-      </c>
-    </row>
-    <row r="39" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B39" s="55">
-        <v>20017</v>
-      </c>
-      <c r="C39" t="str">
-        <v>Mohan Patel</v>
-      </c>
-      <c r="D39">
-        <v>26</v>
-      </c>
-      <c r="E39" t="str">
-        <v>Engineer</v>
-      </c>
-      <c r="F39" t="str">
-        <v>Technical</v>
-      </c>
-      <c r="G39">
-        <v>33000</v>
-      </c>
-      <c r="H39" t="str">
-        <v>Bhopal</v>
-      </c>
-      <c r="I39" s="114">
-        <v>9874563214</v>
-      </c>
-    </row>
-    <row r="40" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B40" s="55">
-        <v>20018</v>
-      </c>
-      <c r="C40" t="str">
-        <v>Ravi Verma</v>
-      </c>
-      <c r="D40">
-        <v>25</v>
-      </c>
-      <c r="E40" t="str">
-        <v>CAD Designer</v>
-      </c>
-      <c r="F40" t="str">
-        <v>Technical</v>
-      </c>
-      <c r="G40">
-        <v>21000</v>
-      </c>
-      <c r="H40" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="I40" s="114">
-        <v>8974563214</v>
-      </c>
-    </row>
-    <row r="41" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B41" s="55">
-        <v>20021</v>
-      </c>
-      <c r="C41" t="str">
-        <v>Gopal Jat</v>
-      </c>
-      <c r="D41">
-        <v>27</v>
-      </c>
-      <c r="E41" t="str">
-        <v>Engineer</v>
-      </c>
-      <c r="F41" t="str">
-        <v>Technical</v>
-      </c>
-      <c r="G41">
-        <v>25500</v>
-      </c>
-      <c r="H41" t="str">
-        <v>ujjain</v>
-      </c>
-      <c r="I41" s="114">
-        <v>8574965874</v>
-      </c>
-    </row>
-    <row r="42" spans="2:9" ht="14.25" customHeight="1" thickBot="1">
-      <c r="B42" s="56">
-        <v>20023</v>
-      </c>
-      <c r="C42" s="57" t="str">
-        <v>Janwi Rai</v>
-      </c>
-      <c r="D42" s="57">
-        <v>27</v>
-      </c>
-      <c r="E42" s="57" t="str">
-        <v>CAD Designer</v>
-      </c>
-      <c r="F42" s="57" t="str">
-        <v>Technical</v>
-      </c>
-      <c r="G42" s="57">
-        <v>21000</v>
-      </c>
-      <c r="H42" s="57" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="I42" s="58">
-        <v>8569745623</v>
-      </c>
-    </row>
-    <row r="43" spans="2:9" ht="21" customHeight="1">
-      <c r="B43" s="122" t="s">
-        <v>33</v>
-      </c>
-      <c r="C43" s="123"/>
-      <c r="D43" s="123"/>
-      <c r="E43" s="123"/>
-      <c r="F43" s="123"/>
-      <c r="G43" s="123"/>
-      <c r="H43" s="123"/>
-      <c r="I43" s="124"/>
-    </row>
-    <row r="44" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B44" s="55">
-        <f t="array" ref="B44:I47">_xlfn._xlws.FILTER(A3:H15,G3:G15="Bhopal")</f>
-        <v>20013</v>
-      </c>
-      <c r="C44" t="str">
-        <v>Sunil Grover</v>
-      </c>
-      <c r="D44">
-        <v>25</v>
-      </c>
-      <c r="E44" t="str">
-        <v>Accountant</v>
-      </c>
-      <c r="F44" t="str">
-        <v>Finance</v>
-      </c>
-      <c r="G44">
-        <v>13000</v>
-      </c>
-      <c r="H44" t="str">
-        <v>Bhopal</v>
-      </c>
-      <c r="I44" s="114">
-        <v>8569741235</v>
-      </c>
-    </row>
-    <row r="45" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B45" s="55">
-        <v>20015</v>
-      </c>
-      <c r="C45" t="str">
-        <v>Ali Asgar</v>
-      </c>
-      <c r="D45">
-        <v>27</v>
-      </c>
-      <c r="E45" t="str">
-        <v>Accountant</v>
-      </c>
-      <c r="F45" t="str">
-        <v>Finance</v>
-      </c>
-      <c r="G45">
-        <v>15000</v>
-      </c>
-      <c r="H45" t="str">
-        <v>Bhopal</v>
-      </c>
-      <c r="I45" s="114">
-        <v>7788994455</v>
-      </c>
-    </row>
-    <row r="46" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B46" s="55">
-        <v>20017</v>
-      </c>
-      <c r="C46" t="str">
-        <v>Mohan Patel</v>
-      </c>
-      <c r="D46">
-        <v>26</v>
-      </c>
-      <c r="E46" t="str">
-        <v>Engineer</v>
-      </c>
-      <c r="F46" t="str">
-        <v>Technical</v>
-      </c>
-      <c r="G46">
-        <v>33000</v>
-      </c>
-      <c r="H46" t="str">
-        <v>Bhopal</v>
-      </c>
-      <c r="I46" s="114">
-        <v>9874563214</v>
-      </c>
-    </row>
-    <row r="47" spans="2:9" ht="14.25" customHeight="1" thickBot="1">
-      <c r="B47" s="56">
-        <v>20019</v>
-      </c>
-      <c r="C47" s="57" t="str">
-        <v>Deepak Singh</v>
-      </c>
-      <c r="D47" s="57">
-        <v>26</v>
-      </c>
-      <c r="E47" s="57" t="str">
-        <v>Accountant</v>
-      </c>
-      <c r="F47" s="57" t="str">
-        <v>Finance</v>
-      </c>
-      <c r="G47" s="57">
-        <v>31500</v>
-      </c>
-      <c r="H47" s="57" t="str">
-        <v>Bhopal</v>
-      </c>
-      <c r="I47" s="58">
-        <v>8745968745</v>
-      </c>
-    </row>
-    <row r="48" spans="2:9" ht="21" customHeight="1">
-      <c r="B48" s="122" t="s">
-        <v>34</v>
-      </c>
-      <c r="C48" s="123"/>
-      <c r="D48" s="123"/>
-      <c r="E48" s="123"/>
-      <c r="F48" s="123"/>
-      <c r="G48" s="123"/>
-      <c r="H48" s="123"/>
-      <c r="I48" s="124"/>
-    </row>
-    <row r="49" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B49" s="55" t="str">
-        <f t="array" ref="B49:I52">_xlfn._xlws.FILTER(A3:H15,F3:F15&gt;30000)</f>
-        <v>Emp. ID</v>
-      </c>
-      <c r="C49" t="str">
-        <v>Name</v>
-      </c>
-      <c r="D49" t="str">
-        <v>Age</v>
-      </c>
-      <c r="E49" t="str">
-        <v>Designation</v>
-      </c>
-      <c r="F49" t="str">
-        <v>Department</v>
-      </c>
-      <c r="G49" t="str">
-        <v>Salary</v>
-      </c>
-      <c r="H49" t="str">
-        <v>Place</v>
-      </c>
-      <c r="I49" s="54" t="str">
-        <v>Mob.No.</v>
-      </c>
-    </row>
-    <row r="50" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B50" s="55">
-        <v>20017</v>
-      </c>
-      <c r="C50" t="str">
-        <v>Mohan Patel</v>
-      </c>
-      <c r="D50">
-        <v>26</v>
-      </c>
-      <c r="E50" t="str">
-        <v>Engineer</v>
-      </c>
-      <c r="F50" t="str">
-        <v>Technical</v>
-      </c>
-      <c r="G50">
-        <v>33000</v>
-      </c>
-      <c r="H50" t="str">
-        <v>Bhopal</v>
-      </c>
-      <c r="I50" s="114">
-        <v>9874563214</v>
-      </c>
-    </row>
-    <row r="51" spans="2:9" ht="14.25" customHeight="1">
-      <c r="B51" s="55">
-        <v>20019</v>
-      </c>
-      <c r="C51" t="str">
-        <v>Deepak Singh</v>
-      </c>
-      <c r="D51">
-        <v>26</v>
-      </c>
-      <c r="E51" t="str">
-        <v>Accountant</v>
-      </c>
-      <c r="F51" t="str">
-        <v>Finance</v>
-      </c>
-      <c r="G51">
-        <v>31500</v>
-      </c>
-      <c r="H51" t="str">
-        <v>Bhopal</v>
-      </c>
-      <c r="I51" s="114">
-        <v>8745968745</v>
-      </c>
-    </row>
-    <row r="52" spans="2:9" ht="14.25" customHeight="1" thickBot="1">
-      <c r="B52" s="56">
-        <v>20020</v>
-      </c>
-      <c r="C52" s="57" t="str">
-        <v>Vikas Patel</v>
-      </c>
-      <c r="D52" s="57">
-        <v>28</v>
-      </c>
-      <c r="E52" s="57" t="str">
-        <v>Accountant</v>
-      </c>
-      <c r="F52" s="57" t="str">
-        <v>Finance</v>
-      </c>
-      <c r="G52" s="57">
-        <v>40500</v>
-      </c>
-      <c r="H52" s="57" t="str">
-        <v>Indore</v>
-      </c>
-      <c r="I52" s="58">
-        <v>9874569874</v>
-      </c>
-    </row>
-    <row r="55" spans="2:9" ht="21" customHeight="1"/>
-    <row r="56" spans="2:9" ht="68.25" customHeight="1"/>
-    <row r="57" spans="2:9" ht="81.75" customHeight="1"/>
-    <row r="58" spans="2:9" ht="41.25" customHeight="1"/>
-    <row r="59" spans="2:9" ht="27.75" customHeight="1"/>
-    <row r="60" spans="2:9" ht="41.25" customHeight="1"/>
-    <row r="61" spans="2:9" ht="27.75" customHeight="1"/>
-    <row r="62" spans="2:9" ht="54.75" customHeight="1"/>
-    <row r="63" spans="2:9" ht="95.25" customHeight="1"/>
-    <row r="64" spans="2:9" ht="68.25" customHeight="1"/>
+    <row r="48" spans="11:18" ht="21" customHeight="1"/>
+    <row r="49" ht="14.25" customHeight="1"/>
+    <row r="50" ht="14.25" customHeight="1"/>
+    <row r="51" ht="14.25" customHeight="1"/>
+    <row r="52" ht="14.25" customHeight="1"/>
+    <row r="55" ht="21" customHeight="1"/>
+    <row r="56" ht="68.25" customHeight="1"/>
+    <row r="57" ht="81.75" customHeight="1"/>
+    <row r="58" ht="41.25" customHeight="1"/>
+    <row r="59" ht="27.75" customHeight="1"/>
+    <row r="60" ht="41.25" customHeight="1"/>
+    <row r="61" ht="27.75" customHeight="1"/>
+    <row r="62" ht="54.75" customHeight="1"/>
+    <row r="63" ht="95.25" customHeight="1"/>
+    <row r="64" ht="68.25" customHeight="1"/>
     <row r="65" ht="41.25" customHeight="1"/>
     <row r="66" ht="68.25" customHeight="1"/>
     <row r="67" ht="41.25" customHeight="1"/>
@@ -3377,13 +3372,13 @@
     <row r="70" ht="81.75" customHeight="1"/>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="B43:I43"/>
-    <mergeCell ref="B48:I48"/>
+    <mergeCell ref="K38:R38"/>
+    <mergeCell ref="K43:R43"/>
     <mergeCell ref="W2:X2"/>
     <mergeCell ref="A1:H2"/>
     <mergeCell ref="K3:Q3"/>
-    <mergeCell ref="B24:I24"/>
-    <mergeCell ref="B35:I35"/>
+    <mergeCell ref="K19:R19"/>
+    <mergeCell ref="K30:R30"/>
   </mergeCells>
   <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="A4:A15" xr:uid="{00000000-0002-0000-0000-000000000000}">
@@ -3544,7 +3539,7 @@
         <v>60</v>
       </c>
       <c r="K2" s="4">
-        <f>SUBTOTAL(9,H4:H15)</f>
+        <f t="array" ref="K2">SUBTOTAL(9,H4:H15)</f>
         <v>43850</v>
       </c>
     </row>
